--- a/INVENTARIO_AMPERIAL_2026.xlsx
+++ b/INVENTARIO_AMPERIAL_2026.xlsx
@@ -1,16 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Amperial Website\AmperialWebsite\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFD80A2-A596-4AF4-80D1-3A7ADF6C0CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="11520" windowHeight="7995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEPTIEMBRE 2026" sheetId="1" r:id="rId1"/>
     <sheet name="OCTUBRE 2026" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1892,7 +1912,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd"/>
   </numFmts>
@@ -1995,7 +2015,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2074,6 +2094,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2424,7 +2450,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2620,9 +2646,6 @@
     <xf numFmtId="49" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2724,6 +2747,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="15" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="15" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="20% - Énfasis1" xfId="2" builtinId="30"/>
@@ -2878,17 +2910,17 @@
     </dxf>
   </dxfs>
   <tableStyles count="3" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="INVENTARIO-style" pivot="0" count="3">
+    <tableStyle name="INVENTARIO-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="headerRow" dxfId="20"/>
       <tableStyleElement type="firstRowStripe" dxfId="19"/>
       <tableStyleElement type="secondRowStripe" dxfId="18"/>
     </tableStyle>
-    <tableStyle name="INVENTARIO-style 2" pivot="0" count="3">
+    <tableStyle name="INVENTARIO-style 2" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="headerRow" dxfId="17"/>
       <tableStyleElement type="firstRowStripe" dxfId="16"/>
       <tableStyleElement type="secondRowStripe" dxfId="15"/>
     </tableStyle>
-    <tableStyle name="INVENTARIO-style 3" pivot="0" count="3">
+    <tableStyle name="INVENTARIO-style 3" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
       <tableStyleElement type="headerRow" dxfId="14"/>
       <tableStyleElement type="firstRowStripe" dxfId="13"/>
       <tableStyleElement type="secondRowStripe" dxfId="12"/>
@@ -2898,71 +2930,74 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PRODUCTOS" displayName="PRODUCTOS" ref="B3:H303" headerRowDxfId="11">
-  <sortState ref="B4:G289">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PRODUCTOS" displayName="PRODUCTOS" ref="B3:H303" headerRowDxfId="11">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:G289">
     <sortCondition ref="B3"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" name="CÓDIGO DEL PRODUCTO" dataDxfId="10"/>
-    <tableColumn id="2" name="NOMBRE DEL PRODUCTO" dataDxfId="9"/>
-    <tableColumn id="6" name="CONTEO INICIAL" dataDxfId="8"/>
-    <tableColumn id="3" name="ENTRADAS">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="CÓDIGO DEL PRODUCTO" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="NOMBRE DEL PRODUCTO" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CONTEO INICIAL" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ENTRADAS">
       <calculatedColumnFormula>SUMIF($J$4:$J$5000, B4, $M$4:$M$5000)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" name="SALIDAS">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="SALIDAS">
       <calculatedColumnFormula>SUMIF($O$4:$O$5000, B4, $R$4:$R$5000)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" name="STOCK" dataDxfId="7">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="STOCK" dataDxfId="7">
       <calculatedColumnFormula>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E4-F4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="Columna1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Columna1"/>
   </tableColumns>
   <tableStyleInfo name="INVENTARIO-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ENTRADAS" displayName="ENTRADAS" ref="J3:M287" headerRowDxfId="6" headerRowCellStyle="Énfasis3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ENTRADAS" displayName="ENTRADAS" ref="J3:M287" headerRowDxfId="6" headerRowCellStyle="Énfasis3">
   <tableColumns count="4">
-    <tableColumn id="1" name="COD"/>
-    <tableColumn id="2" name="PRODUCTO"/>
-    <tableColumn id="3" name="FECHA"/>
-    <tableColumn id="4" name="CANTIDAD"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="COD"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="PRODUCTO"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="FECHA"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="CANTIDAD"/>
   </tableColumns>
   <tableStyleInfo name="INVENTARIO-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SALIDAS" displayName="SALIDAS" ref="O3:R287" headerRowDxfId="5" headerRowCellStyle="Énfasis3">
-  <autoFilter ref="O3:R287"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="SALIDAS" displayName="SALIDAS" ref="O3:R287" headerRowDxfId="5" headerRowCellStyle="Énfasis3">
+  <autoFilter ref="O3:R287" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="COD"/>
-    <tableColumn id="2" name="PRODUCTO"/>
-    <tableColumn id="3" name="FECHA"/>
-    <tableColumn id="4" name="CANTIDAD"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="COD"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="PRODUCTO"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="FECHA"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="CANTIDAD"/>
   </tableColumns>
   <tableStyleInfo name="INVENTARIO-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PRODUCTOS5" displayName="PRODUCTOS5" ref="B3:F287" headerRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="PRODUCTOS5" displayName="PRODUCTOS5" ref="B3:F287" headerRowDxfId="4">
   <tableColumns count="5">
-    <tableColumn id="1" name="CÓDIGO DEL PRODUCTO" dataDxfId="3"/>
-    <tableColumn id="2" name="NOMBRE DEL PRODUCTO" dataDxfId="2"/>
-    <tableColumn id="3" name="ENTRADAS">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="CÓDIGO DEL PRODUCTO" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="NOMBRE DEL PRODUCTO" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="ENTRADAS">
       <calculatedColumnFormula>SUMIF($I$4:$I$5000, B4, $L$4:$L$5000)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" name="SALIDAS">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="SALIDAS">
       <calculatedColumnFormula>SUMIF($N$4:$N$5000, B4, $Q$4:$Q$5000)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" name="STOCK">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="STOCK">
       <calculatedColumnFormula>D4-E4</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2971,29 +3006,29 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ENTRADAS6" displayName="ENTRADAS6" ref="I3:L287" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="ENTRADAS6" displayName="ENTRADAS6" ref="I3:L287" headerRowDxfId="1">
   <tableColumns count="4">
-    <tableColumn id="1" name="COD"/>
-    <tableColumn id="2" name="PRODUCTO">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="COD"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="PRODUCTO">
       <calculatedColumnFormula>IF(I4="", "", IFERROR(VLOOKUP(I4&amp;"", $B$4:$C$5000, 2, FALSE), "NO EXISTE"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="FECHA"/>
-    <tableColumn id="4" name="CANTIDAD"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="FECHA"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="CANTIDAD"/>
   </tableColumns>
   <tableStyleInfo name="INVENTARIO-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="SALIDAS7" displayName="SALIDAS7" ref="N3:Q287" headerRowDxfId="0">
-  <autoFilter ref="N3:Q287"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="SALIDAS7" displayName="SALIDAS7" ref="N3:Q287" headerRowDxfId="0">
+  <autoFilter ref="N3:Q287" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="COD"/>
-    <tableColumn id="2" name="PRODUCTO">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="COD"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="PRODUCTO">
       <calculatedColumnFormula>IF(N4="", "", IFERROR(VLOOKUP(N4&amp;"", $B$4:$C$5000, 2, FALSE), "NO EXISTE"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="FECHA"/>
-    <tableColumn id="4" name="CANTIDAD"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="FECHA"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="CANTIDAD"/>
   </tableColumns>
   <tableStyleInfo name="INVENTARIO-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3196,7 +3231,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -3204,7 +3239,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="3" max="3" width="71.85546875" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
@@ -3249,27 +3284,27 @@
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
+      <c r="B2" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
       <c r="H2" s="1"/>
-      <c r="J2" s="100" t="s">
+      <c r="J2" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="O2" s="100" t="s">
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="O2" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="100"/>
-      <c r="Q2" s="100"/>
-      <c r="R2" s="100"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
+      <c r="R2" s="99"/>
       <c r="T2" s="57" t="s">
         <v>574</v>
       </c>
@@ -3388,7 +3423,7 @@
       <c r="T4" s="51" t="s">
         <v>571</v>
       </c>
-      <c r="U4" s="79"/>
+      <c r="U4" s="78"/>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
@@ -3749,22 +3784,22 @@
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="80" t="s">
+      <c r="B13" s="79" t="s">
         <v>608</v>
       </c>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81" t="s">
+      <c r="C13" s="80"/>
+      <c r="D13" s="80" t="s">
         <v>609</v>
       </c>
-      <c r="E13" s="83">
+      <c r="E13" s="82">
         <f>SUMIF($J$4:$J$5000, B13, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="83">
+      <c r="F13" s="82">
         <f>SUMIF($O$4:$O$5000, B13, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="84">
+      <c r="G13" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E13-F13</f>
         <v>75</v>
       </c>
@@ -3789,24 +3824,24 @@
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="80" t="s">
+      <c r="B14" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="81" t="s">
+      <c r="C14" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="82">
+      <c r="D14" s="81">
         <v>20</v>
       </c>
-      <c r="E14" s="83">
+      <c r="E14" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F14" s="83">
+      <c r="F14" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G14" s="84">
+      <c r="G14" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E14-F14</f>
         <v>20</v>
       </c>
@@ -4016,24 +4051,24 @@
       <c r="R19" s="11"/>
     </row>
     <row r="20" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="74" t="s">
+      <c r="B20" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="75" t="s">
+      <c r="C20" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="76">
+      <c r="D20" s="75">
         <v>4</v>
       </c>
-      <c r="E20" s="77">
+      <c r="E20" s="76">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F20" s="77">
+      <c r="F20" s="76">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="78">
+      <c r="G20" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E20-F20</f>
         <v>4</v>
       </c>
@@ -4368,24 +4403,24 @@
       <c r="R29" s="11"/>
     </row>
     <row r="30" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="80" t="s">
+      <c r="B30" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="81" t="s">
+      <c r="C30" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="82">
+      <c r="D30" s="81">
         <v>10</v>
       </c>
-      <c r="E30" s="83">
+      <c r="E30" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F30" s="83">
+      <c r="F30" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G30" s="84">
+      <c r="G30" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E30-F30</f>
         <v>10</v>
       </c>
@@ -4405,24 +4440,24 @@
       <c r="R30" s="14"/>
     </row>
     <row r="31" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="80" t="s">
+      <c r="B31" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="81" t="s">
+      <c r="C31" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="82">
+      <c r="D31" s="81">
         <v>20</v>
       </c>
-      <c r="E31" s="83">
+      <c r="E31" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F31" s="83">
+      <c r="F31" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G31" s="84">
+      <c r="G31" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E31-F31</f>
         <v>20</v>
       </c>
@@ -5247,24 +5282,24 @@
       <c r="R54" s="14"/>
     </row>
     <row r="55" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="80" t="s">
+      <c r="B55" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="C55" s="81" t="s">
+      <c r="C55" s="80" t="s">
         <v>112</v>
       </c>
-      <c r="D55" s="82">
+      <c r="D55" s="81">
         <v>64</v>
       </c>
-      <c r="E55" s="83">
+      <c r="E55" s="82">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F55" s="83">
+      <c r="F55" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G55" s="84">
+      <c r="G55" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E55-F55</f>
         <v>64</v>
       </c>
@@ -5669,24 +5704,24 @@
       <c r="R66" s="14"/>
     </row>
     <row r="67" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="74" t="s">
+      <c r="B67" s="73" t="s">
         <v>600</v>
       </c>
-      <c r="C67" s="75" t="s">
+      <c r="C67" s="74" t="s">
         <v>136</v>
       </c>
-      <c r="D67" s="76">
+      <c r="D67" s="75">
         <v>8</v>
       </c>
-      <c r="E67" s="77">
+      <c r="E67" s="76">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F67" s="77">
+      <c r="F67" s="76">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G67" s="78">
+      <c r="G67" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E67-F67</f>
         <v>8</v>
       </c>
@@ -5706,24 +5741,24 @@
       <c r="R67" s="11"/>
     </row>
     <row r="68" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="74" t="s">
+      <c r="B68" s="73" t="s">
         <v>601</v>
       </c>
-      <c r="C68" s="75" t="s">
+      <c r="C68" s="74" t="s">
         <v>138</v>
       </c>
-      <c r="D68" s="76">
+      <c r="D68" s="75">
         <v>3</v>
       </c>
-      <c r="E68" s="77">
+      <c r="E68" s="76">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F68" s="77">
+      <c r="F68" s="76">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G68" s="78">
+      <c r="G68" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E68-F68</f>
         <v>3</v>
       </c>
@@ -5987,7 +6022,7 @@
       <c r="Q75" s="10"/>
       <c r="R75" s="11"/>
     </row>
-    <row r="76" spans="2:18" s="71" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:18" s="70" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B76" s="27" t="s">
         <v>152</v>
       </c>
@@ -6008,44 +6043,44 @@
         <v>250</v>
       </c>
       <c r="H76"/>
-      <c r="J76" s="88"/>
-      <c r="K76" s="85" t="str">
+      <c r="J76" s="87"/>
+      <c r="K76" s="84" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="L76" s="89"/>
-      <c r="M76" s="90"/>
-      <c r="O76" s="88"/>
-      <c r="P76" s="85" t="str">
+      <c r="L76" s="88"/>
+      <c r="M76" s="89"/>
+      <c r="O76" s="87"/>
+      <c r="P76" s="84" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q76" s="91"/>
-      <c r="R76" s="90"/>
+      <c r="Q76" s="90"/>
+      <c r="R76" s="89"/>
     </row>
     <row r="77" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="80" t="s">
+      <c r="B77" s="79" t="s">
         <v>154</v>
       </c>
-      <c r="C77" s="81" t="s">
+      <c r="C77" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="D77" s="82">
+      <c r="D77" s="81">
         <v>900</v>
       </c>
-      <c r="E77" s="83">
+      <c r="E77" s="82">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F77" s="83">
+      <c r="F77" s="82">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G77" s="84">
+      <c r="G77" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E77-F77</f>
         <v>900</v>
       </c>
-      <c r="H77" s="71"/>
+      <c r="H77" s="70"/>
       <c r="J77" s="9"/>
       <c r="K77" s="19" t="str">
         <f t="shared" si="4"/>
@@ -6062,24 +6097,24 @@
       <c r="R77" s="11"/>
     </row>
     <row r="78" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="80" t="s">
+      <c r="B78" s="79" t="s">
         <v>156</v>
       </c>
-      <c r="C78" s="81" t="s">
+      <c r="C78" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="D78" s="82">
+      <c r="D78" s="81">
         <v>132</v>
       </c>
-      <c r="E78" s="83">
+      <c r="E78" s="82">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F78" s="83">
+      <c r="F78" s="82">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G78" s="84">
+      <c r="G78" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E78-F78</f>
         <v>132</v>
       </c>
@@ -6133,7 +6168,7 @@
       <c r="Q79" s="10"/>
       <c r="R79" s="11"/>
     </row>
-    <row r="80" spans="2:18" s="71" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" s="70" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B80" s="27" t="s">
         <v>160</v>
       </c>
@@ -6154,44 +6189,44 @@
         <v>250</v>
       </c>
       <c r="H80"/>
-      <c r="J80" s="88"/>
-      <c r="K80" s="85" t="str">
+      <c r="J80" s="87"/>
+      <c r="K80" s="84" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="L80" s="89"/>
-      <c r="M80" s="90"/>
-      <c r="O80" s="88"/>
-      <c r="P80" s="85" t="str">
+      <c r="L80" s="88"/>
+      <c r="M80" s="89"/>
+      <c r="O80" s="87"/>
+      <c r="P80" s="84" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q80" s="91"/>
-      <c r="R80" s="90"/>
+      <c r="Q80" s="90"/>
+      <c r="R80" s="89"/>
     </row>
     <row r="81" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="80" t="s">
+      <c r="B81" s="79" t="s">
         <v>162</v>
       </c>
-      <c r="C81" s="81" t="s">
+      <c r="C81" s="80" t="s">
         <v>163</v>
       </c>
-      <c r="D81" s="82">
+      <c r="D81" s="81">
         <v>1000</v>
       </c>
-      <c r="E81" s="83">
+      <c r="E81" s="82">
         <f>SUMIF($J$4:$J$5000, B81, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F81" s="83">
+      <c r="F81" s="82">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G81" s="84">
+      <c r="G81" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E81-F81</f>
         <v>1000</v>
       </c>
-      <c r="H81" s="71"/>
+      <c r="H81" s="70"/>
       <c r="J81" s="9"/>
       <c r="K81" s="19" t="str">
         <f t="shared" si="4"/>
@@ -6523,24 +6558,24 @@
       <c r="R90" s="14"/>
     </row>
     <row r="91" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B91" s="74" t="s">
+      <c r="B91" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="C91" s="75" t="s">
+      <c r="C91" s="74" t="s">
         <v>183</v>
       </c>
-      <c r="D91" s="76">
+      <c r="D91" s="75">
         <v>4</v>
       </c>
-      <c r="E91" s="77">
+      <c r="E91" s="76">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F91" s="77">
+      <c r="F91" s="76">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G91" s="78">
+      <c r="G91" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E91-F91</f>
         <v>4</v>
       </c>
@@ -7117,22 +7152,22 @@
       </c>
     </row>
     <row r="109" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="74" t="s">
+      <c r="B109" s="73" t="s">
         <v>224</v>
       </c>
-      <c r="C109" s="75" t="s">
+      <c r="C109" s="74" t="s">
         <v>225</v>
       </c>
-      <c r="D109" s="76"/>
-      <c r="E109" s="77">
+      <c r="D109" s="75"/>
+      <c r="E109" s="76">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F109" s="77">
+      <c r="F109" s="76">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G109" s="78">
+      <c r="G109" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E109-F109</f>
         <v>0</v>
       </c>
@@ -7235,7 +7270,7 @@
       </c>
     </row>
     <row r="113" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="60" t="s">
+      <c r="B113" s="104" t="s">
         <v>206</v>
       </c>
       <c r="C113" s="61" t="s">
@@ -7449,7 +7484,7 @@
       </c>
     </row>
     <row r="120" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="60" t="s">
+      <c r="B120" s="104" t="s">
         <v>208</v>
       </c>
       <c r="C120" s="61" t="s">
@@ -7511,7 +7546,7 @@
       </c>
     </row>
     <row r="122" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B122" s="60" t="s">
+      <c r="B122" s="104" t="s">
         <v>210</v>
       </c>
       <c r="C122" s="61" t="s">
@@ -7600,7 +7635,7 @@
       </c>
     </row>
     <row r="125" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="44" t="s">
+      <c r="B125" s="104" t="s">
         <v>250</v>
       </c>
       <c r="C125" s="45" t="s">
@@ -7631,7 +7666,7 @@
       </c>
     </row>
     <row r="126" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="60" t="s">
+      <c r="B126" s="104" t="s">
         <v>252</v>
       </c>
       <c r="C126" s="61" t="s">
@@ -7662,7 +7697,7 @@
       </c>
     </row>
     <row r="127" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="60" t="s">
+      <c r="B127" s="104" t="s">
         <v>254</v>
       </c>
       <c r="C127" s="61" t="s">
@@ -7693,7 +7728,7 @@
       </c>
     </row>
     <row r="128" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B128" s="60" t="s">
+      <c r="B128" s="104" t="s">
         <v>256</v>
       </c>
       <c r="C128" s="61" t="s">
@@ -7724,7 +7759,7 @@
       </c>
     </row>
     <row r="129" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="67" t="s">
+      <c r="B129" s="105" t="s">
         <v>258</v>
       </c>
       <c r="C129" s="61" t="s">
@@ -7755,24 +7790,24 @@
       </c>
     </row>
     <row r="130" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="80" t="s">
+      <c r="B130" s="104" t="s">
         <v>260</v>
       </c>
-      <c r="C130" s="81" t="s">
+      <c r="C130" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="D130" s="82">
+      <c r="D130" s="81">
         <v>253</v>
       </c>
-      <c r="E130" s="83">
+      <c r="E130" s="82">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F130" s="83">
+      <c r="F130" s="82">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G130" s="84">
+      <c r="G130" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E130-F130</f>
         <v>253</v>
       </c>
@@ -7786,7 +7821,7 @@
       </c>
     </row>
     <row r="131" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="44" t="s">
+      <c r="B131" s="104" t="s">
         <v>262</v>
       </c>
       <c r="C131" s="45" t="s">
@@ -7846,24 +7881,24 @@
       </c>
     </row>
     <row r="133" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="74" t="s">
+      <c r="B133" s="104" t="s">
         <v>266</v>
       </c>
-      <c r="C133" s="75" t="s">
+      <c r="C133" s="74" t="s">
         <v>267</v>
       </c>
-      <c r="D133" s="76">
+      <c r="D133" s="75">
         <v>54</v>
       </c>
-      <c r="E133" s="77">
+      <c r="E133" s="76">
         <f t="shared" ref="E133:E198" si="9">SUMIF($J$4:$J$5000, B133, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F133" s="77">
+      <c r="F133" s="76">
         <f t="shared" ref="F133:F198" si="10">SUMIF($O$4:$O$5000, B133, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G133" s="78">
+      <c r="G133" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E133-F133</f>
         <v>54</v>
       </c>
@@ -7877,24 +7912,24 @@
       </c>
     </row>
     <row r="134" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B134" s="74" t="s">
+      <c r="B134" s="104" t="s">
         <v>268</v>
       </c>
-      <c r="C134" s="75" t="s">
+      <c r="C134" s="74" t="s">
         <v>269</v>
       </c>
-      <c r="D134" s="76">
+      <c r="D134" s="75">
         <v>60</v>
       </c>
-      <c r="E134" s="77">
+      <c r="E134" s="76">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F134" s="77">
+      <c r="F134" s="76">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G134" s="78">
+      <c r="G134" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E134-F134</f>
         <v>60</v>
       </c>
@@ -7908,7 +7943,7 @@
       </c>
     </row>
     <row r="135" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B135" s="44" t="s">
+      <c r="B135" s="104" t="s">
         <v>270</v>
       </c>
       <c r="C135" s="45" t="s">
@@ -7939,7 +7974,7 @@
       </c>
     </row>
     <row r="136" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B136" s="44" t="s">
+      <c r="B136" s="104" t="s">
         <v>272</v>
       </c>
       <c r="C136" s="45" t="s">
@@ -7970,7 +8005,7 @@
       </c>
     </row>
     <row r="137" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B137" s="44" t="s">
+      <c r="B137" s="104" t="s">
         <v>274</v>
       </c>
       <c r="C137" s="45" t="s">
@@ -8001,7 +8036,7 @@
       </c>
     </row>
     <row r="138" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B138" s="44" t="s">
+      <c r="B138" s="104" t="s">
         <v>276</v>
       </c>
       <c r="C138" s="45" t="s">
@@ -8091,7 +8126,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:16" s="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:16" s="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B141" s="44" t="s">
         <v>282</v>
       </c>
@@ -8114,72 +8149,72 @@
         <v>47</v>
       </c>
       <c r="H141"/>
-      <c r="K141" s="85" t="str">
+      <c r="K141" s="84" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P141" s="85" t="str">
+      <c r="P141" s="84" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="142" spans="2:16" s="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B142" s="80" t="s">
+    <row r="142" spans="2:16" s="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B142" s="79" t="s">
         <v>284</v>
       </c>
-      <c r="C142" s="81" t="s">
+      <c r="C142" s="80" t="s">
         <v>285</v>
       </c>
-      <c r="D142" s="82">
+      <c r="D142" s="81">
         <v>38</v>
       </c>
-      <c r="E142" s="83">
+      <c r="E142" s="82">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F142" s="83">
+      <c r="F142" s="82">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G142" s="84">
+      <c r="G142" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E142-F142</f>
         <v>38</v>
       </c>
-      <c r="H142" s="71" t="s">
+      <c r="H142" s="70" t="s">
         <v>605</v>
       </c>
-      <c r="K142" s="85" t="str">
+      <c r="K142" s="84" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P142" s="85" t="str">
+      <c r="P142" s="84" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="143" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B143" s="80" t="s">
+      <c r="B143" s="79" t="s">
         <v>286</v>
       </c>
-      <c r="C143" s="81" t="s">
+      <c r="C143" s="80" t="s">
         <v>287</v>
       </c>
-      <c r="D143" s="82">
+      <c r="D143" s="81">
         <v>18</v>
       </c>
-      <c r="E143" s="83">
+      <c r="E143" s="82">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F143" s="83">
+      <c r="F143" s="82">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G143" s="84">
+      <c r="G143" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E143-F143</f>
         <v>18</v>
       </c>
-      <c r="H143" s="71"/>
+      <c r="H143" s="70"/>
       <c r="K143" s="19" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8190,7 +8225,7 @@
       </c>
     </row>
     <row r="144" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B144" s="60" t="s">
+      <c r="B144" s="104" t="s">
         <v>212</v>
       </c>
       <c r="C144" s="61" t="s">
@@ -8456,7 +8491,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:16" s="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:16" s="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B153" s="49" t="s">
         <v>576</v>
       </c>
@@ -8477,36 +8512,36 @@
         <v>37</v>
       </c>
       <c r="H153"/>
-      <c r="K153" s="85" t="str">
+      <c r="K153" s="84" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P153" s="85" t="str">
+      <c r="P153" s="84" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="154" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B154" s="86" t="s">
+      <c r="B154" s="85" t="s">
         <v>606</v>
       </c>
-      <c r="C154" s="81"/>
-      <c r="D154" s="87" t="s">
+      <c r="C154" s="80"/>
+      <c r="D154" s="86" t="s">
         <v>607</v>
       </c>
-      <c r="E154" s="83">
+      <c r="E154" s="82">
         <f>SUMIF($J$4:$J$5000, B154, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F154" s="83">
+      <c r="F154" s="82">
         <f>SUMIF($O$4:$O$5000, B154, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G154" s="84">
+      <c r="G154" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E154-F154</f>
         <v>47</v>
       </c>
-      <c r="H154" s="71"/>
+      <c r="H154" s="70"/>
       <c r="K154" s="19" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8517,24 +8552,24 @@
       </c>
     </row>
     <row r="155" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B155" s="80" t="s">
+      <c r="B155" s="79" t="s">
         <v>304</v>
       </c>
-      <c r="C155" s="81" t="s">
+      <c r="C155" s="80" t="s">
         <v>305</v>
       </c>
-      <c r="D155" s="82">
+      <c r="D155" s="81">
         <v>260</v>
       </c>
-      <c r="E155" s="83">
+      <c r="E155" s="82">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F155" s="83">
+      <c r="F155" s="82">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G155" s="84">
+      <c r="G155" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E155-F155</f>
         <v>260</v>
       </c>
@@ -8606,24 +8641,24 @@
       </c>
     </row>
     <row r="158" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B158" s="80" t="s">
+      <c r="B158" s="79" t="s">
         <v>310</v>
       </c>
-      <c r="C158" s="81" t="s">
+      <c r="C158" s="80" t="s">
         <v>311</v>
       </c>
-      <c r="D158" s="82">
+      <c r="D158" s="81">
         <v>33</v>
       </c>
-      <c r="E158" s="83">
+      <c r="E158" s="82">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F158" s="83">
+      <c r="F158" s="82">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G158" s="84">
+      <c r="G158" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E158-F158</f>
         <v>33</v>
       </c>
@@ -8811,28 +8846,28 @@
       </c>
     </row>
     <row r="165" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B165" s="74" t="s">
+      <c r="B165" s="73" t="s">
         <v>324</v>
       </c>
-      <c r="C165" s="75" t="s">
+      <c r="C165" s="74" t="s">
         <v>325</v>
       </c>
-      <c r="D165" s="76">
+      <c r="D165" s="75">
         <v>2</v>
       </c>
-      <c r="E165" s="77">
+      <c r="E165" s="76">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F165" s="77">
+      <c r="F165" s="76">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G165" s="78">
+      <c r="G165" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E165-F165</f>
         <v>2</v>
       </c>
-      <c r="H165" s="72" t="s">
+      <c r="H165" s="71" t="s">
         <v>586</v>
       </c>
       <c r="K165" s="19" t="str">
@@ -8874,24 +8909,24 @@
       </c>
     </row>
     <row r="167" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B167" s="74" t="s">
+      <c r="B167" s="73" t="s">
         <v>328</v>
       </c>
-      <c r="C167" s="75" t="s">
+      <c r="C167" s="74" t="s">
         <v>329</v>
       </c>
-      <c r="D167" s="76">
+      <c r="D167" s="75">
         <v>5</v>
       </c>
-      <c r="E167" s="77">
+      <c r="E167" s="76">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F167" s="77">
+      <c r="F167" s="76">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G167" s="78">
+      <c r="G167" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E167-F167</f>
         <v>5</v>
       </c>
@@ -8905,24 +8940,24 @@
       </c>
     </row>
     <row r="168" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B168" s="80" t="s">
+      <c r="B168" s="79" t="s">
         <v>332</v>
       </c>
-      <c r="C168" s="81" t="s">
+      <c r="C168" s="80" t="s">
         <v>333</v>
       </c>
-      <c r="D168" s="82">
+      <c r="D168" s="81">
         <v>10</v>
       </c>
-      <c r="E168" s="83">
+      <c r="E168" s="82">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F168" s="83">
+      <c r="F168" s="82">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G168" s="84">
+      <c r="G168" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E168-F168</f>
         <v>10</v>
       </c>
@@ -8936,24 +8971,24 @@
       </c>
     </row>
     <row r="169" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B169" s="80" t="s">
+      <c r="B169" s="79" t="s">
         <v>330</v>
       </c>
-      <c r="C169" s="81" t="s">
+      <c r="C169" s="80" t="s">
         <v>331</v>
       </c>
-      <c r="D169" s="82">
+      <c r="D169" s="81">
         <v>4</v>
       </c>
-      <c r="E169" s="83">
+      <c r="E169" s="82">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F169" s="83">
+      <c r="F169" s="82">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G169" s="84">
+      <c r="G169" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E169-F169</f>
         <v>4</v>
       </c>
@@ -9112,24 +9147,24 @@
       </c>
     </row>
     <row r="175" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B175" s="74" t="s">
+      <c r="B175" s="73" t="s">
         <v>346</v>
       </c>
-      <c r="C175" s="75" t="s">
+      <c r="C175" s="74" t="s">
         <v>347</v>
       </c>
-      <c r="D175" s="76">
+      <c r="D175" s="75">
         <v>156</v>
       </c>
-      <c r="E175" s="77">
+      <c r="E175" s="76">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F175" s="77">
+      <c r="F175" s="76">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G175" s="78">
+      <c r="G175" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E175-F175</f>
         <v>156</v>
       </c>
@@ -9143,24 +9178,24 @@
       </c>
     </row>
     <row r="176" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B176" s="74" t="s">
+      <c r="B176" s="73" t="s">
         <v>348</v>
       </c>
-      <c r="C176" s="75" t="s">
+      <c r="C176" s="74" t="s">
         <v>349</v>
       </c>
-      <c r="D176" s="76">
+      <c r="D176" s="75">
         <v>1</v>
       </c>
-      <c r="E176" s="77">
+      <c r="E176" s="76">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F176" s="77">
+      <c r="F176" s="76">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G176" s="78">
+      <c r="G176" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E176-F176</f>
         <v>1</v>
       </c>
@@ -9174,24 +9209,24 @@
       </c>
     </row>
     <row r="177" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B177" s="74" t="s">
+      <c r="B177" s="73" t="s">
         <v>350</v>
       </c>
-      <c r="C177" s="75" t="s">
+      <c r="C177" s="74" t="s">
         <v>351</v>
       </c>
-      <c r="D177" s="76">
+      <c r="D177" s="75">
         <v>42</v>
       </c>
-      <c r="E177" s="77">
+      <c r="E177" s="76">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F177" s="77">
+      <c r="F177" s="76">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G177" s="78">
+      <c r="G177" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E177-F177</f>
         <v>42</v>
       </c>
@@ -9205,24 +9240,24 @@
       </c>
     </row>
     <row r="178" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B178" s="74" t="s">
+      <c r="B178" s="73" t="s">
         <v>352</v>
       </c>
-      <c r="C178" s="75" t="s">
+      <c r="C178" s="74" t="s">
         <v>353</v>
       </c>
-      <c r="D178" s="76">
+      <c r="D178" s="75">
         <v>2</v>
       </c>
-      <c r="E178" s="77">
+      <c r="E178" s="76">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F178" s="77">
+      <c r="F178" s="76">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G178" s="78">
+      <c r="G178" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E178-F178</f>
         <v>2</v>
       </c>
@@ -9236,24 +9271,24 @@
       </c>
     </row>
     <row r="179" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B179" s="74" t="s">
+      <c r="B179" s="73" t="s">
         <v>620</v>
       </c>
-      <c r="C179" s="75" t="s">
+      <c r="C179" s="74" t="s">
         <v>621</v>
       </c>
-      <c r="D179" s="75" t="s">
+      <c r="D179" s="74" t="s">
         <v>622</v>
       </c>
-      <c r="E179" s="77">
+      <c r="E179" s="76">
         <f>SUMIF($J$4:$J$5000, B179, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F179" s="77">
+      <c r="F179" s="76">
         <f>SUMIF($O$4:$O$5000, B179, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G179" s="78">
+      <c r="G179" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E179-F179</f>
         <v>4</v>
       </c>
@@ -9470,24 +9505,24 @@
       </c>
     </row>
     <row r="187" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B187" s="74" t="s">
+      <c r="B187" s="73" t="s">
         <v>604</v>
       </c>
-      <c r="C187" s="75" t="s">
+      <c r="C187" s="74" t="s">
         <v>366</v>
       </c>
-      <c r="D187" s="76">
+      <c r="D187" s="75">
         <v>1</v>
       </c>
-      <c r="E187" s="77">
+      <c r="E187" s="76">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F187" s="77">
+      <c r="F187" s="76">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G187" s="78">
+      <c r="G187" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E187-F187</f>
         <v>1</v>
       </c>
@@ -9530,24 +9565,24 @@
       </c>
     </row>
     <row r="189" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B189" s="74" t="s">
+      <c r="B189" s="73" t="s">
         <v>369</v>
       </c>
-      <c r="C189" s="75" t="s">
+      <c r="C189" s="74" t="s">
         <v>370</v>
       </c>
-      <c r="D189" s="76">
+      <c r="D189" s="75">
         <v>4</v>
       </c>
-      <c r="E189" s="77">
+      <c r="E189" s="76">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F189" s="77">
+      <c r="F189" s="76">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G189" s="78">
+      <c r="G189" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E189-F189</f>
         <v>4</v>
       </c>
@@ -9561,24 +9596,24 @@
       </c>
     </row>
     <row r="190" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B190" s="74" t="s">
+      <c r="B190" s="73" t="s">
         <v>371</v>
       </c>
-      <c r="C190" s="75" t="s">
+      <c r="C190" s="74" t="s">
         <v>372</v>
       </c>
-      <c r="D190" s="76">
+      <c r="D190" s="75">
         <v>61</v>
       </c>
-      <c r="E190" s="77">
+      <c r="E190" s="76">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F190" s="77">
+      <c r="F190" s="76">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G190" s="78">
+      <c r="G190" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E190-F190</f>
         <v>61</v>
       </c>
@@ -9620,7 +9655,7 @@
         <v/>
       </c>
     </row>
-    <row r="192" spans="2:16" s="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:16" s="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B192" s="27" t="s">
         <v>375</v>
       </c>
@@ -9641,16 +9676,16 @@
         <v>0</v>
       </c>
       <c r="H192"/>
-      <c r="K192" s="85" t="str">
+      <c r="K192" s="84" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P192" s="85" t="str">
+      <c r="P192" s="84" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="193" spans="2:16" s="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:16" s="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B193" s="27" t="s">
         <v>376</v>
       </c>
@@ -9671,38 +9706,38 @@
         <v>0</v>
       </c>
       <c r="H193"/>
-      <c r="K193" s="85" t="str">
+      <c r="K193" s="84" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P193" s="85" t="str">
+      <c r="P193" s="84" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="194" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B194" s="80" t="s">
+      <c r="B194" s="79" t="s">
         <v>378</v>
       </c>
-      <c r="C194" s="81" t="s">
+      <c r="C194" s="80" t="s">
         <v>379</v>
       </c>
-      <c r="D194" s="82">
+      <c r="D194" s="81">
         <v>165</v>
       </c>
-      <c r="E194" s="83">
+      <c r="E194" s="82">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F194" s="83">
+      <c r="F194" s="82">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G194" s="84">
+      <c r="G194" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E194-F194</f>
         <v>165</v>
       </c>
-      <c r="H194" s="71"/>
+      <c r="H194" s="70"/>
       <c r="K194" s="19" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9713,28 +9748,28 @@
       </c>
     </row>
     <row r="195" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B195" s="80" t="s">
+      <c r="B195" s="79" t="s">
         <v>380</v>
       </c>
-      <c r="C195" s="81" t="s">
+      <c r="C195" s="80" t="s">
         <v>381</v>
       </c>
-      <c r="D195" s="82">
+      <c r="D195" s="81">
         <v>329</v>
       </c>
-      <c r="E195" s="83">
+      <c r="E195" s="82">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F195" s="83">
+      <c r="F195" s="82">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G195" s="84">
+      <c r="G195" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E195-F195</f>
         <v>329</v>
       </c>
-      <c r="H195" s="71"/>
+      <c r="H195" s="70"/>
       <c r="K195" s="19" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -10035,24 +10070,24 @@
       </c>
     </row>
     <row r="206" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B206" s="74" t="s">
+      <c r="B206" s="73" t="s">
         <v>406</v>
       </c>
-      <c r="C206" s="75" t="s">
+      <c r="C206" s="74" t="s">
         <v>407</v>
       </c>
-      <c r="D206" s="76">
+      <c r="D206" s="75">
         <v>50</v>
       </c>
-      <c r="E206" s="77">
+      <c r="E206" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F206" s="77">
+      <c r="F206" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G206" s="78">
+      <c r="G206" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E206-F206</f>
         <v>50</v>
       </c>
@@ -10066,24 +10101,24 @@
       </c>
     </row>
     <row r="207" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B207" s="74" t="s">
+      <c r="B207" s="73" t="s">
         <v>408</v>
       </c>
-      <c r="C207" s="75" t="s">
+      <c r="C207" s="74" t="s">
         <v>409</v>
       </c>
-      <c r="D207" s="76">
+      <c r="D207" s="75">
         <v>30</v>
       </c>
-      <c r="E207" s="77">
+      <c r="E207" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F207" s="77">
+      <c r="F207" s="76">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
-      <c r="G207" s="78">
+      <c r="G207" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E207-F207</f>
         <v>10</v>
       </c>
@@ -10129,24 +10164,24 @@
       </c>
     </row>
     <row r="209" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B209" s="74" t="s">
+      <c r="B209" s="73" t="s">
         <v>412</v>
       </c>
-      <c r="C209" s="75" t="s">
+      <c r="C209" s="74" t="s">
         <v>413</v>
       </c>
-      <c r="D209" s="76">
+      <c r="D209" s="75">
         <v>70</v>
       </c>
-      <c r="E209" s="77">
+      <c r="E209" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F209" s="77">
+      <c r="F209" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G209" s="78">
+      <c r="G209" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E209-F209</f>
         <v>70</v>
       </c>
@@ -10160,24 +10195,24 @@
       </c>
     </row>
     <row r="210" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B210" s="74" t="s">
+      <c r="B210" s="73" t="s">
         <v>414</v>
       </c>
-      <c r="C210" s="75" t="s">
+      <c r="C210" s="74" t="s">
         <v>415</v>
       </c>
-      <c r="D210" s="76">
+      <c r="D210" s="75">
         <v>80</v>
       </c>
-      <c r="E210" s="77">
+      <c r="E210" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F210" s="77">
+      <c r="F210" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G210" s="78">
+      <c r="G210" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E210-F210</f>
         <v>80</v>
       </c>
@@ -10220,24 +10255,24 @@
       </c>
     </row>
     <row r="212" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B212" s="74" t="s">
+      <c r="B212" s="73" t="s">
         <v>418</v>
       </c>
-      <c r="C212" s="75" t="s">
+      <c r="C212" s="74" t="s">
         <v>419</v>
       </c>
-      <c r="D212" s="76">
+      <c r="D212" s="75">
         <v>50</v>
       </c>
-      <c r="E212" s="77">
+      <c r="E212" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F212" s="77">
+      <c r="F212" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G212" s="78">
+      <c r="G212" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E212-F212</f>
         <v>50</v>
       </c>
@@ -10757,24 +10792,24 @@
       </c>
     </row>
     <row r="230" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B230" s="80" t="s">
+      <c r="B230" s="79" t="s">
         <v>452</v>
       </c>
-      <c r="C230" s="81" t="s">
+      <c r="C230" s="80" t="s">
         <v>453</v>
       </c>
-      <c r="D230" s="82">
+      <c r="D230" s="81">
         <v>958</v>
       </c>
-      <c r="E230" s="83">
+      <c r="E230" s="82">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F230" s="83">
+      <c r="F230" s="82">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G230" s="84">
+      <c r="G230" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E230-F230</f>
         <v>958</v>
       </c>
@@ -10788,24 +10823,24 @@
       </c>
     </row>
     <row r="231" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B231" s="74" t="s">
+      <c r="B231" s="73" t="s">
         <v>454</v>
       </c>
-      <c r="C231" s="75" t="s">
+      <c r="C231" s="74" t="s">
         <v>455</v>
       </c>
-      <c r="D231" s="76">
+      <c r="D231" s="75">
         <v>14</v>
       </c>
-      <c r="E231" s="77">
+      <c r="E231" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F231" s="77">
+      <c r="F231" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G231" s="78">
+      <c r="G231" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E231-F231</f>
         <v>14</v>
       </c>
@@ -10848,24 +10883,24 @@
       </c>
     </row>
     <row r="233" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B233" s="74" t="s">
+      <c r="B233" s="73" t="s">
         <v>458</v>
       </c>
-      <c r="C233" s="75" t="s">
+      <c r="C233" s="74" t="s">
         <v>459</v>
       </c>
-      <c r="D233" s="76">
+      <c r="D233" s="75">
         <v>30</v>
       </c>
-      <c r="E233" s="77">
+      <c r="E233" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F233" s="77">
+      <c r="F233" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G233" s="78">
+      <c r="G233" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E233-F233</f>
         <v>30</v>
       </c>
@@ -10879,24 +10914,24 @@
       </c>
     </row>
     <row r="234" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B234" s="74" t="s">
+      <c r="B234" s="73" t="s">
         <v>460</v>
       </c>
-      <c r="C234" s="75" t="s">
+      <c r="C234" s="74" t="s">
         <v>461</v>
       </c>
-      <c r="D234" s="76">
+      <c r="D234" s="75">
         <v>19</v>
       </c>
-      <c r="E234" s="77">
+      <c r="E234" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F234" s="77">
+      <c r="F234" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G234" s="78">
+      <c r="G234" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E234-F234</f>
         <v>19</v>
       </c>
@@ -10970,24 +11005,24 @@
       </c>
     </row>
     <row r="237" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B237" s="74" t="s">
+      <c r="B237" s="73" t="s">
         <v>466</v>
       </c>
-      <c r="C237" s="75" t="s">
+      <c r="C237" s="74" t="s">
         <v>467</v>
       </c>
-      <c r="D237" s="76">
+      <c r="D237" s="75">
         <v>50</v>
       </c>
-      <c r="E237" s="77">
+      <c r="E237" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F237" s="77">
+      <c r="F237" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G237" s="78">
+      <c r="G237" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E237-F237</f>
         <v>50</v>
       </c>
@@ -11001,24 +11036,24 @@
       </c>
     </row>
     <row r="238" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B238" s="74" t="s">
+      <c r="B238" s="73" t="s">
         <v>468</v>
       </c>
-      <c r="C238" s="75" t="s">
+      <c r="C238" s="74" t="s">
         <v>469</v>
       </c>
-      <c r="D238" s="76">
+      <c r="D238" s="75">
         <v>50</v>
       </c>
-      <c r="E238" s="77">
+      <c r="E238" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F238" s="77">
+      <c r="F238" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G238" s="78">
+      <c r="G238" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E238-F238</f>
         <v>50</v>
       </c>
@@ -11032,22 +11067,22 @@
       </c>
     </row>
     <row r="239" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B239" s="74" t="s">
+      <c r="B239" s="73" t="s">
         <v>470</v>
       </c>
-      <c r="C239" s="75" t="s">
+      <c r="C239" s="74" t="s">
         <v>471</v>
       </c>
-      <c r="D239" s="76"/>
-      <c r="E239" s="77">
+      <c r="D239" s="75"/>
+      <c r="E239" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F239" s="77">
+      <c r="F239" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G239" s="78">
+      <c r="G239" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E239-F239</f>
         <v>0</v>
       </c>
@@ -11092,24 +11127,24 @@
       </c>
     </row>
     <row r="241" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B241" s="74" t="s">
+      <c r="B241" s="73" t="s">
         <v>591</v>
       </c>
-      <c r="C241" s="75" t="s">
+      <c r="C241" s="74" t="s">
         <v>395</v>
       </c>
-      <c r="D241" s="76">
+      <c r="D241" s="75">
         <v>1000</v>
       </c>
-      <c r="E241" s="77">
+      <c r="E241" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F241" s="77">
+      <c r="F241" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G241" s="78">
+      <c r="G241" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E241-F241</f>
         <v>1000</v>
       </c>
@@ -11152,7 +11187,7 @@
       </c>
     </row>
     <row r="243" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B243" s="44" t="s">
+      <c r="B243" s="104" t="s">
         <v>476</v>
       </c>
       <c r="C243" s="45" t="s">
@@ -11183,24 +11218,24 @@
       </c>
     </row>
     <row r="244" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B244" s="74" t="s">
+      <c r="B244" s="73" t="s">
         <v>589</v>
       </c>
-      <c r="C244" s="75" t="s">
+      <c r="C244" s="74" t="s">
         <v>397</v>
       </c>
-      <c r="D244" s="76">
+      <c r="D244" s="75">
         <v>100</v>
       </c>
-      <c r="E244" s="77">
+      <c r="E244" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F244" s="77">
+      <c r="F244" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G244" s="78">
+      <c r="G244" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E244-F244</f>
         <v>100</v>
       </c>
@@ -11214,24 +11249,24 @@
       </c>
     </row>
     <row r="245" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B245" s="74" t="s">
+      <c r="B245" s="104" t="s">
         <v>478</v>
       </c>
-      <c r="C245" s="75" t="s">
+      <c r="C245" s="74" t="s">
         <v>479</v>
       </c>
-      <c r="D245" s="76">
+      <c r="D245" s="75">
         <v>32</v>
       </c>
-      <c r="E245" s="77">
+      <c r="E245" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F245" s="77">
+      <c r="F245" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G245" s="78">
+      <c r="G245" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E245-F245</f>
         <v>32</v>
       </c>
@@ -11245,24 +11280,24 @@
       </c>
     </row>
     <row r="246" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B246" s="74" t="s">
+      <c r="B246" s="104" t="s">
         <v>480</v>
       </c>
-      <c r="C246" s="75" t="s">
+      <c r="C246" s="74" t="s">
         <v>481</v>
       </c>
-      <c r="D246" s="76">
+      <c r="D246" s="75">
         <v>4</v>
       </c>
-      <c r="E246" s="77">
+      <c r="E246" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F246" s="77">
+      <c r="F246" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G246" s="78">
+      <c r="G246" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E246-F246</f>
         <v>4</v>
       </c>
@@ -11305,7 +11340,7 @@
       </c>
     </row>
     <row r="248" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B248" s="60" t="s">
+      <c r="B248" s="104" t="s">
         <v>484</v>
       </c>
       <c r="C248" s="61" t="s">
@@ -11339,24 +11374,24 @@
       </c>
     </row>
     <row r="249" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B249" s="74" t="s">
+      <c r="B249" s="104" t="s">
         <v>486</v>
       </c>
-      <c r="C249" s="75" t="s">
+      <c r="C249" s="74" t="s">
         <v>487</v>
       </c>
-      <c r="D249" s="76">
+      <c r="D249" s="75">
         <v>30</v>
       </c>
-      <c r="E249" s="77">
+      <c r="E249" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F249" s="77">
+      <c r="F249" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G249" s="78">
+      <c r="G249" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E249-F249</f>
         <v>30</v>
       </c>
@@ -11370,24 +11405,24 @@
       </c>
     </row>
     <row r="250" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B250" s="74" t="s">
+      <c r="B250" s="104" t="s">
         <v>488</v>
       </c>
-      <c r="C250" s="75" t="s">
+      <c r="C250" s="74" t="s">
         <v>489</v>
       </c>
-      <c r="D250" s="76">
+      <c r="D250" s="75">
         <v>30</v>
       </c>
-      <c r="E250" s="77">
+      <c r="E250" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F250" s="77">
+      <c r="F250" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G250" s="78">
+      <c r="G250" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E250-F250</f>
         <v>30</v>
       </c>
@@ -11401,7 +11436,7 @@
       </c>
     </row>
     <row r="251" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B251" s="27" t="s">
+      <c r="B251" s="104" t="s">
         <v>490</v>
       </c>
       <c r="C251" s="25" t="s">
@@ -11430,7 +11465,7 @@
       </c>
     </row>
     <row r="252" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B252" s="27" t="s">
+      <c r="B252" s="104" t="s">
         <v>492</v>
       </c>
       <c r="C252" s="25" t="s">
@@ -11459,24 +11494,24 @@
       </c>
     </row>
     <row r="253" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B253" s="74" t="s">
+      <c r="B253" s="73" t="s">
         <v>494</v>
       </c>
-      <c r="C253" s="75" t="s">
+      <c r="C253" s="74" t="s">
         <v>495</v>
       </c>
-      <c r="D253" s="76">
+      <c r="D253" s="75">
         <v>49</v>
       </c>
-      <c r="E253" s="77">
+      <c r="E253" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F253" s="77">
+      <c r="F253" s="76">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
-      <c r="G253" s="78">
+      <c r="G253" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E253-F253</f>
         <v>29</v>
       </c>
@@ -11493,24 +11528,24 @@
       </c>
     </row>
     <row r="254" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B254" s="80" t="s">
+      <c r="B254" s="104" t="s">
         <v>496</v>
       </c>
-      <c r="C254" s="81" t="s">
+      <c r="C254" s="80" t="s">
         <v>497</v>
       </c>
-      <c r="D254" s="82">
+      <c r="D254" s="81">
         <v>126</v>
       </c>
-      <c r="E254" s="83">
+      <c r="E254" s="82">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F254" s="83">
+      <c r="F254" s="82">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G254" s="84">
+      <c r="G254" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E254-F254</f>
         <v>126</v>
       </c>
@@ -11524,7 +11559,7 @@
       </c>
     </row>
     <row r="255" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B255" s="27" t="s">
+      <c r="B255" s="104" t="s">
         <v>498</v>
       </c>
       <c r="C255" s="25" t="s">
@@ -11553,24 +11588,24 @@
       </c>
     </row>
     <row r="256" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B256" s="74" t="s">
+      <c r="B256" s="104" t="s">
         <v>500</v>
       </c>
-      <c r="C256" s="75" t="s">
+      <c r="C256" s="74" t="s">
         <v>501</v>
       </c>
-      <c r="D256" s="76">
+      <c r="D256" s="75">
         <v>13</v>
       </c>
-      <c r="E256" s="77">
+      <c r="E256" s="76">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F256" s="77">
+      <c r="F256" s="76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G256" s="78">
+      <c r="G256" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E256-F256</f>
         <v>13</v>
       </c>
@@ -11819,24 +11854,24 @@
       </c>
     </row>
     <row r="265" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B265" s="74" t="s">
+      <c r="B265" s="104" t="s">
         <v>502</v>
       </c>
-      <c r="C265" s="75" t="s">
+      <c r="C265" s="74" t="s">
         <v>503</v>
       </c>
-      <c r="D265" s="76">
+      <c r="D265" s="75">
         <v>79</v>
       </c>
-      <c r="E265" s="77">
+      <c r="E265" s="76">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F265" s="77">
+      <c r="F265" s="76">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G265" s="78">
+      <c r="G265" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E265-F265</f>
         <v>79</v>
       </c>
@@ -11850,7 +11885,7 @@
       </c>
     </row>
     <row r="266" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B266" s="60" t="s">
+      <c r="B266" s="104" t="s">
         <v>520</v>
       </c>
       <c r="C266" s="61" t="s">
@@ -11880,7 +11915,7 @@
       </c>
     </row>
     <row r="267" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B267" s="60" t="s">
+      <c r="B267" s="104" t="s">
         <v>522</v>
       </c>
       <c r="C267" s="61" t="s">
@@ -11910,7 +11945,7 @@
       </c>
     </row>
     <row r="268" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B268" s="60" t="s">
+      <c r="B268" s="104" t="s">
         <v>524</v>
       </c>
       <c r="C268" s="61" t="s">
@@ -11943,7 +11978,7 @@
       </c>
     </row>
     <row r="269" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B269" s="60" t="s">
+      <c r="B269" s="104" t="s">
         <v>526</v>
       </c>
       <c r="C269" s="61" t="s">
@@ -11973,22 +12008,22 @@
       </c>
     </row>
     <row r="270" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B270" s="74" t="s">
+      <c r="B270" s="73" t="s">
         <v>528</v>
       </c>
-      <c r="C270" s="75" t="s">
+      <c r="C270" s="74" t="s">
         <v>529</v>
       </c>
-      <c r="D270" s="76"/>
-      <c r="E270" s="77">
+      <c r="D270" s="75"/>
+      <c r="E270" s="76">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F270" s="77">
+      <c r="F270" s="76">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G270" s="78">
+      <c r="G270" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E270-F270</f>
         <v>0</v>
       </c>
@@ -12031,7 +12066,7 @@
       </c>
     </row>
     <row r="272" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B272" s="60" t="s">
+      <c r="B272" s="104" t="s">
         <v>532</v>
       </c>
       <c r="C272" s="61" t="s">
@@ -12061,7 +12096,7 @@
       </c>
     </row>
     <row r="273" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B273" s="60" t="s">
+      <c r="B273" s="104" t="s">
         <v>534</v>
       </c>
       <c r="C273" s="61" t="s">
@@ -12178,24 +12213,24 @@
       </c>
     </row>
     <row r="277" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B277" s="74" t="s">
+      <c r="B277" s="73" t="s">
         <v>542</v>
       </c>
-      <c r="C277" s="75" t="s">
+      <c r="C277" s="74" t="s">
         <v>543</v>
       </c>
-      <c r="D277" s="76">
+      <c r="D277" s="75">
         <v>44</v>
       </c>
-      <c r="E277" s="77">
+      <c r="E277" s="76">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F277" s="77">
+      <c r="F277" s="76">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G277" s="78">
+      <c r="G277" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E277-F277</f>
         <v>44</v>
       </c>
@@ -12209,24 +12244,24 @@
       </c>
     </row>
     <row r="278" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B278" s="74" t="s">
+      <c r="B278" s="73" t="s">
         <v>544</v>
       </c>
-      <c r="C278" s="75" t="s">
+      <c r="C278" s="74" t="s">
         <v>543</v>
       </c>
-      <c r="D278" s="76">
+      <c r="D278" s="75">
         <v>15</v>
       </c>
-      <c r="E278" s="77">
+      <c r="E278" s="76">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F278" s="77">
+      <c r="F278" s="76">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G278" s="78">
+      <c r="G278" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E278-F278</f>
         <v>15</v>
       </c>
@@ -12240,24 +12275,24 @@
       </c>
     </row>
     <row r="279" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B279" s="74" t="s">
+      <c r="B279" s="73" t="s">
         <v>545</v>
       </c>
-      <c r="C279" s="75" t="s">
+      <c r="C279" s="74" t="s">
         <v>546</v>
       </c>
-      <c r="D279" s="76">
+      <c r="D279" s="75">
         <v>10</v>
       </c>
-      <c r="E279" s="77">
+      <c r="E279" s="76">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F279" s="77">
+      <c r="F279" s="76">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G279" s="78">
+      <c r="G279" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E279-F279</f>
         <v>10</v>
       </c>
@@ -12299,125 +12334,125 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="2:16" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B281" s="80" t="s">
+    <row r="281" spans="2:16" s="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B281" s="79" t="s">
         <v>549</v>
       </c>
-      <c r="C281" s="81" t="s">
+      <c r="C281" s="80" t="s">
         <v>550</v>
       </c>
-      <c r="D281" s="82">
+      <c r="D281" s="81">
         <v>6</v>
       </c>
-      <c r="E281" s="83">
+      <c r="E281" s="82">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F281" s="83">
+      <c r="F281" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G281" s="84">
+      <c r="G281" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E281-F281</f>
         <v>6</v>
       </c>
       <c r="H281"/>
-      <c r="K281" s="69" t="str">
+      <c r="K281" s="68" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="P281" s="69" t="str">
+      <c r="P281" s="68" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="282" spans="2:16" s="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B282" s="80" t="s">
+    <row r="282" spans="2:16" s="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B282" s="79" t="s">
         <v>551</v>
       </c>
-      <c r="C282" s="81" t="s">
+      <c r="C282" s="80" t="s">
         <v>552</v>
       </c>
-      <c r="D282" s="82">
+      <c r="D282" s="81">
         <v>5</v>
       </c>
-      <c r="E282" s="83">
+      <c r="E282" s="82">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F282" s="83">
+      <c r="F282" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G282" s="84">
+      <c r="G282" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E282-F282</f>
         <v>5</v>
       </c>
       <c r="H282"/>
-      <c r="K282" s="85" t="str">
+      <c r="K282" s="84" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="P282" s="85" t="str">
+      <c r="P282" s="84" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="283" spans="2:16" s="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B283" s="80" t="s">
+    <row r="283" spans="2:16" s="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B283" s="79" t="s">
         <v>553</v>
       </c>
-      <c r="C283" s="81" t="s">
+      <c r="C283" s="80" t="s">
         <v>554</v>
       </c>
-      <c r="D283" s="82">
+      <c r="D283" s="81">
         <v>7</v>
       </c>
-      <c r="E283" s="83">
+      <c r="E283" s="82">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F283" s="83">
+      <c r="F283" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G283" s="84">
+      <c r="G283" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E283-F283</f>
         <v>7</v>
       </c>
       <c r="H283"/>
-      <c r="K283" s="85" t="str">
+      <c r="K283" s="84" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="P283" s="85" t="str">
+      <c r="P283" s="84" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="284" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B284" s="80" t="s">
+      <c r="B284" s="79" t="s">
         <v>555</v>
       </c>
-      <c r="C284" s="81" t="s">
+      <c r="C284" s="80" t="s">
         <v>556</v>
       </c>
-      <c r="D284" s="82">
+      <c r="D284" s="81">
         <v>6</v>
       </c>
-      <c r="E284" s="83">
+      <c r="E284" s="82">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F284" s="83">
+      <c r="F284" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G284" s="84">
+      <c r="G284" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E284-F284</f>
         <v>6</v>
       </c>
-      <c r="H284" s="71"/>
+      <c r="H284" s="70"/>
       <c r="K284" s="19" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -12428,28 +12463,28 @@
       </c>
     </row>
     <row r="285" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B285" s="80" t="s">
+      <c r="B285" s="79" t="s">
         <v>557</v>
       </c>
-      <c r="C285" s="81" t="s">
+      <c r="C285" s="80" t="s">
         <v>558</v>
       </c>
-      <c r="D285" s="82">
+      <c r="D285" s="81">
         <v>43</v>
       </c>
-      <c r="E285" s="83">
+      <c r="E285" s="82">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F285" s="83">
+      <c r="F285" s="82">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G285" s="84">
+      <c r="G285" s="83">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E285-F285</f>
         <v>43</v>
       </c>
-      <c r="H285" s="71"/>
+      <c r="H285" s="70"/>
       <c r="K285" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -12517,7 +12552,7 @@
         <v/>
       </c>
     </row>
-    <row r="288" spans="2:16" s="68" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="288" spans="2:16" s="67" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B288" s="58" t="s">
         <v>567</v>
       </c>
@@ -12536,16 +12571,16 @@
         <v>0</v>
       </c>
       <c r="H288"/>
-      <c r="J288" s="68" t="str">
+      <c r="J288" s="67" t="str">
         <f t="shared" ref="J288:J351" si="20">IF(I288="", "", IFERROR(VLOOKUP(I288&amp;"", $B$4:$C$5005, 2, FALSE), "NO EXISTE"))</f>
         <v/>
       </c>
-      <c r="O288" s="68" t="str">
+      <c r="O288" s="67" t="str">
         <f t="shared" ref="O288:O351" si="21">IF(N288="", "", IFERROR(VLOOKUP(N288&amp;"", $B$4:$C$5005, 2, FALSE), "NO EXISTE"))</f>
         <v/>
       </c>
     </row>
-    <row r="289" spans="2:15" s="68" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="289" spans="2:15" s="67" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B289" s="27" t="s">
         <v>563</v>
       </c>
@@ -12566,11 +12601,11 @@
         <v>0</v>
       </c>
       <c r="H289"/>
-      <c r="J289" s="68" t="str">
+      <c r="J289" s="67" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="O289" s="68" t="str">
+      <c r="O289" s="67" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -12611,7 +12646,7 @@
       <c r="C291" s="66" t="s">
         <v>583</v>
       </c>
-      <c r="D291" s="70" t="s">
+      <c r="D291" s="69" t="s">
         <v>585</v>
       </c>
       <c r="E291" s="62"/>
@@ -12623,7 +12658,7 @@
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E291-F291</f>
         <v>1</v>
       </c>
-      <c r="H291" s="68"/>
+      <c r="H291" s="67"/>
       <c r="J291" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -12634,28 +12669,28 @@
       </c>
     </row>
     <row r="292" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B292" s="94" t="s">
+      <c r="B292" s="106" t="s">
         <v>246</v>
       </c>
-      <c r="C292" s="94" t="s">
+      <c r="C292" s="93" t="s">
         <v>584</v>
       </c>
-      <c r="D292" s="93">
+      <c r="D292" s="92">
         <v>1360</v>
       </c>
-      <c r="E292" s="77">
+      <c r="E292" s="76">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F292" s="77">
+      <c r="F292" s="76">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G292" s="78">
+      <c r="G292" s="77">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E292-F292</f>
         <v>1360</v>
       </c>
-      <c r="H292" s="68"/>
+      <c r="H292" s="67"/>
       <c r="J292" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -12666,22 +12701,22 @@
       </c>
     </row>
     <row r="293" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B293" s="92" t="s">
+      <c r="B293" s="91" t="s">
         <v>587</v>
       </c>
-      <c r="C293" s="92"/>
-      <c r="D293" s="93" t="s">
+      <c r="C293" s="91"/>
+      <c r="D293" s="92" t="s">
         <v>588</v>
       </c>
-      <c r="E293" s="93">
+      <c r="E293" s="92">
         <f>SUMIF($J$4:$J$5000, B293, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F293" s="93">
+      <c r="F293" s="92">
         <f>SUMIF($O$4:$O$5000, B293, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G293" s="93">
+      <c r="G293" s="92">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E293-F293</f>
         <v>400</v>
       </c>
@@ -12695,16 +12730,16 @@
       </c>
     </row>
     <row r="294" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B294" s="74" t="s">
+      <c r="B294" s="73" t="s">
         <v>408</v>
       </c>
-      <c r="C294" s="92"/>
-      <c r="D294" s="93" t="s">
+      <c r="C294" s="91"/>
+      <c r="D294" s="92" t="s">
         <v>594</v>
       </c>
-      <c r="E294" s="93"/>
-      <c r="F294" s="93"/>
-      <c r="G294" s="93"/>
+      <c r="E294" s="92"/>
+      <c r="F294" s="92"/>
+      <c r="G294" s="92"/>
       <c r="J294" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -12715,22 +12750,22 @@
       </c>
     </row>
     <row r="295" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B295" s="74" t="s">
+      <c r="B295" s="73" t="s">
         <v>597</v>
       </c>
-      <c r="C295" s="92"/>
-      <c r="D295" s="93" t="s">
+      <c r="C295" s="91"/>
+      <c r="D295" s="92" t="s">
         <v>594</v>
       </c>
-      <c r="E295" s="93">
+      <c r="E295" s="92">
         <f t="shared" ref="E295:E302" si="22">SUMIF($J$4:$J$5000, B295, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F295" s="93">
+      <c r="F295" s="92">
         <f t="shared" ref="F295:F302" si="23">SUMIF($O$4:$O$5000, B295, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G295" s="93">
+      <c r="G295" s="92">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E295-F295</f>
         <v>50</v>
       </c>
@@ -12744,22 +12779,22 @@
       </c>
     </row>
     <row r="296" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B296" s="92" t="s">
+      <c r="B296" s="91" t="s">
         <v>598</v>
       </c>
-      <c r="C296" s="92"/>
-      <c r="D296" s="94" t="s">
+      <c r="C296" s="91"/>
+      <c r="D296" s="93" t="s">
         <v>599</v>
       </c>
-      <c r="E296" s="93">
+      <c r="E296" s="92">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F296" s="93">
+      <c r="F296" s="92">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G296" s="95">
+      <c r="G296" s="94">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E296-F296</f>
         <v>91</v>
       </c>
@@ -12773,22 +12808,22 @@
       </c>
     </row>
     <row r="297" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B297" s="96" t="s">
+      <c r="B297" s="95" t="s">
         <v>610</v>
       </c>
-      <c r="C297" s="96"/>
-      <c r="D297" s="97" t="s">
+      <c r="C297" s="95"/>
+      <c r="D297" s="96" t="s">
         <v>611</v>
       </c>
-      <c r="E297" s="98">
+      <c r="E297" s="97">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F297" s="98">
+      <c r="F297" s="97">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G297" s="99">
+      <c r="G297" s="98">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E297-F297</f>
         <v>8</v>
       </c>
@@ -12802,24 +12837,24 @@
       </c>
     </row>
     <row r="298" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B298" s="96" t="s">
+      <c r="B298" s="95" t="s">
         <v>612</v>
       </c>
-      <c r="C298" s="96" t="s">
+      <c r="C298" s="95" t="s">
         <v>613</v>
       </c>
-      <c r="D298" s="97" t="s">
+      <c r="D298" s="96" t="s">
         <v>614</v>
       </c>
-      <c r="E298" s="98">
+      <c r="E298" s="97">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F298" s="98">
+      <c r="F298" s="97">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G298" s="99">
+      <c r="G298" s="98">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E298-F298</f>
         <v>35</v>
       </c>
@@ -12833,22 +12868,22 @@
       </c>
     </row>
     <row r="299" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B299" s="96" t="s">
+      <c r="B299" s="95" t="s">
         <v>615</v>
       </c>
-      <c r="C299" s="96"/>
-      <c r="D299" s="97" t="s">
+      <c r="C299" s="95"/>
+      <c r="D299" s="96" t="s">
         <v>616</v>
       </c>
-      <c r="E299" s="98">
+      <c r="E299" s="97">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F299" s="98">
+      <c r="F299" s="97">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G299" s="99">
+      <c r="G299" s="98">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E299-F299</f>
         <v>192</v>
       </c>
@@ -12862,22 +12897,22 @@
       </c>
     </row>
     <row r="300" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B300" s="96">
+      <c r="B300" s="95">
         <v>41040</v>
       </c>
-      <c r="C300" s="96"/>
-      <c r="D300" s="97" t="s">
+      <c r="C300" s="95"/>
+      <c r="D300" s="96" t="s">
         <v>590</v>
       </c>
-      <c r="E300" s="98">
+      <c r="E300" s="97">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F300" s="98">
+      <c r="F300" s="97">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G300" s="99">
+      <c r="G300" s="98">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E300-F300</f>
         <v>100</v>
       </c>
@@ -12891,22 +12926,22 @@
       </c>
     </row>
     <row r="301" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B301" s="96" t="s">
+      <c r="B301" s="95" t="s">
         <v>617</v>
       </c>
-      <c r="C301" s="96"/>
-      <c r="D301" s="97" t="s">
+      <c r="C301" s="95"/>
+      <c r="D301" s="96" t="s">
         <v>618</v>
       </c>
-      <c r="E301" s="98">
+      <c r="E301" s="97">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F301" s="98">
+      <c r="F301" s="97">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G301" s="99">
+      <c r="G301" s="98">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E301-F301</f>
         <v>15</v>
       </c>
@@ -12920,22 +12955,22 @@
       </c>
     </row>
     <row r="302" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B302" s="80" t="s">
+      <c r="B302" s="79" t="s">
         <v>619</v>
       </c>
-      <c r="C302" s="96"/>
-      <c r="D302" s="97" t="s">
+      <c r="C302" s="95"/>
+      <c r="D302" s="96" t="s">
         <v>585</v>
       </c>
-      <c r="E302" s="98">
+      <c r="E302" s="97">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F302" s="98">
+      <c r="F302" s="97">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G302" s="99">
+      <c r="G302" s="98">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E302-F302</f>
         <v>1</v>
       </c>
@@ -12949,22 +12984,22 @@
       </c>
     </row>
     <row r="303" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B303" s="96">
+      <c r="B303" s="95">
         <v>8003</v>
       </c>
-      <c r="C303" s="96"/>
-      <c r="D303" s="97" t="s">
+      <c r="C303" s="95"/>
+      <c r="D303" s="96" t="s">
         <v>623</v>
       </c>
-      <c r="E303" s="98">
+      <c r="E303" s="97">
         <f>SUMIF($J$4:$J$5000, B303, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F303" s="98">
+      <c r="F303" s="97">
         <f>SUMIF($O$4:$O$5000, B303, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G303" s="99">
+      <c r="G303" s="98">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E303-F303</f>
         <v>20</v>
       </c>
@@ -12978,10 +13013,10 @@
       </c>
     </row>
     <row r="304" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="D304" s="73"/>
-      <c r="E304" s="73"/>
-      <c r="F304" s="73"/>
-      <c r="G304" s="73"/>
+      <c r="D304" s="72"/>
+      <c r="E304" s="72"/>
+      <c r="F304" s="72"/>
+      <c r="G304" s="72"/>
       <c r="J304" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -14971,7 +15006,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -15017,28 +15052,28 @@
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="104"/>
+      <c r="B2" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="103"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="104"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="103"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="102" t="s">
+      <c r="N2" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="103"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="104"/>
+      <c r="O2" s="102"/>
+      <c r="P2" s="102"/>
+      <c r="Q2" s="103"/>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">

--- a/INVENTARIO_AMPERIAL_2026.xlsx
+++ b/INVENTARIO_AMPERIAL_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Amperial Website\AmperialWebsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFD80A2-A596-4AF4-80D1-3A7ADF6C0CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA593B7-4CDC-4D9F-ACB1-C8BED8AC9EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1905" yWindow="1905" windowWidth="11520" windowHeight="7995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2450,7 +2450,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2578,9 +2578,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3239,7 +3236,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="3" width="71.85546875" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
@@ -3284,31 +3281,31 @@
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
+      <c r="B2" s="99" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
       <c r="H2" s="1"/>
-      <c r="J2" s="99" t="s">
+      <c r="J2" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="O2" s="99" t="s">
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="O2" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="99"/>
-      <c r="T2" s="57" t="s">
+      <c r="P2" s="98"/>
+      <c r="Q2" s="98"/>
+      <c r="R2" s="98"/>
+      <c r="T2" s="56" t="s">
         <v>574</v>
       </c>
-      <c r="U2" s="57" t="s">
+      <c r="U2" s="56" t="s">
         <v>573</v>
       </c>
     </row>
@@ -3332,7 +3329,7 @@
       <c r="G3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="64" t="s">
+      <c r="H3" s="63" t="s">
         <v>578</v>
       </c>
       <c r="I3" s="1"/>
@@ -3362,10 +3359,10 @@
         <v>9</v>
       </c>
       <c r="S3" s="1"/>
-      <c r="T3" s="51" t="s">
+      <c r="T3" s="50" t="s">
         <v>570</v>
       </c>
-      <c r="U3" s="52"/>
+      <c r="U3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
@@ -3420,10 +3417,10 @@
         <v>210</v>
       </c>
       <c r="S4" s="1"/>
-      <c r="T4" s="51" t="s">
+      <c r="T4" s="50" t="s">
         <v>571</v>
       </c>
-      <c r="U4" s="78"/>
+      <c r="U4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
@@ -3478,10 +3475,10 @@
         <v>125</v>
       </c>
       <c r="S5" s="1"/>
-      <c r="T5" s="51" t="s">
+      <c r="T5" s="50" t="s">
         <v>572</v>
       </c>
-      <c r="U5" s="53"/>
+      <c r="U5" s="52"/>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
@@ -3528,10 +3525,10 @@
         <v>28</v>
       </c>
       <c r="S6" s="1"/>
-      <c r="T6" s="54" t="s">
+      <c r="T6" s="53" t="s">
         <v>577</v>
       </c>
-      <c r="U6" s="55"/>
+      <c r="U6" s="54"/>
     </row>
     <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
@@ -3578,8 +3575,8 @@
         <v>20</v>
       </c>
       <c r="S7" s="1"/>
-      <c r="T7" s="56"/>
-      <c r="U7" s="56"/>
+      <c r="T7" s="55"/>
+      <c r="U7" s="55"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
@@ -3784,22 +3781,22 @@
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="79" t="s">
+      <c r="B13" s="78" t="s">
         <v>608</v>
       </c>
-      <c r="C13" s="80"/>
-      <c r="D13" s="80" t="s">
+      <c r="C13" s="79"/>
+      <c r="D13" s="79" t="s">
         <v>609</v>
       </c>
-      <c r="E13" s="82">
+      <c r="E13" s="81">
         <f>SUMIF($J$4:$J$5000, B13, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="82">
+      <c r="F13" s="81">
         <f>SUMIF($O$4:$O$5000, B13, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="83">
+      <c r="G13" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E13-F13</f>
         <v>75</v>
       </c>
@@ -3824,24 +3821,24 @@
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="80" t="s">
+      <c r="C14" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="81">
+      <c r="D14" s="80">
         <v>20</v>
       </c>
-      <c r="E14" s="82">
+      <c r="E14" s="81">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F14" s="82">
+      <c r="F14" s="81">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G14" s="83">
+      <c r="G14" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E14-F14</f>
         <v>20</v>
       </c>
@@ -4051,24 +4048,24 @@
       <c r="R19" s="11"/>
     </row>
     <row r="20" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="73" t="s">
+      <c r="B20" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="74" t="s">
+      <c r="C20" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="75">
+      <c r="D20" s="74">
         <v>4</v>
       </c>
-      <c r="E20" s="76">
+      <c r="E20" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F20" s="76">
+      <c r="F20" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="77">
+      <c r="G20" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E20-F20</f>
         <v>4</v>
       </c>
@@ -4403,24 +4400,24 @@
       <c r="R29" s="11"/>
     </row>
     <row r="30" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="79" t="s">
+      <c r="B30" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="80" t="s">
+      <c r="C30" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="81">
+      <c r="D30" s="80">
         <v>10</v>
       </c>
-      <c r="E30" s="82">
+      <c r="E30" s="81">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F30" s="82">
+      <c r="F30" s="81">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G30" s="83">
+      <c r="G30" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E30-F30</f>
         <v>10</v>
       </c>
@@ -4440,24 +4437,24 @@
       <c r="R30" s="14"/>
     </row>
     <row r="31" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="79" t="s">
+      <c r="B31" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="80" t="s">
+      <c r="C31" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="81">
+      <c r="D31" s="80">
         <v>20</v>
       </c>
-      <c r="E31" s="82">
+      <c r="E31" s="81">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F31" s="82">
+      <c r="F31" s="81">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G31" s="83">
+      <c r="G31" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E31-F31</f>
         <v>20</v>
       </c>
@@ -5282,24 +5279,24 @@
       <c r="R54" s="14"/>
     </row>
     <row r="55" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="79" t="s">
+      <c r="B55" s="78" t="s">
         <v>111</v>
       </c>
-      <c r="C55" s="80" t="s">
+      <c r="C55" s="79" t="s">
         <v>112</v>
       </c>
-      <c r="D55" s="81">
+      <c r="D55" s="80">
         <v>64</v>
       </c>
-      <c r="E55" s="82">
+      <c r="E55" s="81">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F55" s="82">
+      <c r="F55" s="81">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G55" s="83">
+      <c r="G55" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E55-F55</f>
         <v>64</v>
       </c>
@@ -5704,24 +5701,24 @@
       <c r="R66" s="14"/>
     </row>
     <row r="67" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="73" t="s">
+      <c r="B67" s="72" t="s">
         <v>600</v>
       </c>
-      <c r="C67" s="74" t="s">
+      <c r="C67" s="73" t="s">
         <v>136</v>
       </c>
-      <c r="D67" s="75">
+      <c r="D67" s="74">
         <v>8</v>
       </c>
-      <c r="E67" s="76">
+      <c r="E67" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F67" s="76">
+      <c r="F67" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G67" s="77">
+      <c r="G67" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E67-F67</f>
         <v>8</v>
       </c>
@@ -5741,24 +5738,24 @@
       <c r="R67" s="11"/>
     </row>
     <row r="68" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="73" t="s">
+      <c r="B68" s="72" t="s">
         <v>601</v>
       </c>
-      <c r="C68" s="74" t="s">
+      <c r="C68" s="73" t="s">
         <v>138</v>
       </c>
-      <c r="D68" s="75">
+      <c r="D68" s="74">
         <v>3</v>
       </c>
-      <c r="E68" s="76">
+      <c r="E68" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F68" s="76">
+      <c r="F68" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G68" s="77">
+      <c r="G68" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E68-F68</f>
         <v>3</v>
       </c>
@@ -6022,7 +6019,7 @@
       <c r="Q75" s="10"/>
       <c r="R75" s="11"/>
     </row>
-    <row r="76" spans="2:18" s="70" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:18" s="69" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B76" s="27" t="s">
         <v>152</v>
       </c>
@@ -6043,44 +6040,44 @@
         <v>250</v>
       </c>
       <c r="H76"/>
-      <c r="J76" s="87"/>
-      <c r="K76" s="84" t="str">
+      <c r="J76" s="86"/>
+      <c r="K76" s="83" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="L76" s="88"/>
-      <c r="M76" s="89"/>
-      <c r="O76" s="87"/>
-      <c r="P76" s="84" t="str">
+      <c r="L76" s="87"/>
+      <c r="M76" s="88"/>
+      <c r="O76" s="86"/>
+      <c r="P76" s="83" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q76" s="90"/>
-      <c r="R76" s="89"/>
+      <c r="Q76" s="89"/>
+      <c r="R76" s="88"/>
     </row>
     <row r="77" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="79" t="s">
+      <c r="B77" s="78" t="s">
         <v>154</v>
       </c>
-      <c r="C77" s="80" t="s">
+      <c r="C77" s="79" t="s">
         <v>155</v>
       </c>
-      <c r="D77" s="81">
+      <c r="D77" s="80">
         <v>900</v>
       </c>
-      <c r="E77" s="82">
+      <c r="E77" s="81">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F77" s="82">
+      <c r="F77" s="81">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G77" s="83">
+      <c r="G77" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E77-F77</f>
         <v>900</v>
       </c>
-      <c r="H77" s="70"/>
+      <c r="H77" s="69"/>
       <c r="J77" s="9"/>
       <c r="K77" s="19" t="str">
         <f t="shared" si="4"/>
@@ -6097,24 +6094,24 @@
       <c r="R77" s="11"/>
     </row>
     <row r="78" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="79" t="s">
+      <c r="B78" s="78" t="s">
         <v>156</v>
       </c>
-      <c r="C78" s="80" t="s">
+      <c r="C78" s="79" t="s">
         <v>157</v>
       </c>
-      <c r="D78" s="81">
+      <c r="D78" s="80">
         <v>132</v>
       </c>
-      <c r="E78" s="82">
+      <c r="E78" s="81">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F78" s="82">
+      <c r="F78" s="81">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G78" s="83">
+      <c r="G78" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E78-F78</f>
         <v>132</v>
       </c>
@@ -6168,7 +6165,7 @@
       <c r="Q79" s="10"/>
       <c r="R79" s="11"/>
     </row>
-    <row r="80" spans="2:18" s="70" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" s="69" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B80" s="27" t="s">
         <v>160</v>
       </c>
@@ -6189,44 +6186,44 @@
         <v>250</v>
       </c>
       <c r="H80"/>
-      <c r="J80" s="87"/>
-      <c r="K80" s="84" t="str">
+      <c r="J80" s="86"/>
+      <c r="K80" s="83" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="L80" s="88"/>
-      <c r="M80" s="89"/>
-      <c r="O80" s="87"/>
-      <c r="P80" s="84" t="str">
+      <c r="L80" s="87"/>
+      <c r="M80" s="88"/>
+      <c r="O80" s="86"/>
+      <c r="P80" s="83" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q80" s="90"/>
-      <c r="R80" s="89"/>
+      <c r="Q80" s="89"/>
+      <c r="R80" s="88"/>
     </row>
     <row r="81" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="79" t="s">
+      <c r="B81" s="78" t="s">
         <v>162</v>
       </c>
-      <c r="C81" s="80" t="s">
+      <c r="C81" s="79" t="s">
         <v>163</v>
       </c>
-      <c r="D81" s="81">
+      <c r="D81" s="80">
         <v>1000</v>
       </c>
-      <c r="E81" s="82">
+      <c r="E81" s="81">
         <f>SUMIF($J$4:$J$5000, B81, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F81" s="82">
+      <c r="F81" s="81">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G81" s="83">
+      <c r="G81" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E81-F81</f>
         <v>1000</v>
       </c>
-      <c r="H81" s="70"/>
+      <c r="H81" s="69"/>
       <c r="J81" s="9"/>
       <c r="K81" s="19" t="str">
         <f t="shared" si="4"/>
@@ -6558,24 +6555,24 @@
       <c r="R90" s="14"/>
     </row>
     <row r="91" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B91" s="73" t="s">
+      <c r="B91" s="72" t="s">
         <v>182</v>
       </c>
-      <c r="C91" s="74" t="s">
+      <c r="C91" s="73" t="s">
         <v>183</v>
       </c>
-      <c r="D91" s="75">
+      <c r="D91" s="74">
         <v>4</v>
       </c>
-      <c r="E91" s="76">
+      <c r="E91" s="75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F91" s="76">
+      <c r="F91" s="75">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G91" s="77">
+      <c r="G91" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E91-F91</f>
         <v>4</v>
       </c>
@@ -6875,24 +6872,24 @@
       <c r="R99" s="22"/>
     </row>
     <row r="100" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B100" s="60" t="s">
+      <c r="B100" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="C100" s="61" t="s">
+      <c r="C100" s="60" t="s">
         <v>201</v>
       </c>
-      <c r="D100" s="59">
+      <c r="D100" s="58">
         <v>38</v>
       </c>
-      <c r="E100" s="62">
+      <c r="E100" s="61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F100" s="62">
+      <c r="F100" s="61">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G100" s="63">
+      <c r="G100" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E100-F100</f>
         <v>38</v>
       </c>
@@ -7001,7 +6998,7 @@
       </c>
     </row>
     <row r="104" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B104" s="27" t="s">
+      <c r="B104" s="103" t="s">
         <v>214</v>
       </c>
       <c r="C104" s="25" t="s">
@@ -7030,24 +7027,24 @@
       </c>
     </row>
     <row r="105" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="44" t="s">
+      <c r="B105" s="103" t="s">
         <v>216</v>
       </c>
-      <c r="C105" s="45" t="s">
+      <c r="C105" s="44" t="s">
         <v>217</v>
       </c>
-      <c r="D105" s="46">
+      <c r="D105" s="45">
         <v>158</v>
       </c>
-      <c r="E105" s="47">
+      <c r="E105" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F105" s="47">
+      <c r="F105" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G105" s="48">
+      <c r="G105" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E105-F105</f>
         <v>158</v>
       </c>
@@ -7061,24 +7058,24 @@
       </c>
     </row>
     <row r="106" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="44" t="s">
+      <c r="B106" s="103" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="45" t="s">
+      <c r="C106" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="D106" s="46">
+      <c r="D106" s="45">
         <v>308</v>
       </c>
-      <c r="E106" s="47">
+      <c r="E106" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F106" s="47">
+      <c r="F106" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G106" s="48">
+      <c r="G106" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E106-F106</f>
         <v>308</v>
       </c>
@@ -7092,24 +7089,24 @@
       </c>
     </row>
     <row r="107" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="44" t="s">
+      <c r="B107" s="103" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="45" t="s">
+      <c r="C107" s="44" t="s">
         <v>221</v>
       </c>
-      <c r="D107" s="46">
+      <c r="D107" s="45">
         <v>50</v>
       </c>
-      <c r="E107" s="47">
+      <c r="E107" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F107" s="47">
+      <c r="F107" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G107" s="48">
+      <c r="G107" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E107-F107</f>
         <v>50</v>
       </c>
@@ -7123,7 +7120,7 @@
       </c>
     </row>
     <row r="108" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="27" t="s">
+      <c r="B108" s="103" t="s">
         <v>222</v>
       </c>
       <c r="C108" s="25" t="s">
@@ -7152,22 +7149,22 @@
       </c>
     </row>
     <row r="109" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="73" t="s">
+      <c r="B109" s="103" t="s">
         <v>224</v>
       </c>
-      <c r="C109" s="74" t="s">
+      <c r="C109" s="73" t="s">
         <v>225</v>
       </c>
-      <c r="D109" s="75"/>
-      <c r="E109" s="76">
+      <c r="D109" s="74"/>
+      <c r="E109" s="75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F109" s="76">
+      <c r="F109" s="75">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G109" s="77">
+      <c r="G109" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E109-F109</f>
         <v>0</v>
       </c>
@@ -7181,7 +7178,7 @@
       </c>
     </row>
     <row r="110" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B110" s="27" t="s">
+      <c r="B110" s="103" t="s">
         <v>226</v>
       </c>
       <c r="C110" s="25" t="s">
@@ -7210,24 +7207,24 @@
       </c>
     </row>
     <row r="111" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="44" t="s">
+      <c r="B111" s="103" t="s">
         <v>228</v>
       </c>
-      <c r="C111" s="45" t="s">
+      <c r="C111" s="44" t="s">
         <v>229</v>
       </c>
-      <c r="D111" s="46">
+      <c r="D111" s="45">
         <v>143</v>
       </c>
-      <c r="E111" s="47">
+      <c r="E111" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F111" s="47">
+      <c r="F111" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G111" s="48">
+      <c r="G111" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E111-F111</f>
         <v>143</v>
       </c>
@@ -7270,28 +7267,28 @@
       </c>
     </row>
     <row r="113" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="104" t="s">
+      <c r="B113" s="103" t="s">
         <v>206</v>
       </c>
-      <c r="C113" s="61" t="s">
+      <c r="C113" s="60" t="s">
         <v>207</v>
       </c>
-      <c r="D113" s="59">
+      <c r="D113" s="58">
         <v>13</v>
       </c>
-      <c r="E113" s="62">
+      <c r="E113" s="61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F113" s="62">
+      <c r="F113" s="61">
         <f t="shared" si="6"/>
         <v>28</v>
       </c>
-      <c r="G113" s="63">
+      <c r="G113" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E113-F113</f>
         <v>-15</v>
       </c>
-      <c r="H113" s="65" t="s">
+      <c r="H113" s="64" t="s">
         <v>579</v>
       </c>
       <c r="K113" s="19" t="str">
@@ -7304,7 +7301,7 @@
       </c>
     </row>
     <row r="114" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="27" t="s">
+      <c r="B114" s="103" t="s">
         <v>232</v>
       </c>
       <c r="C114" s="25" t="s">
@@ -7333,24 +7330,24 @@
       </c>
     </row>
     <row r="115" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="44" t="s">
+      <c r="B115" s="103" t="s">
         <v>234</v>
       </c>
-      <c r="C115" s="45" t="s">
+      <c r="C115" s="44" t="s">
         <v>235</v>
       </c>
-      <c r="D115" s="46">
+      <c r="D115" s="45">
         <v>89</v>
       </c>
-      <c r="E115" s="47">
+      <c r="E115" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F115" s="47">
+      <c r="F115" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G115" s="48">
+      <c r="G115" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E115-F115</f>
         <v>89</v>
       </c>
@@ -7364,7 +7361,7 @@
       </c>
     </row>
     <row r="116" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B116" s="27" t="s">
+      <c r="B116" s="103" t="s">
         <v>236</v>
       </c>
       <c r="C116" s="25" t="s">
@@ -7393,24 +7390,24 @@
       </c>
     </row>
     <row r="117" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="44" t="s">
+      <c r="B117" s="103" t="s">
         <v>238</v>
       </c>
-      <c r="C117" s="45" t="s">
+      <c r="C117" s="44" t="s">
         <v>239</v>
       </c>
-      <c r="D117" s="46">
+      <c r="D117" s="45">
         <v>69</v>
       </c>
-      <c r="E117" s="47">
+      <c r="E117" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F117" s="47">
+      <c r="F117" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G117" s="48">
+      <c r="G117" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E117-F117</f>
         <v>69</v>
       </c>
@@ -7424,24 +7421,24 @@
       </c>
     </row>
     <row r="118" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="44" t="s">
+      <c r="B118" s="103" t="s">
         <v>240</v>
       </c>
-      <c r="C118" s="45" t="s">
+      <c r="C118" s="44" t="s">
         <v>241</v>
       </c>
-      <c r="D118" s="46">
+      <c r="D118" s="45">
         <v>180</v>
       </c>
-      <c r="E118" s="47">
+      <c r="E118" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F118" s="47">
+      <c r="F118" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G118" s="48">
+      <c r="G118" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E118-F118</f>
         <v>180</v>
       </c>
@@ -7455,7 +7452,7 @@
       </c>
     </row>
     <row r="119" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="27" t="s">
+      <c r="B119" s="103" t="s">
         <v>242</v>
       </c>
       <c r="C119" s="25" t="s">
@@ -7484,24 +7481,24 @@
       </c>
     </row>
     <row r="120" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="104" t="s">
+      <c r="B120" s="103" t="s">
         <v>208</v>
       </c>
-      <c r="C120" s="61" t="s">
+      <c r="C120" s="60" t="s">
         <v>209</v>
       </c>
-      <c r="D120" s="59">
+      <c r="D120" s="58">
         <v>54</v>
       </c>
-      <c r="E120" s="62">
+      <c r="E120" s="61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F120" s="62">
+      <c r="F120" s="61">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G120" s="63">
+      <c r="G120" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E120-F120</f>
         <v>54</v>
       </c>
@@ -7515,24 +7512,24 @@
       </c>
     </row>
     <row r="121" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="44" t="s">
+      <c r="B121" s="103" t="s">
         <v>244</v>
       </c>
-      <c r="C121" s="45" t="s">
+      <c r="C121" s="44" t="s">
         <v>245</v>
       </c>
-      <c r="D121" s="46">
+      <c r="D121" s="45">
         <v>99</v>
       </c>
-      <c r="E121" s="47">
+      <c r="E121" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F121" s="47">
+      <c r="F121" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G121" s="48">
+      <c r="G121" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E121-F121</f>
         <v>99</v>
       </c>
@@ -7546,24 +7543,24 @@
       </c>
     </row>
     <row r="122" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B122" s="104" t="s">
+      <c r="B122" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="C122" s="61" t="s">
+      <c r="C122" s="60" t="s">
         <v>211</v>
       </c>
-      <c r="D122" s="59">
+      <c r="D122" s="58">
         <v>39</v>
       </c>
-      <c r="E122" s="62">
+      <c r="E122" s="61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F122" s="62">
+      <c r="F122" s="61">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G122" s="63">
+      <c r="G122" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E122-F122</f>
         <v>39</v>
       </c>
@@ -7577,7 +7574,7 @@
       </c>
     </row>
     <row r="123" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="27" t="s">
+      <c r="B123" s="103" t="s">
         <v>246</v>
       </c>
       <c r="C123" s="25" t="s">
@@ -7606,7 +7603,7 @@
       </c>
     </row>
     <row r="124" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="27" t="s">
+      <c r="B124" s="103" t="s">
         <v>248</v>
       </c>
       <c r="C124" s="25" t="s">
@@ -7635,24 +7632,24 @@
       </c>
     </row>
     <row r="125" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="104" t="s">
+      <c r="B125" s="103" t="s">
         <v>250</v>
       </c>
-      <c r="C125" s="45" t="s">
+      <c r="C125" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="D125" s="46">
+      <c r="D125" s="45">
         <v>99</v>
       </c>
-      <c r="E125" s="47">
+      <c r="E125" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F125" s="47">
+      <c r="F125" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G125" s="48">
+      <c r="G125" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E125-F125</f>
         <v>99</v>
       </c>
@@ -7666,24 +7663,24 @@
       </c>
     </row>
     <row r="126" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="104" t="s">
+      <c r="B126" s="103" t="s">
         <v>252</v>
       </c>
-      <c r="C126" s="61" t="s">
+      <c r="C126" s="60" t="s">
         <v>253</v>
       </c>
-      <c r="D126" s="59">
+      <c r="D126" s="58">
         <v>90</v>
       </c>
-      <c r="E126" s="62">
+      <c r="E126" s="61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F126" s="62">
+      <c r="F126" s="61">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G126" s="63">
+      <c r="G126" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E126-F126</f>
         <v>90</v>
       </c>
@@ -7697,24 +7694,24 @@
       </c>
     </row>
     <row r="127" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="104" t="s">
+      <c r="B127" s="103" t="s">
         <v>254</v>
       </c>
-      <c r="C127" s="61" t="s">
+      <c r="C127" s="60" t="s">
         <v>255</v>
       </c>
-      <c r="D127" s="59">
+      <c r="D127" s="58">
         <v>34</v>
       </c>
-      <c r="E127" s="62">
+      <c r="E127" s="61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F127" s="62">
+      <c r="F127" s="61">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G127" s="63">
+      <c r="G127" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E127-F127</f>
         <v>34</v>
       </c>
@@ -7728,24 +7725,24 @@
       </c>
     </row>
     <row r="128" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B128" s="104" t="s">
+      <c r="B128" s="103" t="s">
         <v>256</v>
       </c>
-      <c r="C128" s="61" t="s">
+      <c r="C128" s="60" t="s">
         <v>257</v>
       </c>
-      <c r="D128" s="59">
+      <c r="D128" s="58">
         <v>74</v>
       </c>
-      <c r="E128" s="62">
+      <c r="E128" s="61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F128" s="62">
+      <c r="F128" s="61">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G128" s="63">
+      <c r="G128" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E128-F128</f>
         <v>74</v>
       </c>
@@ -7759,24 +7756,24 @@
       </c>
     </row>
     <row r="129" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="105" t="s">
+      <c r="B129" s="104" t="s">
         <v>258</v>
       </c>
-      <c r="C129" s="61" t="s">
+      <c r="C129" s="60" t="s">
         <v>259</v>
       </c>
-      <c r="D129" s="59">
+      <c r="D129" s="58">
         <v>200</v>
       </c>
-      <c r="E129" s="62">
+      <c r="E129" s="61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F129" s="62">
+      <c r="F129" s="61">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G129" s="63">
+      <c r="G129" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E129-F129</f>
         <v>200</v>
       </c>
@@ -7790,24 +7787,24 @@
       </c>
     </row>
     <row r="130" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="104" t="s">
+      <c r="B130" s="103" t="s">
         <v>260</v>
       </c>
-      <c r="C130" s="80" t="s">
+      <c r="C130" s="79" t="s">
         <v>261</v>
       </c>
-      <c r="D130" s="81">
+      <c r="D130" s="80">
         <v>253</v>
       </c>
-      <c r="E130" s="82">
+      <c r="E130" s="81">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F130" s="82">
+      <c r="F130" s="81">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G130" s="83">
+      <c r="G130" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E130-F130</f>
         <v>253</v>
       </c>
@@ -7821,24 +7818,24 @@
       </c>
     </row>
     <row r="131" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="104" t="s">
+      <c r="B131" s="103" t="s">
         <v>262</v>
       </c>
-      <c r="C131" s="45" t="s">
+      <c r="C131" s="44" t="s">
         <v>263</v>
       </c>
-      <c r="D131" s="46">
+      <c r="D131" s="45">
         <v>29</v>
       </c>
-      <c r="E131" s="47">
+      <c r="E131" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F131" s="47">
+      <c r="F131" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G131" s="48">
+      <c r="G131" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E131-F131</f>
         <v>29</v>
       </c>
@@ -7852,7 +7849,7 @@
       </c>
     </row>
     <row r="132" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="27" t="s">
+      <c r="B132" s="103" t="s">
         <v>264</v>
       </c>
       <c r="C132" s="25" t="s">
@@ -7881,24 +7878,24 @@
       </c>
     </row>
     <row r="133" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="104" t="s">
+      <c r="B133" s="103" t="s">
         <v>266</v>
       </c>
-      <c r="C133" s="74" t="s">
+      <c r="C133" s="73" t="s">
         <v>267</v>
       </c>
-      <c r="D133" s="75">
+      <c r="D133" s="74">
         <v>54</v>
       </c>
-      <c r="E133" s="76">
+      <c r="E133" s="75">
         <f t="shared" ref="E133:E198" si="9">SUMIF($J$4:$J$5000, B133, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F133" s="76">
+      <c r="F133" s="75">
         <f t="shared" ref="F133:F198" si="10">SUMIF($O$4:$O$5000, B133, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G133" s="77">
+      <c r="G133" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E133-F133</f>
         <v>54</v>
       </c>
@@ -7912,24 +7909,24 @@
       </c>
     </row>
     <row r="134" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B134" s="104" t="s">
+      <c r="B134" s="103" t="s">
         <v>268</v>
       </c>
-      <c r="C134" s="74" t="s">
+      <c r="C134" s="73" t="s">
         <v>269</v>
       </c>
-      <c r="D134" s="75">
+      <c r="D134" s="74">
         <v>60</v>
       </c>
-      <c r="E134" s="76">
+      <c r="E134" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F134" s="76">
+      <c r="F134" s="75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G134" s="77">
+      <c r="G134" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E134-F134</f>
         <v>60</v>
       </c>
@@ -7943,24 +7940,24 @@
       </c>
     </row>
     <row r="135" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B135" s="104" t="s">
+      <c r="B135" s="103" t="s">
         <v>270</v>
       </c>
-      <c r="C135" s="45" t="s">
+      <c r="C135" s="44" t="s">
         <v>271</v>
       </c>
-      <c r="D135" s="46">
+      <c r="D135" s="45">
         <v>11</v>
       </c>
-      <c r="E135" s="47">
+      <c r="E135" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F135" s="47">
+      <c r="F135" s="46">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G135" s="48">
+      <c r="G135" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E135-F135</f>
         <v>11</v>
       </c>
@@ -7974,24 +7971,24 @@
       </c>
     </row>
     <row r="136" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B136" s="104" t="s">
+      <c r="B136" s="103" t="s">
         <v>272</v>
       </c>
-      <c r="C136" s="45" t="s">
+      <c r="C136" s="44" t="s">
         <v>273</v>
       </c>
-      <c r="D136" s="46">
+      <c r="D136" s="45">
         <v>40</v>
       </c>
-      <c r="E136" s="47">
+      <c r="E136" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F136" s="47">
+      <c r="F136" s="46">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G136" s="48">
+      <c r="G136" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E136-F136</f>
         <v>40</v>
       </c>
@@ -8005,24 +8002,24 @@
       </c>
     </row>
     <row r="137" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B137" s="104" t="s">
+      <c r="B137" s="103" t="s">
         <v>274</v>
       </c>
-      <c r="C137" s="45" t="s">
+      <c r="C137" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="D137" s="46">
+      <c r="D137" s="45">
         <v>16</v>
       </c>
-      <c r="E137" s="47">
+      <c r="E137" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F137" s="47">
+      <c r="F137" s="46">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G137" s="48">
+      <c r="G137" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E137-F137</f>
         <v>16</v>
       </c>
@@ -8036,24 +8033,24 @@
       </c>
     </row>
     <row r="138" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B138" s="104" t="s">
+      <c r="B138" s="103" t="s">
         <v>276</v>
       </c>
-      <c r="C138" s="45" t="s">
+      <c r="C138" s="44" t="s">
         <v>277</v>
       </c>
-      <c r="D138" s="46">
+      <c r="D138" s="45">
         <v>5</v>
       </c>
-      <c r="E138" s="47">
+      <c r="E138" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F138" s="47">
+      <c r="F138" s="46">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G138" s="48">
+      <c r="G138" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E138-F138</f>
         <v>5</v>
       </c>
@@ -8067,7 +8064,7 @@
       </c>
     </row>
     <row r="139" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B139" s="27" t="s">
+      <c r="B139" s="103" t="s">
         <v>278</v>
       </c>
       <c r="C139" s="25" t="s">
@@ -8096,24 +8093,24 @@
       </c>
     </row>
     <row r="140" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B140" s="44" t="s">
+      <c r="B140" s="103" t="s">
         <v>280</v>
       </c>
-      <c r="C140" s="45" t="s">
+      <c r="C140" s="44" t="s">
         <v>281</v>
       </c>
-      <c r="D140" s="46">
+      <c r="D140" s="45">
         <v>39</v>
       </c>
-      <c r="E140" s="47">
+      <c r="E140" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F140" s="47">
+      <c r="F140" s="46">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G140" s="48">
+      <c r="G140" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E140-F140</f>
         <v>39</v>
       </c>
@@ -8126,95 +8123,95 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:16" s="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B141" s="44" t="s">
+    <row r="141" spans="2:16" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B141" s="103" t="s">
         <v>282</v>
       </c>
-      <c r="C141" s="45" t="s">
+      <c r="C141" s="44" t="s">
         <v>283</v>
       </c>
-      <c r="D141" s="46">
+      <c r="D141" s="45">
         <v>47</v>
       </c>
-      <c r="E141" s="47">
+      <c r="E141" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F141" s="47">
+      <c r="F141" s="46">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G141" s="48">
+      <c r="G141" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E141-F141</f>
         <v>47</v>
       </c>
       <c r="H141"/>
-      <c r="K141" s="84" t="str">
+      <c r="K141" s="83" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P141" s="84" t="str">
+      <c r="P141" s="83" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="142" spans="2:16" s="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B142" s="79" t="s">
+    <row r="142" spans="2:16" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B142" s="103" t="s">
         <v>284</v>
       </c>
-      <c r="C142" s="80" t="s">
+      <c r="C142" s="79" t="s">
         <v>285</v>
       </c>
-      <c r="D142" s="81">
+      <c r="D142" s="80">
         <v>38</v>
       </c>
-      <c r="E142" s="82">
+      <c r="E142" s="81">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F142" s="82">
+      <c r="F142" s="81">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G142" s="83">
+      <c r="G142" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E142-F142</f>
         <v>38</v>
       </c>
-      <c r="H142" s="70" t="s">
+      <c r="H142" s="69" t="s">
         <v>605</v>
       </c>
-      <c r="K142" s="84" t="str">
+      <c r="K142" s="83" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P142" s="84" t="str">
+      <c r="P142" s="83" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="143" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B143" s="79" t="s">
+      <c r="B143" s="103" t="s">
         <v>286</v>
       </c>
-      <c r="C143" s="80" t="s">
+      <c r="C143" s="79" t="s">
         <v>287</v>
       </c>
-      <c r="D143" s="81">
+      <c r="D143" s="80">
         <v>18</v>
       </c>
-      <c r="E143" s="82">
+      <c r="E143" s="81">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F143" s="82">
+      <c r="F143" s="81">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G143" s="83">
+      <c r="G143" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E143-F143</f>
         <v>18</v>
       </c>
-      <c r="H143" s="70"/>
+      <c r="H143" s="69"/>
       <c r="K143" s="19" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8225,24 +8222,24 @@
       </c>
     </row>
     <row r="144" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B144" s="104" t="s">
+      <c r="B144" s="103" t="s">
         <v>212</v>
       </c>
-      <c r="C144" s="61" t="s">
+      <c r="C144" s="60" t="s">
         <v>213</v>
       </c>
-      <c r="D144" s="59">
+      <c r="D144" s="58">
         <v>7</v>
       </c>
-      <c r="E144" s="62">
+      <c r="E144" s="61">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F144" s="62">
+      <c r="F144" s="61">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G144" s="63">
+      <c r="G144" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E144-F144</f>
         <v>7</v>
       </c>
@@ -8256,24 +8253,24 @@
       </c>
     </row>
     <row r="145" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B145" s="44" t="s">
+      <c r="B145" s="103" t="s">
         <v>288</v>
       </c>
-      <c r="C145" s="45" t="s">
+      <c r="C145" s="44" t="s">
         <v>289</v>
       </c>
-      <c r="D145" s="46">
+      <c r="D145" s="45">
         <v>50</v>
       </c>
-      <c r="E145" s="47">
+      <c r="E145" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F145" s="47">
+      <c r="F145" s="46">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G145" s="48">
+      <c r="G145" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E145-F145</f>
         <v>50</v>
       </c>
@@ -8287,24 +8284,24 @@
       </c>
     </row>
     <row r="146" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B146" s="44" t="s">
+      <c r="B146" s="103" t="s">
         <v>290</v>
       </c>
-      <c r="C146" s="45" t="s">
+      <c r="C146" s="44" t="s">
         <v>291</v>
       </c>
-      <c r="D146" s="46">
+      <c r="D146" s="45">
         <v>39</v>
       </c>
-      <c r="E146" s="47">
+      <c r="E146" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F146" s="47">
+      <c r="F146" s="46">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G146" s="48">
+      <c r="G146" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E146-F146</f>
         <v>39</v>
       </c>
@@ -8318,7 +8315,7 @@
       </c>
     </row>
     <row r="147" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B147" s="27" t="s">
+      <c r="B147" s="103" t="s">
         <v>292</v>
       </c>
       <c r="C147" s="25" t="s">
@@ -8347,7 +8344,7 @@
       </c>
     </row>
     <row r="148" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B148" s="27" t="s">
+      <c r="B148" s="103" t="s">
         <v>294</v>
       </c>
       <c r="C148" s="25" t="s">
@@ -8376,7 +8373,7 @@
       </c>
     </row>
     <row r="149" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B149" s="27" t="s">
+      <c r="B149" s="103" t="s">
         <v>296</v>
       </c>
       <c r="C149" s="25" t="s">
@@ -8405,7 +8402,7 @@
       </c>
     </row>
     <row r="150" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B150" s="27" t="s">
+      <c r="B150" s="103" t="s">
         <v>298</v>
       </c>
       <c r="C150" s="25" t="s">
@@ -8434,7 +8431,7 @@
       </c>
     </row>
     <row r="151" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B151" s="27" t="s">
+      <c r="B151" s="103" t="s">
         <v>300</v>
       </c>
       <c r="C151" s="25" t="s">
@@ -8463,7 +8460,7 @@
       </c>
     </row>
     <row r="152" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B152" s="27" t="s">
+      <c r="B152" s="103" t="s">
         <v>302</v>
       </c>
       <c r="C152" s="25" t="s">
@@ -8491,57 +8488,57 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:16" s="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B153" s="49" t="s">
+    <row r="153" spans="2:16" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B153" s="48" t="s">
         <v>576</v>
       </c>
-      <c r="C153" s="45"/>
-      <c r="D153" s="50">
+      <c r="C153" s="44"/>
+      <c r="D153" s="49">
         <v>37</v>
       </c>
-      <c r="E153" s="47">
+      <c r="E153" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F153" s="47">
+      <c r="F153" s="46">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G153" s="48">
+      <c r="G153" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E153-F153</f>
         <v>37</v>
       </c>
       <c r="H153"/>
-      <c r="K153" s="84" t="str">
+      <c r="K153" s="83" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P153" s="84" t="str">
+      <c r="P153" s="83" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="154" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B154" s="85" t="s">
+      <c r="B154" s="84" t="s">
         <v>606</v>
       </c>
-      <c r="C154" s="80"/>
-      <c r="D154" s="86" t="s">
+      <c r="C154" s="79"/>
+      <c r="D154" s="85" t="s">
         <v>607</v>
       </c>
-      <c r="E154" s="82">
+      <c r="E154" s="81">
         <f>SUMIF($J$4:$J$5000, B154, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F154" s="82">
+      <c r="F154" s="81">
         <f>SUMIF($O$4:$O$5000, B154, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G154" s="83">
+      <c r="G154" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E154-F154</f>
         <v>47</v>
       </c>
-      <c r="H154" s="70"/>
+      <c r="H154" s="69"/>
       <c r="K154" s="19" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8552,24 +8549,24 @@
       </c>
     </row>
     <row r="155" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B155" s="79" t="s">
+      <c r="B155" s="78" t="s">
         <v>304</v>
       </c>
-      <c r="C155" s="80" t="s">
+      <c r="C155" s="79" t="s">
         <v>305</v>
       </c>
-      <c r="D155" s="81">
+      <c r="D155" s="80">
         <v>260</v>
       </c>
-      <c r="E155" s="82">
+      <c r="E155" s="81">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F155" s="82">
+      <c r="F155" s="81">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G155" s="83">
+      <c r="G155" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E155-F155</f>
         <v>260</v>
       </c>
@@ -8641,24 +8638,24 @@
       </c>
     </row>
     <row r="158" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B158" s="79" t="s">
+      <c r="B158" s="78" t="s">
         <v>310</v>
       </c>
-      <c r="C158" s="80" t="s">
+      <c r="C158" s="79" t="s">
         <v>311</v>
       </c>
-      <c r="D158" s="81">
+      <c r="D158" s="80">
         <v>33</v>
       </c>
-      <c r="E158" s="82">
+      <c r="E158" s="81">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F158" s="82">
+      <c r="F158" s="81">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G158" s="83">
+      <c r="G158" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E158-F158</f>
         <v>33</v>
       </c>
@@ -8846,28 +8843,28 @@
       </c>
     </row>
     <row r="165" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B165" s="73" t="s">
+      <c r="B165" s="103" t="s">
         <v>324</v>
       </c>
-      <c r="C165" s="74" t="s">
+      <c r="C165" s="73" t="s">
         <v>325</v>
       </c>
-      <c r="D165" s="75">
+      <c r="D165" s="74">
         <v>2</v>
       </c>
-      <c r="E165" s="76">
+      <c r="E165" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F165" s="76">
+      <c r="F165" s="75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G165" s="77">
+      <c r="G165" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E165-F165</f>
         <v>2</v>
       </c>
-      <c r="H165" s="71" t="s">
+      <c r="H165" s="70" t="s">
         <v>586</v>
       </c>
       <c r="K165" s="19" t="str">
@@ -8880,7 +8877,7 @@
       </c>
     </row>
     <row r="166" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B166" s="27" t="s">
+      <c r="B166" s="103" t="s">
         <v>326</v>
       </c>
       <c r="C166" s="25" t="s">
@@ -8909,24 +8906,24 @@
       </c>
     </row>
     <row r="167" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B167" s="73" t="s">
+      <c r="B167" s="103" t="s">
         <v>328</v>
       </c>
-      <c r="C167" s="74" t="s">
+      <c r="C167" s="73" t="s">
         <v>329</v>
       </c>
-      <c r="D167" s="75">
+      <c r="D167" s="74">
         <v>5</v>
       </c>
-      <c r="E167" s="76">
+      <c r="E167" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F167" s="76">
+      <c r="F167" s="75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G167" s="77">
+      <c r="G167" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E167-F167</f>
         <v>5</v>
       </c>
@@ -8940,24 +8937,24 @@
       </c>
     </row>
     <row r="168" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B168" s="79" t="s">
+      <c r="B168" s="103" t="s">
         <v>332</v>
       </c>
-      <c r="C168" s="80" t="s">
+      <c r="C168" s="79" t="s">
         <v>333</v>
       </c>
-      <c r="D168" s="81">
+      <c r="D168" s="80">
         <v>10</v>
       </c>
-      <c r="E168" s="82">
+      <c r="E168" s="81">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F168" s="82">
+      <c r="F168" s="81">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G168" s="83">
+      <c r="G168" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E168-F168</f>
         <v>10</v>
       </c>
@@ -8971,24 +8968,24 @@
       </c>
     </row>
     <row r="169" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B169" s="79" t="s">
+      <c r="B169" s="103" t="s">
         <v>330</v>
       </c>
-      <c r="C169" s="80" t="s">
+      <c r="C169" s="79" t="s">
         <v>331</v>
       </c>
-      <c r="D169" s="81">
+      <c r="D169" s="80">
         <v>4</v>
       </c>
-      <c r="E169" s="82">
+      <c r="E169" s="81">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F169" s="82">
+      <c r="F169" s="81">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G169" s="83">
+      <c r="G169" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E169-F169</f>
         <v>4</v>
       </c>
@@ -9147,24 +9144,24 @@
       </c>
     </row>
     <row r="175" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B175" s="73" t="s">
+      <c r="B175" s="103" t="s">
         <v>346</v>
       </c>
-      <c r="C175" s="74" t="s">
+      <c r="C175" s="73" t="s">
         <v>347</v>
       </c>
-      <c r="D175" s="75">
+      <c r="D175" s="74">
         <v>156</v>
       </c>
-      <c r="E175" s="76">
+      <c r="E175" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F175" s="76">
+      <c r="F175" s="75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G175" s="77">
+      <c r="G175" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E175-F175</f>
         <v>156</v>
       </c>
@@ -9178,24 +9175,24 @@
       </c>
     </row>
     <row r="176" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B176" s="73" t="s">
+      <c r="B176" s="103" t="s">
         <v>348</v>
       </c>
-      <c r="C176" s="74" t="s">
+      <c r="C176" s="73" t="s">
         <v>349</v>
       </c>
-      <c r="D176" s="75">
+      <c r="D176" s="74">
         <v>1</v>
       </c>
-      <c r="E176" s="76">
+      <c r="E176" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F176" s="76">
+      <c r="F176" s="75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G176" s="77">
+      <c r="G176" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E176-F176</f>
         <v>1</v>
       </c>
@@ -9209,24 +9206,24 @@
       </c>
     </row>
     <row r="177" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B177" s="73" t="s">
+      <c r="B177" s="103" t="s">
         <v>350</v>
       </c>
-      <c r="C177" s="74" t="s">
+      <c r="C177" s="73" t="s">
         <v>351</v>
       </c>
-      <c r="D177" s="75">
+      <c r="D177" s="74">
         <v>42</v>
       </c>
-      <c r="E177" s="76">
+      <c r="E177" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F177" s="76">
+      <c r="F177" s="75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G177" s="77">
+      <c r="G177" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E177-F177</f>
         <v>42</v>
       </c>
@@ -9240,24 +9237,24 @@
       </c>
     </row>
     <row r="178" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B178" s="73" t="s">
+      <c r="B178" s="103" t="s">
         <v>352</v>
       </c>
-      <c r="C178" s="74" t="s">
+      <c r="C178" s="73" t="s">
         <v>353</v>
       </c>
-      <c r="D178" s="75">
+      <c r="D178" s="74">
         <v>2</v>
       </c>
-      <c r="E178" s="76">
+      <c r="E178" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F178" s="76">
+      <c r="F178" s="75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G178" s="77">
+      <c r="G178" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E178-F178</f>
         <v>2</v>
       </c>
@@ -9271,24 +9268,24 @@
       </c>
     </row>
     <row r="179" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B179" s="73" t="s">
+      <c r="B179" s="103" t="s">
         <v>620</v>
       </c>
-      <c r="C179" s="74" t="s">
+      <c r="C179" s="73" t="s">
         <v>621</v>
       </c>
-      <c r="D179" s="74" t="s">
+      <c r="D179" s="73" t="s">
         <v>622</v>
       </c>
-      <c r="E179" s="76">
+      <c r="E179" s="75">
         <f>SUMIF($J$4:$J$5000, B179, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F179" s="76">
+      <c r="F179" s="75">
         <f>SUMIF($O$4:$O$5000, B179, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G179" s="77">
+      <c r="G179" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E179-F179</f>
         <v>4</v>
       </c>
@@ -9505,24 +9502,24 @@
       </c>
     </row>
     <row r="187" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B187" s="73" t="s">
+      <c r="B187" s="72" t="s">
         <v>604</v>
       </c>
-      <c r="C187" s="74" t="s">
+      <c r="C187" s="73" t="s">
         <v>366</v>
       </c>
-      <c r="D187" s="75">
+      <c r="D187" s="74">
         <v>1</v>
       </c>
-      <c r="E187" s="76">
+      <c r="E187" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F187" s="76">
+      <c r="F187" s="75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G187" s="77">
+      <c r="G187" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E187-F187</f>
         <v>1</v>
       </c>
@@ -9565,24 +9562,24 @@
       </c>
     </row>
     <row r="189" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B189" s="73" t="s">
+      <c r="B189" s="72" t="s">
         <v>369</v>
       </c>
-      <c r="C189" s="74" t="s">
+      <c r="C189" s="73" t="s">
         <v>370</v>
       </c>
-      <c r="D189" s="75">
+      <c r="D189" s="74">
         <v>4</v>
       </c>
-      <c r="E189" s="76">
+      <c r="E189" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F189" s="76">
+      <c r="F189" s="75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G189" s="77">
+      <c r="G189" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E189-F189</f>
         <v>4</v>
       </c>
@@ -9596,24 +9593,24 @@
       </c>
     </row>
     <row r="190" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B190" s="73" t="s">
+      <c r="B190" s="72" t="s">
         <v>371</v>
       </c>
-      <c r="C190" s="74" t="s">
+      <c r="C190" s="73" t="s">
         <v>372</v>
       </c>
-      <c r="D190" s="75">
+      <c r="D190" s="74">
         <v>61</v>
       </c>
-      <c r="E190" s="76">
+      <c r="E190" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F190" s="76">
+      <c r="F190" s="75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G190" s="77">
+      <c r="G190" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E190-F190</f>
         <v>61</v>
       </c>
@@ -9655,7 +9652,7 @@
         <v/>
       </c>
     </row>
-    <row r="192" spans="2:16" s="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:16" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B192" s="27" t="s">
         <v>375</v>
       </c>
@@ -9676,16 +9673,16 @@
         <v>0</v>
       </c>
       <c r="H192"/>
-      <c r="K192" s="84" t="str">
+      <c r="K192" s="83" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P192" s="84" t="str">
+      <c r="P192" s="83" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="193" spans="2:16" s="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:16" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B193" s="27" t="s">
         <v>376</v>
       </c>
@@ -9706,38 +9703,38 @@
         <v>0</v>
       </c>
       <c r="H193"/>
-      <c r="K193" s="84" t="str">
+      <c r="K193" s="83" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P193" s="84" t="str">
+      <c r="P193" s="83" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="194" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B194" s="79" t="s">
+      <c r="B194" s="78" t="s">
         <v>378</v>
       </c>
-      <c r="C194" s="80" t="s">
+      <c r="C194" s="79" t="s">
         <v>379</v>
       </c>
-      <c r="D194" s="81">
+      <c r="D194" s="80">
         <v>165</v>
       </c>
-      <c r="E194" s="82">
+      <c r="E194" s="81">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F194" s="82">
+      <c r="F194" s="81">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G194" s="83">
+      <c r="G194" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E194-F194</f>
         <v>165</v>
       </c>
-      <c r="H194" s="70"/>
+      <c r="H194" s="69"/>
       <c r="K194" s="19" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9748,28 +9745,28 @@
       </c>
     </row>
     <row r="195" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B195" s="79" t="s">
+      <c r="B195" s="78" t="s">
         <v>380</v>
       </c>
-      <c r="C195" s="80" t="s">
+      <c r="C195" s="79" t="s">
         <v>381</v>
       </c>
-      <c r="D195" s="81">
+      <c r="D195" s="80">
         <v>329</v>
       </c>
-      <c r="E195" s="82">
+      <c r="E195" s="81">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F195" s="82">
+      <c r="F195" s="81">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G195" s="83">
+      <c r="G195" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E195-F195</f>
         <v>329</v>
       </c>
-      <c r="H195" s="70"/>
+      <c r="H195" s="69"/>
       <c r="K195" s="19" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -10041,7 +10038,7 @@
       </c>
     </row>
     <row r="205" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B205" s="27" t="s">
+      <c r="B205" s="103" t="s">
         <v>404</v>
       </c>
       <c r="C205" s="25" t="s">
@@ -10070,24 +10067,24 @@
       </c>
     </row>
     <row r="206" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B206" s="73" t="s">
+      <c r="B206" s="103" t="s">
         <v>406</v>
       </c>
-      <c r="C206" s="74" t="s">
+      <c r="C206" s="73" t="s">
         <v>407</v>
       </c>
-      <c r="D206" s="75">
+      <c r="D206" s="74">
         <v>50</v>
       </c>
-      <c r="E206" s="76">
+      <c r="E206" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F206" s="76">
+      <c r="F206" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G206" s="77">
+      <c r="G206" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E206-F206</f>
         <v>50</v>
       </c>
@@ -10101,24 +10098,24 @@
       </c>
     </row>
     <row r="207" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B207" s="73" t="s">
+      <c r="B207" s="103" t="s">
         <v>408</v>
       </c>
-      <c r="C207" s="74" t="s">
+      <c r="C207" s="73" t="s">
         <v>409</v>
       </c>
-      <c r="D207" s="75">
+      <c r="D207" s="74">
         <v>30</v>
       </c>
-      <c r="E207" s="76">
+      <c r="E207" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F207" s="76">
+      <c r="F207" s="75">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
-      <c r="G207" s="77">
+      <c r="G207" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E207-F207</f>
         <v>10</v>
       </c>
@@ -10135,7 +10132,7 @@
       </c>
     </row>
     <row r="208" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B208" s="27" t="s">
+      <c r="B208" s="103" t="s">
         <v>410</v>
       </c>
       <c r="C208" s="25" t="s">
@@ -10164,24 +10161,24 @@
       </c>
     </row>
     <row r="209" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B209" s="73" t="s">
+      <c r="B209" s="103" t="s">
         <v>412</v>
       </c>
-      <c r="C209" s="74" t="s">
+      <c r="C209" s="73" t="s">
         <v>413</v>
       </c>
-      <c r="D209" s="75">
+      <c r="D209" s="74">
         <v>70</v>
       </c>
-      <c r="E209" s="76">
+      <c r="E209" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F209" s="76">
+      <c r="F209" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G209" s="77">
+      <c r="G209" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E209-F209</f>
         <v>70</v>
       </c>
@@ -10195,24 +10192,24 @@
       </c>
     </row>
     <row r="210" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B210" s="73" t="s">
+      <c r="B210" s="103" t="s">
         <v>414</v>
       </c>
-      <c r="C210" s="74" t="s">
+      <c r="C210" s="73" t="s">
         <v>415</v>
       </c>
-      <c r="D210" s="75">
+      <c r="D210" s="74">
         <v>80</v>
       </c>
-      <c r="E210" s="76">
+      <c r="E210" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F210" s="76">
+      <c r="F210" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G210" s="77">
+      <c r="G210" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E210-F210</f>
         <v>80</v>
       </c>
@@ -10226,7 +10223,7 @@
       </c>
     </row>
     <row r="211" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B211" s="27" t="s">
+      <c r="B211" s="103" t="s">
         <v>416</v>
       </c>
       <c r="C211" s="25" t="s">
@@ -10255,24 +10252,24 @@
       </c>
     </row>
     <row r="212" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B212" s="73" t="s">
+      <c r="B212" s="103" t="s">
         <v>418</v>
       </c>
-      <c r="C212" s="74" t="s">
+      <c r="C212" s="73" t="s">
         <v>419</v>
       </c>
-      <c r="D212" s="75">
+      <c r="D212" s="74">
         <v>50</v>
       </c>
-      <c r="E212" s="76">
+      <c r="E212" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F212" s="76">
+      <c r="F212" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G212" s="77">
+      <c r="G212" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E212-F212</f>
         <v>50</v>
       </c>
@@ -10286,7 +10283,7 @@
       </c>
     </row>
     <row r="213" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B213" s="27" t="s">
+      <c r="B213" s="103" t="s">
         <v>420</v>
       </c>
       <c r="C213" s="25" t="s">
@@ -10315,7 +10312,7 @@
       </c>
     </row>
     <row r="214" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B214" s="27" t="s">
+      <c r="B214" s="103" t="s">
         <v>422</v>
       </c>
       <c r="C214" s="25" t="s">
@@ -10402,22 +10399,22 @@
       </c>
     </row>
     <row r="217" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B217" s="44" t="s">
+      <c r="B217" s="103" t="s">
         <v>575</v>
       </c>
-      <c r="C217" s="45"/>
-      <c r="D217" s="50">
+      <c r="C217" s="44"/>
+      <c r="D217" s="49">
         <v>20</v>
       </c>
-      <c r="E217" s="47">
+      <c r="E217" s="46">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F217" s="47">
+      <c r="F217" s="46">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G217" s="48">
+      <c r="G217" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E217-F217</f>
         <v>20</v>
       </c>
@@ -10431,7 +10428,7 @@
       </c>
     </row>
     <row r="218" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B218" s="27" t="s">
+      <c r="B218" s="103" t="s">
         <v>428</v>
       </c>
       <c r="C218" s="25" t="s">
@@ -10460,7 +10457,7 @@
       </c>
     </row>
     <row r="219" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B219" s="27" t="s">
+      <c r="B219" s="103" t="s">
         <v>430</v>
       </c>
       <c r="C219" s="25" t="s">
@@ -10547,24 +10544,24 @@
       </c>
     </row>
     <row r="222" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B222" s="44" t="s">
+      <c r="B222" s="103" t="s">
         <v>436</v>
       </c>
-      <c r="C222" s="45" t="s">
+      <c r="C222" s="44" t="s">
         <v>437</v>
       </c>
-      <c r="D222" s="46">
+      <c r="D222" s="45">
         <v>480</v>
       </c>
-      <c r="E222" s="47">
+      <c r="E222" s="46">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F222" s="47">
+      <c r="F222" s="46">
         <f t="shared" si="14"/>
         <v>210</v>
       </c>
-      <c r="G222" s="48">
+      <c r="G222" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E222-F222</f>
         <v>270</v>
       </c>
@@ -10578,24 +10575,24 @@
       </c>
     </row>
     <row r="223" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B223" s="44" t="s">
+      <c r="B223" s="103" t="s">
         <v>438</v>
       </c>
-      <c r="C223" s="45" t="s">
+      <c r="C223" s="44" t="s">
         <v>439</v>
       </c>
-      <c r="D223" s="46">
+      <c r="D223" s="45">
         <v>119</v>
       </c>
-      <c r="E223" s="47">
+      <c r="E223" s="46">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F223" s="47">
+      <c r="F223" s="46">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G223" s="48">
+      <c r="G223" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E223-F223</f>
         <v>119</v>
       </c>
@@ -10609,24 +10606,24 @@
       </c>
     </row>
     <row r="224" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B224" s="44" t="s">
+      <c r="B224" s="103" t="s">
         <v>440</v>
       </c>
-      <c r="C224" s="45" t="s">
+      <c r="C224" s="44" t="s">
         <v>441</v>
       </c>
-      <c r="D224" s="46">
+      <c r="D224" s="45">
         <v>89</v>
       </c>
-      <c r="E224" s="47">
+      <c r="E224" s="46">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F224" s="47">
+      <c r="F224" s="46">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G224" s="48">
+      <c r="G224" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E224-F224</f>
         <v>89</v>
       </c>
@@ -10698,7 +10695,7 @@
       </c>
     </row>
     <row r="227" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B227" s="27" t="s">
+      <c r="B227" s="103" t="s">
         <v>446</v>
       </c>
       <c r="C227" s="25" t="s">
@@ -10727,24 +10724,24 @@
       </c>
     </row>
     <row r="228" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B228" s="60" t="s">
+      <c r="B228" s="103" t="s">
         <v>448</v>
       </c>
-      <c r="C228" s="61" t="s">
+      <c r="C228" s="60" t="s">
         <v>449</v>
       </c>
-      <c r="D228" s="59">
+      <c r="D228" s="58">
         <v>700</v>
       </c>
-      <c r="E228" s="62">
+      <c r="E228" s="61">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F228" s="62">
+      <c r="F228" s="61">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G228" s="63">
+      <c r="G228" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E228-F228</f>
         <v>700</v>
       </c>
@@ -10758,28 +10755,28 @@
       </c>
     </row>
     <row r="229" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B229" s="60" t="s">
+      <c r="B229" s="103" t="s">
         <v>450</v>
       </c>
-      <c r="C229" s="61" t="s">
+      <c r="C229" s="60" t="s">
         <v>451</v>
       </c>
-      <c r="D229" s="59">
+      <c r="D229" s="58">
         <v>445</v>
       </c>
-      <c r="E229" s="62">
+      <c r="E229" s="61">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F229" s="62">
+      <c r="F229" s="61">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G229" s="63">
+      <c r="G229" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E229-F229</f>
         <v>445</v>
       </c>
-      <c r="H229" s="65" t="s">
+      <c r="H229" s="64" t="s">
         <v>581</v>
       </c>
       <c r="K229" s="19" t="str">
@@ -10792,24 +10789,24 @@
       </c>
     </row>
     <row r="230" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B230" s="79" t="s">
+      <c r="B230" s="103" t="s">
         <v>452</v>
       </c>
-      <c r="C230" s="80" t="s">
+      <c r="C230" s="79" t="s">
         <v>453</v>
       </c>
-      <c r="D230" s="81">
+      <c r="D230" s="80">
         <v>958</v>
       </c>
-      <c r="E230" s="82">
+      <c r="E230" s="81">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F230" s="82">
+      <c r="F230" s="81">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G230" s="83">
+      <c r="G230" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E230-F230</f>
         <v>958</v>
       </c>
@@ -10823,24 +10820,24 @@
       </c>
     </row>
     <row r="231" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B231" s="73" t="s">
+      <c r="B231" s="103" t="s">
         <v>454</v>
       </c>
-      <c r="C231" s="74" t="s">
+      <c r="C231" s="73" t="s">
         <v>455</v>
       </c>
-      <c r="D231" s="75">
+      <c r="D231" s="74">
         <v>14</v>
       </c>
-      <c r="E231" s="76">
+      <c r="E231" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F231" s="76">
+      <c r="F231" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G231" s="77">
+      <c r="G231" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E231-F231</f>
         <v>14</v>
       </c>
@@ -10854,7 +10851,7 @@
       </c>
     </row>
     <row r="232" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B232" s="27" t="s">
+      <c r="B232" s="103" t="s">
         <v>456</v>
       </c>
       <c r="C232" s="25" t="s">
@@ -10883,24 +10880,24 @@
       </c>
     </row>
     <row r="233" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B233" s="73" t="s">
+      <c r="B233" s="103" t="s">
         <v>458</v>
       </c>
-      <c r="C233" s="74" t="s">
+      <c r="C233" s="73" t="s">
         <v>459</v>
       </c>
-      <c r="D233" s="75">
+      <c r="D233" s="74">
         <v>30</v>
       </c>
-      <c r="E233" s="76">
+      <c r="E233" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F233" s="76">
+      <c r="F233" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G233" s="77">
+      <c r="G233" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E233-F233</f>
         <v>30</v>
       </c>
@@ -10914,24 +10911,24 @@
       </c>
     </row>
     <row r="234" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B234" s="73" t="s">
+      <c r="B234" s="103" t="s">
         <v>460</v>
       </c>
-      <c r="C234" s="74" t="s">
+      <c r="C234" s="73" t="s">
         <v>461</v>
       </c>
-      <c r="D234" s="75">
+      <c r="D234" s="74">
         <v>19</v>
       </c>
-      <c r="E234" s="76">
+      <c r="E234" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F234" s="76">
+      <c r="F234" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G234" s="77">
+      <c r="G234" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E234-F234</f>
         <v>19</v>
       </c>
@@ -10945,24 +10942,24 @@
       </c>
     </row>
     <row r="235" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B235" s="44" t="s">
+      <c r="B235" s="103" t="s">
         <v>462</v>
       </c>
-      <c r="C235" s="45" t="s">
+      <c r="C235" s="44" t="s">
         <v>463</v>
       </c>
-      <c r="D235" s="46">
+      <c r="D235" s="45">
         <v>113</v>
       </c>
-      <c r="E235" s="47">
+      <c r="E235" s="46">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F235" s="47">
+      <c r="F235" s="46">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G235" s="48">
+      <c r="G235" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E235-F235</f>
         <v>113</v>
       </c>
@@ -10976,7 +10973,7 @@
       </c>
     </row>
     <row r="236" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B236" s="27" t="s">
+      <c r="B236" s="103" t="s">
         <v>464</v>
       </c>
       <c r="C236" s="25" t="s">
@@ -11005,24 +11002,24 @@
       </c>
     </row>
     <row r="237" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B237" s="73" t="s">
+      <c r="B237" s="103" t="s">
         <v>466</v>
       </c>
-      <c r="C237" s="74" t="s">
+      <c r="C237" s="73" t="s">
         <v>467</v>
       </c>
-      <c r="D237" s="75">
+      <c r="D237" s="74">
         <v>50</v>
       </c>
-      <c r="E237" s="76">
+      <c r="E237" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F237" s="76">
+      <c r="F237" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G237" s="77">
+      <c r="G237" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E237-F237</f>
         <v>50</v>
       </c>
@@ -11036,24 +11033,24 @@
       </c>
     </row>
     <row r="238" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B238" s="73" t="s">
+      <c r="B238" s="103" t="s">
         <v>468</v>
       </c>
-      <c r="C238" s="74" t="s">
+      <c r="C238" s="73" t="s">
         <v>469</v>
       </c>
-      <c r="D238" s="75">
+      <c r="D238" s="74">
         <v>50</v>
       </c>
-      <c r="E238" s="76">
+      <c r="E238" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F238" s="76">
+      <c r="F238" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G238" s="77">
+      <c r="G238" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E238-F238</f>
         <v>50</v>
       </c>
@@ -11067,22 +11064,22 @@
       </c>
     </row>
     <row r="239" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B239" s="73" t="s">
+      <c r="B239" s="103" t="s">
         <v>470</v>
       </c>
-      <c r="C239" s="74" t="s">
+      <c r="C239" s="73" t="s">
         <v>471</v>
       </c>
-      <c r="D239" s="75"/>
-      <c r="E239" s="76">
+      <c r="D239" s="74"/>
+      <c r="E239" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F239" s="76">
+      <c r="F239" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G239" s="77">
+      <c r="G239" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E239-F239</f>
         <v>0</v>
       </c>
@@ -11096,24 +11093,24 @@
       </c>
     </row>
     <row r="240" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B240" s="44" t="s">
+      <c r="B240" s="103" t="s">
         <v>472</v>
       </c>
-      <c r="C240" s="45" t="s">
+      <c r="C240" s="44" t="s">
         <v>473</v>
       </c>
-      <c r="D240" s="46">
+      <c r="D240" s="45">
         <v>34</v>
       </c>
-      <c r="E240" s="47">
+      <c r="E240" s="46">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F240" s="47">
+      <c r="F240" s="46">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G240" s="48">
+      <c r="G240" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E240-F240</f>
         <v>34</v>
       </c>
@@ -11127,24 +11124,24 @@
       </c>
     </row>
     <row r="241" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B241" s="73" t="s">
+      <c r="B241" s="72" t="s">
         <v>591</v>
       </c>
-      <c r="C241" s="74" t="s">
+      <c r="C241" s="73" t="s">
         <v>395</v>
       </c>
-      <c r="D241" s="75">
+      <c r="D241" s="74">
         <v>1000</v>
       </c>
-      <c r="E241" s="76">
+      <c r="E241" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F241" s="76">
+      <c r="F241" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G241" s="77">
+      <c r="G241" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E241-F241</f>
         <v>1000</v>
       </c>
@@ -11187,24 +11184,24 @@
       </c>
     </row>
     <row r="243" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B243" s="104" t="s">
+      <c r="B243" s="103" t="s">
         <v>476</v>
       </c>
-      <c r="C243" s="45" t="s">
+      <c r="C243" s="44" t="s">
         <v>477</v>
       </c>
-      <c r="D243" s="46">
+      <c r="D243" s="45">
         <v>210</v>
       </c>
-      <c r="E243" s="47">
+      <c r="E243" s="46">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F243" s="47">
+      <c r="F243" s="46">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G243" s="48">
+      <c r="G243" s="47">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E243-F243</f>
         <v>210</v>
       </c>
@@ -11218,24 +11215,24 @@
       </c>
     </row>
     <row r="244" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B244" s="73" t="s">
+      <c r="B244" s="72" t="s">
         <v>589</v>
       </c>
-      <c r="C244" s="74" t="s">
+      <c r="C244" s="73" t="s">
         <v>397</v>
       </c>
-      <c r="D244" s="75">
+      <c r="D244" s="74">
         <v>100</v>
       </c>
-      <c r="E244" s="76">
+      <c r="E244" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F244" s="76">
+      <c r="F244" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G244" s="77">
+      <c r="G244" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E244-F244</f>
         <v>100</v>
       </c>
@@ -11249,24 +11246,24 @@
       </c>
     </row>
     <row r="245" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B245" s="104" t="s">
+      <c r="B245" s="103" t="s">
         <v>478</v>
       </c>
-      <c r="C245" s="74" t="s">
+      <c r="C245" s="73" t="s">
         <v>479</v>
       </c>
-      <c r="D245" s="75">
+      <c r="D245" s="74">
         <v>32</v>
       </c>
-      <c r="E245" s="76">
+      <c r="E245" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F245" s="76">
+      <c r="F245" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G245" s="77">
+      <c r="G245" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E245-F245</f>
         <v>32</v>
       </c>
@@ -11280,24 +11277,24 @@
       </c>
     </row>
     <row r="246" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B246" s="104" t="s">
+      <c r="B246" s="103" t="s">
         <v>480</v>
       </c>
-      <c r="C246" s="74" t="s">
+      <c r="C246" s="73" t="s">
         <v>481</v>
       </c>
-      <c r="D246" s="75">
+      <c r="D246" s="74">
         <v>4</v>
       </c>
-      <c r="E246" s="76">
+      <c r="E246" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F246" s="76">
+      <c r="F246" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G246" s="77">
+      <c r="G246" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E246-F246</f>
         <v>4</v>
       </c>
@@ -11340,24 +11337,24 @@
       </c>
     </row>
     <row r="248" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B248" s="104" t="s">
+      <c r="B248" s="103" t="s">
         <v>484</v>
       </c>
-      <c r="C248" s="61" t="s">
+      <c r="C248" s="60" t="s">
         <v>485</v>
       </c>
-      <c r="D248" s="59">
+      <c r="D248" s="58">
         <v>32</v>
       </c>
-      <c r="E248" s="62">
+      <c r="E248" s="61">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F248" s="62">
+      <c r="F248" s="61">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G248" s="63">
+      <c r="G248" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E248-F248</f>
         <v>32</v>
       </c>
@@ -11374,24 +11371,24 @@
       </c>
     </row>
     <row r="249" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B249" s="104" t="s">
+      <c r="B249" s="103" t="s">
         <v>486</v>
       </c>
-      <c r="C249" s="74" t="s">
+      <c r="C249" s="73" t="s">
         <v>487</v>
       </c>
-      <c r="D249" s="75">
+      <c r="D249" s="74">
         <v>30</v>
       </c>
-      <c r="E249" s="76">
+      <c r="E249" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F249" s="76">
+      <c r="F249" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G249" s="77">
+      <c r="G249" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E249-F249</f>
         <v>30</v>
       </c>
@@ -11405,24 +11402,24 @@
       </c>
     </row>
     <row r="250" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B250" s="104" t="s">
+      <c r="B250" s="103" t="s">
         <v>488</v>
       </c>
-      <c r="C250" s="74" t="s">
+      <c r="C250" s="73" t="s">
         <v>489</v>
       </c>
-      <c r="D250" s="75">
+      <c r="D250" s="74">
         <v>30</v>
       </c>
-      <c r="E250" s="76">
+      <c r="E250" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F250" s="76">
+      <c r="F250" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G250" s="77">
+      <c r="G250" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E250-F250</f>
         <v>30</v>
       </c>
@@ -11436,7 +11433,7 @@
       </c>
     </row>
     <row r="251" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B251" s="104" t="s">
+      <c r="B251" s="103" t="s">
         <v>490</v>
       </c>
       <c r="C251" s="25" t="s">
@@ -11465,7 +11462,7 @@
       </c>
     </row>
     <row r="252" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B252" s="104" t="s">
+      <c r="B252" s="103" t="s">
         <v>492</v>
       </c>
       <c r="C252" s="25" t="s">
@@ -11494,24 +11491,24 @@
       </c>
     </row>
     <row r="253" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B253" s="73" t="s">
+      <c r="B253" s="72" t="s">
         <v>494</v>
       </c>
-      <c r="C253" s="74" t="s">
+      <c r="C253" s="73" t="s">
         <v>495</v>
       </c>
-      <c r="D253" s="75">
+      <c r="D253" s="74">
         <v>49</v>
       </c>
-      <c r="E253" s="76">
+      <c r="E253" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F253" s="76">
+      <c r="F253" s="75">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
-      <c r="G253" s="77">
+      <c r="G253" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E253-F253</f>
         <v>29</v>
       </c>
@@ -11528,24 +11525,24 @@
       </c>
     </row>
     <row r="254" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B254" s="104" t="s">
+      <c r="B254" s="103" t="s">
         <v>496</v>
       </c>
-      <c r="C254" s="80" t="s">
+      <c r="C254" s="79" t="s">
         <v>497</v>
       </c>
-      <c r="D254" s="81">
+      <c r="D254" s="80">
         <v>126</v>
       </c>
-      <c r="E254" s="82">
+      <c r="E254" s="81">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F254" s="82">
+      <c r="F254" s="81">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G254" s="83">
+      <c r="G254" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E254-F254</f>
         <v>126</v>
       </c>
@@ -11559,7 +11556,7 @@
       </c>
     </row>
     <row r="255" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B255" s="104" t="s">
+      <c r="B255" s="103" t="s">
         <v>498</v>
       </c>
       <c r="C255" s="25" t="s">
@@ -11588,24 +11585,24 @@
       </c>
     </row>
     <row r="256" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B256" s="104" t="s">
+      <c r="B256" s="103" t="s">
         <v>500</v>
       </c>
-      <c r="C256" s="74" t="s">
+      <c r="C256" s="73" t="s">
         <v>501</v>
       </c>
-      <c r="D256" s="75">
+      <c r="D256" s="74">
         <v>13</v>
       </c>
-      <c r="E256" s="76">
+      <c r="E256" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F256" s="76">
+      <c r="F256" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G256" s="77">
+      <c r="G256" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E256-F256</f>
         <v>13</v>
       </c>
@@ -11854,24 +11851,24 @@
       </c>
     </row>
     <row r="265" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B265" s="104" t="s">
+      <c r="B265" s="103" t="s">
         <v>502</v>
       </c>
-      <c r="C265" s="74" t="s">
+      <c r="C265" s="73" t="s">
         <v>503</v>
       </c>
-      <c r="D265" s="75">
+      <c r="D265" s="74">
         <v>79</v>
       </c>
-      <c r="E265" s="76">
+      <c r="E265" s="75">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F265" s="76">
+      <c r="F265" s="75">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G265" s="77">
+      <c r="G265" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E265-F265</f>
         <v>79</v>
       </c>
@@ -11885,23 +11882,23 @@
       </c>
     </row>
     <row r="266" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B266" s="104" t="s">
+      <c r="B266" s="103" t="s">
         <v>520</v>
       </c>
-      <c r="C266" s="61" t="s">
+      <c r="C266" s="60" t="s">
         <v>521</v>
       </c>
-      <c r="D266" s="59">
+      <c r="D266" s="58">
         <v>50</v>
       </c>
-      <c r="E266" s="62">
-        <v>0</v>
-      </c>
-      <c r="F266" s="62">
+      <c r="E266" s="61">
+        <v>0</v>
+      </c>
+      <c r="F266" s="61">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G266" s="63">
+      <c r="G266" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E266-F266</f>
         <v>50</v>
       </c>
@@ -11915,23 +11912,23 @@
       </c>
     </row>
     <row r="267" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B267" s="104" t="s">
+      <c r="B267" s="103" t="s">
         <v>522</v>
       </c>
-      <c r="C267" s="61" t="s">
+      <c r="C267" s="60" t="s">
         <v>523</v>
       </c>
-      <c r="D267" s="59">
+      <c r="D267" s="58">
         <v>9</v>
       </c>
-      <c r="E267" s="62">
-        <v>0</v>
-      </c>
-      <c r="F267" s="62">
+      <c r="E267" s="61">
+        <v>0</v>
+      </c>
+      <c r="F267" s="61">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G267" s="63">
+      <c r="G267" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E267-F267</f>
         <v>9</v>
       </c>
@@ -11945,27 +11942,27 @@
       </c>
     </row>
     <row r="268" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B268" s="104" t="s">
+      <c r="B268" s="103" t="s">
         <v>524</v>
       </c>
-      <c r="C268" s="61" t="s">
+      <c r="C268" s="60" t="s">
         <v>525</v>
       </c>
-      <c r="D268" s="59">
+      <c r="D268" s="58">
         <v>6</v>
       </c>
-      <c r="E268" s="62">
-        <v>0</v>
-      </c>
-      <c r="F268" s="62">
+      <c r="E268" s="61">
+        <v>0</v>
+      </c>
+      <c r="F268" s="61">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G268" s="63">
+      <c r="G268" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E268-F268</f>
         <v>6</v>
       </c>
-      <c r="H268" s="65" t="s">
+      <c r="H268" s="64" t="s">
         <v>580</v>
       </c>
       <c r="K268" s="19" t="str">
@@ -11978,23 +11975,23 @@
       </c>
     </row>
     <row r="269" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B269" s="104" t="s">
+      <c r="B269" s="103" t="s">
         <v>526</v>
       </c>
-      <c r="C269" s="61" t="s">
+      <c r="C269" s="60" t="s">
         <v>527</v>
       </c>
-      <c r="D269" s="59">
+      <c r="D269" s="58">
         <v>10</v>
       </c>
-      <c r="E269" s="62">
-        <v>0</v>
-      </c>
-      <c r="F269" s="62">
+      <c r="E269" s="61">
+        <v>0</v>
+      </c>
+      <c r="F269" s="61">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G269" s="63">
+      <c r="G269" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E269-F269</f>
         <v>10</v>
       </c>
@@ -12008,22 +12005,22 @@
       </c>
     </row>
     <row r="270" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B270" s="73" t="s">
+      <c r="B270" s="72" t="s">
         <v>528</v>
       </c>
-      <c r="C270" s="74" t="s">
+      <c r="C270" s="73" t="s">
         <v>529</v>
       </c>
-      <c r="D270" s="75"/>
-      <c r="E270" s="76">
+      <c r="D270" s="74"/>
+      <c r="E270" s="75">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F270" s="76">
+      <c r="F270" s="75">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G270" s="77">
+      <c r="G270" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E270-F270</f>
         <v>0</v>
       </c>
@@ -12066,23 +12063,23 @@
       </c>
     </row>
     <row r="272" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B272" s="104" t="s">
+      <c r="B272" s="103" t="s">
         <v>532</v>
       </c>
-      <c r="C272" s="61" t="s">
+      <c r="C272" s="60" t="s">
         <v>533</v>
       </c>
-      <c r="D272" s="59">
+      <c r="D272" s="58">
         <v>17</v>
       </c>
-      <c r="E272" s="62">
-        <v>0</v>
-      </c>
-      <c r="F272" s="62">
+      <c r="E272" s="61">
+        <v>0</v>
+      </c>
+      <c r="F272" s="61">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G272" s="63">
+      <c r="G272" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E272-F272</f>
         <v>17</v>
       </c>
@@ -12096,23 +12093,23 @@
       </c>
     </row>
     <row r="273" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B273" s="104" t="s">
+      <c r="B273" s="103" t="s">
         <v>534</v>
       </c>
-      <c r="C273" s="61" t="s">
+      <c r="C273" s="60" t="s">
         <v>535</v>
       </c>
-      <c r="D273" s="59">
+      <c r="D273" s="58">
         <v>7</v>
       </c>
-      <c r="E273" s="62">
-        <v>0</v>
-      </c>
-      <c r="F273" s="62">
+      <c r="E273" s="61">
+        <v>0</v>
+      </c>
+      <c r="F273" s="61">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G273" s="63">
+      <c r="G273" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E273-F273</f>
         <v>7</v>
       </c>
@@ -12213,24 +12210,24 @@
       </c>
     </row>
     <row r="277" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B277" s="73" t="s">
+      <c r="B277" s="72" t="s">
         <v>542</v>
       </c>
-      <c r="C277" s="74" t="s">
+      <c r="C277" s="73" t="s">
         <v>543</v>
       </c>
-      <c r="D277" s="75">
+      <c r="D277" s="74">
         <v>44</v>
       </c>
-      <c r="E277" s="76">
+      <c r="E277" s="75">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F277" s="76">
+      <c r="F277" s="75">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G277" s="77">
+      <c r="G277" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E277-F277</f>
         <v>44</v>
       </c>
@@ -12244,24 +12241,24 @@
       </c>
     </row>
     <row r="278" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B278" s="73" t="s">
+      <c r="B278" s="72" t="s">
         <v>544</v>
       </c>
-      <c r="C278" s="74" t="s">
+      <c r="C278" s="73" t="s">
         <v>543</v>
       </c>
-      <c r="D278" s="75">
+      <c r="D278" s="74">
         <v>15</v>
       </c>
-      <c r="E278" s="76">
+      <c r="E278" s="75">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F278" s="76">
+      <c r="F278" s="75">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G278" s="77">
+      <c r="G278" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E278-F278</f>
         <v>15</v>
       </c>
@@ -12275,24 +12272,24 @@
       </c>
     </row>
     <row r="279" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B279" s="73" t="s">
+      <c r="B279" s="72" t="s">
         <v>545</v>
       </c>
-      <c r="C279" s="74" t="s">
+      <c r="C279" s="73" t="s">
         <v>546</v>
       </c>
-      <c r="D279" s="75">
+      <c r="D279" s="74">
         <v>10</v>
       </c>
-      <c r="E279" s="76">
+      <c r="E279" s="75">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F279" s="76">
+      <c r="F279" s="75">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G279" s="77">
+      <c r="G279" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E279-F279</f>
         <v>10</v>
       </c>
@@ -12334,125 +12331,125 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="2:16" s="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B281" s="79" t="s">
+    <row r="281" spans="2:16" s="66" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B281" s="78" t="s">
         <v>549</v>
       </c>
-      <c r="C281" s="80" t="s">
+      <c r="C281" s="79" t="s">
         <v>550</v>
       </c>
-      <c r="D281" s="81">
+      <c r="D281" s="80">
         <v>6</v>
       </c>
-      <c r="E281" s="82">
+      <c r="E281" s="81">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F281" s="82">
+      <c r="F281" s="81">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G281" s="83">
+      <c r="G281" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E281-F281</f>
         <v>6</v>
       </c>
       <c r="H281"/>
-      <c r="K281" s="68" t="str">
+      <c r="K281" s="67" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="P281" s="68" t="str">
+      <c r="P281" s="67" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="282" spans="2:16" s="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B282" s="79" t="s">
+    <row r="282" spans="2:16" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B282" s="78" t="s">
         <v>551</v>
       </c>
-      <c r="C282" s="80" t="s">
+      <c r="C282" s="79" t="s">
         <v>552</v>
       </c>
-      <c r="D282" s="81">
+      <c r="D282" s="80">
         <v>5</v>
       </c>
-      <c r="E282" s="82">
+      <c r="E282" s="81">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F282" s="82">
+      <c r="F282" s="81">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G282" s="83">
+      <c r="G282" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E282-F282</f>
         <v>5</v>
       </c>
       <c r="H282"/>
-      <c r="K282" s="84" t="str">
+      <c r="K282" s="83" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="P282" s="84" t="str">
+      <c r="P282" s="83" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="283" spans="2:16" s="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B283" s="79" t="s">
+    <row r="283" spans="2:16" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B283" s="78" t="s">
         <v>553</v>
       </c>
-      <c r="C283" s="80" t="s">
+      <c r="C283" s="79" t="s">
         <v>554</v>
       </c>
-      <c r="D283" s="81">
+      <c r="D283" s="80">
         <v>7</v>
       </c>
-      <c r="E283" s="82">
+      <c r="E283" s="81">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F283" s="82">
+      <c r="F283" s="81">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G283" s="83">
+      <c r="G283" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E283-F283</f>
         <v>7</v>
       </c>
       <c r="H283"/>
-      <c r="K283" s="84" t="str">
+      <c r="K283" s="83" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="P283" s="84" t="str">
+      <c r="P283" s="83" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="284" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B284" s="79" t="s">
+      <c r="B284" s="78" t="s">
         <v>555</v>
       </c>
-      <c r="C284" s="80" t="s">
+      <c r="C284" s="79" t="s">
         <v>556</v>
       </c>
-      <c r="D284" s="81">
+      <c r="D284" s="80">
         <v>6</v>
       </c>
-      <c r="E284" s="82">
+      <c r="E284" s="81">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F284" s="82">
+      <c r="F284" s="81">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G284" s="83">
+      <c r="G284" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E284-F284</f>
         <v>6</v>
       </c>
-      <c r="H284" s="70"/>
+      <c r="H284" s="69"/>
       <c r="K284" s="19" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -12463,28 +12460,28 @@
       </c>
     </row>
     <row r="285" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B285" s="79" t="s">
+      <c r="B285" s="78" t="s">
         <v>557</v>
       </c>
-      <c r="C285" s="80" t="s">
+      <c r="C285" s="79" t="s">
         <v>558</v>
       </c>
-      <c r="D285" s="81">
+      <c r="D285" s="80">
         <v>43</v>
       </c>
-      <c r="E285" s="82">
+      <c r="E285" s="81">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F285" s="82">
+      <c r="F285" s="81">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G285" s="83">
+      <c r="G285" s="82">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E285-F285</f>
         <v>43</v>
       </c>
-      <c r="H285" s="70"/>
+      <c r="H285" s="69"/>
       <c r="K285" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -12552,8 +12549,8 @@
         <v/>
       </c>
     </row>
-    <row r="288" spans="2:16" s="67" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B288" s="58" t="s">
+    <row r="288" spans="2:16" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B288" s="57" t="s">
         <v>567</v>
       </c>
       <c r="C288" s="17"/>
@@ -12571,16 +12568,16 @@
         <v>0</v>
       </c>
       <c r="H288"/>
-      <c r="J288" s="67" t="str">
+      <c r="J288" s="66" t="str">
         <f t="shared" ref="J288:J351" si="20">IF(I288="", "", IFERROR(VLOOKUP(I288&amp;"", $B$4:$C$5005, 2, FALSE), "NO EXISTE"))</f>
         <v/>
       </c>
-      <c r="O288" s="67" t="str">
+      <c r="O288" s="66" t="str">
         <f t="shared" ref="O288:O351" si="21">IF(N288="", "", IFERROR(VLOOKUP(N288&amp;"", $B$4:$C$5005, 2, FALSE), "NO EXISTE"))</f>
         <v/>
       </c>
     </row>
-    <row r="289" spans="2:15" s="67" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="289" spans="2:15" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B289" s="27" t="s">
         <v>563</v>
       </c>
@@ -12601,11 +12598,11 @@
         <v>0</v>
       </c>
       <c r="H289"/>
-      <c r="J289" s="67" t="str">
+      <c r="J289" s="66" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="O289" s="67" t="str">
+      <c r="O289" s="66" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -12640,25 +12637,25 @@
       </c>
     </row>
     <row r="291" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B291" s="66" t="s">
+      <c r="B291" s="65" t="s">
         <v>582</v>
       </c>
-      <c r="C291" s="66" t="s">
+      <c r="C291" s="65" t="s">
         <v>583</v>
       </c>
-      <c r="D291" s="69" t="s">
+      <c r="D291" s="68" t="s">
         <v>585</v>
       </c>
-      <c r="E291" s="62"/>
-      <c r="F291" s="62">
+      <c r="E291" s="61"/>
+      <c r="F291" s="61">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G291" s="63">
+      <c r="G291" s="62">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E291-F291</f>
         <v>1</v>
       </c>
-      <c r="H291" s="67"/>
+      <c r="H291" s="66"/>
       <c r="J291" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -12669,28 +12666,28 @@
       </c>
     </row>
     <row r="292" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B292" s="106" t="s">
+      <c r="B292" s="105" t="s">
         <v>246</v>
       </c>
-      <c r="C292" s="93" t="s">
+      <c r="C292" s="92" t="s">
         <v>584</v>
       </c>
-      <c r="D292" s="92">
+      <c r="D292" s="91">
         <v>1360</v>
       </c>
-      <c r="E292" s="76">
+      <c r="E292" s="75">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F292" s="76">
+      <c r="F292" s="75">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G292" s="77">
+      <c r="G292" s="76">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E292-F292</f>
         <v>1360</v>
       </c>
-      <c r="H292" s="67"/>
+      <c r="H292" s="66"/>
       <c r="J292" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -12701,22 +12698,22 @@
       </c>
     </row>
     <row r="293" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B293" s="91" t="s">
+      <c r="B293" s="90" t="s">
         <v>587</v>
       </c>
-      <c r="C293" s="91"/>
-      <c r="D293" s="92" t="s">
+      <c r="C293" s="90"/>
+      <c r="D293" s="91" t="s">
         <v>588</v>
       </c>
-      <c r="E293" s="92">
+      <c r="E293" s="91">
         <f>SUMIF($J$4:$J$5000, B293, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F293" s="92">
+      <c r="F293" s="91">
         <f>SUMIF($O$4:$O$5000, B293, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G293" s="92">
+      <c r="G293" s="91">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E293-F293</f>
         <v>400</v>
       </c>
@@ -12730,16 +12727,16 @@
       </c>
     </row>
     <row r="294" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B294" s="73" t="s">
+      <c r="B294" s="72" t="s">
         <v>408</v>
       </c>
-      <c r="C294" s="91"/>
-      <c r="D294" s="92" t="s">
+      <c r="C294" s="90"/>
+      <c r="D294" s="91" t="s">
         <v>594</v>
       </c>
-      <c r="E294" s="92"/>
-      <c r="F294" s="92"/>
-      <c r="G294" s="92"/>
+      <c r="E294" s="91"/>
+      <c r="F294" s="91"/>
+      <c r="G294" s="91"/>
       <c r="J294" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -12750,22 +12747,22 @@
       </c>
     </row>
     <row r="295" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B295" s="73" t="s">
+      <c r="B295" s="72" t="s">
         <v>597</v>
       </c>
-      <c r="C295" s="91"/>
-      <c r="D295" s="92" t="s">
+      <c r="C295" s="90"/>
+      <c r="D295" s="91" t="s">
         <v>594</v>
       </c>
-      <c r="E295" s="92">
+      <c r="E295" s="91">
         <f t="shared" ref="E295:E302" si="22">SUMIF($J$4:$J$5000, B295, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F295" s="92">
+      <c r="F295" s="91">
         <f t="shared" ref="F295:F302" si="23">SUMIF($O$4:$O$5000, B295, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G295" s="92">
+      <c r="G295" s="91">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E295-F295</f>
         <v>50</v>
       </c>
@@ -12779,22 +12776,22 @@
       </c>
     </row>
     <row r="296" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B296" s="91" t="s">
+      <c r="B296" s="90" t="s">
         <v>598</v>
       </c>
-      <c r="C296" s="91"/>
-      <c r="D296" s="93" t="s">
+      <c r="C296" s="90"/>
+      <c r="D296" s="92" t="s">
         <v>599</v>
       </c>
-      <c r="E296" s="92">
+      <c r="E296" s="91">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F296" s="92">
+      <c r="F296" s="91">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G296" s="94">
+      <c r="G296" s="93">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E296-F296</f>
         <v>91</v>
       </c>
@@ -12808,22 +12805,22 @@
       </c>
     </row>
     <row r="297" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B297" s="95" t="s">
+      <c r="B297" s="94" t="s">
         <v>610</v>
       </c>
-      <c r="C297" s="95"/>
-      <c r="D297" s="96" t="s">
+      <c r="C297" s="94"/>
+      <c r="D297" s="95" t="s">
         <v>611</v>
       </c>
-      <c r="E297" s="97">
+      <c r="E297" s="96">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F297" s="97">
+      <c r="F297" s="96">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G297" s="98">
+      <c r="G297" s="97">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E297-F297</f>
         <v>8</v>
       </c>
@@ -12837,24 +12834,24 @@
       </c>
     </row>
     <row r="298" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B298" s="95" t="s">
+      <c r="B298" s="94" t="s">
         <v>612</v>
       </c>
-      <c r="C298" s="95" t="s">
+      <c r="C298" s="94" t="s">
         <v>613</v>
       </c>
-      <c r="D298" s="96" t="s">
+      <c r="D298" s="95" t="s">
         <v>614</v>
       </c>
-      <c r="E298" s="97">
+      <c r="E298" s="96">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F298" s="97">
+      <c r="F298" s="96">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G298" s="98">
+      <c r="G298" s="97">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E298-F298</f>
         <v>35</v>
       </c>
@@ -12868,22 +12865,22 @@
       </c>
     </row>
     <row r="299" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B299" s="95" t="s">
+      <c r="B299" s="94" t="s">
         <v>615</v>
       </c>
-      <c r="C299" s="95"/>
-      <c r="D299" s="96" t="s">
+      <c r="C299" s="94"/>
+      <c r="D299" s="95" t="s">
         <v>616</v>
       </c>
-      <c r="E299" s="97">
+      <c r="E299" s="96">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F299" s="97">
+      <c r="F299" s="96">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G299" s="98">
+      <c r="G299" s="97">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E299-F299</f>
         <v>192</v>
       </c>
@@ -12897,22 +12894,22 @@
       </c>
     </row>
     <row r="300" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B300" s="95">
+      <c r="B300" s="94">
         <v>41040</v>
       </c>
-      <c r="C300" s="95"/>
-      <c r="D300" s="96" t="s">
+      <c r="C300" s="94"/>
+      <c r="D300" s="95" t="s">
         <v>590</v>
       </c>
-      <c r="E300" s="97">
+      <c r="E300" s="96">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F300" s="97">
+      <c r="F300" s="96">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G300" s="98">
+      <c r="G300" s="97">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E300-F300</f>
         <v>100</v>
       </c>
@@ -12926,22 +12923,22 @@
       </c>
     </row>
     <row r="301" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B301" s="95" t="s">
+      <c r="B301" s="94" t="s">
         <v>617</v>
       </c>
-      <c r="C301" s="95"/>
-      <c r="D301" s="96" t="s">
+      <c r="C301" s="94"/>
+      <c r="D301" s="95" t="s">
         <v>618</v>
       </c>
-      <c r="E301" s="97">
+      <c r="E301" s="96">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F301" s="97">
+      <c r="F301" s="96">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G301" s="98">
+      <c r="G301" s="97">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E301-F301</f>
         <v>15</v>
       </c>
@@ -12955,22 +12952,22 @@
       </c>
     </row>
     <row r="302" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B302" s="79" t="s">
+      <c r="B302" s="78" t="s">
         <v>619</v>
       </c>
-      <c r="C302" s="95"/>
-      <c r="D302" s="96" t="s">
+      <c r="C302" s="94"/>
+      <c r="D302" s="95" t="s">
         <v>585</v>
       </c>
-      <c r="E302" s="97">
+      <c r="E302" s="96">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F302" s="97">
+      <c r="F302" s="96">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G302" s="98">
+      <c r="G302" s="97">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E302-F302</f>
         <v>1</v>
       </c>
@@ -12984,22 +12981,22 @@
       </c>
     </row>
     <row r="303" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B303" s="95">
+      <c r="B303" s="94">
         <v>8003</v>
       </c>
-      <c r="C303" s="95"/>
-      <c r="D303" s="96" t="s">
+      <c r="C303" s="94"/>
+      <c r="D303" s="95" t="s">
         <v>623</v>
       </c>
-      <c r="E303" s="97">
+      <c r="E303" s="96">
         <f>SUMIF($J$4:$J$5000, B303, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F303" s="97">
+      <c r="F303" s="96">
         <f>SUMIF($O$4:$O$5000, B303, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G303" s="98">
+      <c r="G303" s="97">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E303-F303</f>
         <v>20</v>
       </c>
@@ -13013,10 +13010,10 @@
       </c>
     </row>
     <row r="304" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="D304" s="72"/>
-      <c r="E304" s="72"/>
-      <c r="F304" s="72"/>
-      <c r="G304" s="72"/>
+      <c r="D304" s="71"/>
+      <c r="E304" s="71"/>
+      <c r="F304" s="71"/>
+      <c r="G304" s="71"/>
       <c r="J304" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -15052,28 +15049,28 @@
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="103"/>
+      <c r="B2" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="102"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="101" t="s">
+      <c r="I2" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="103"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="102"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="101" t="s">
+      <c r="N2" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="102"/>
-      <c r="P2" s="102"/>
-      <c r="Q2" s="103"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="102"/>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">

--- a/INVENTARIO_AMPERIAL_2026.xlsx
+++ b/INVENTARIO_AMPERIAL_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Amperial Website\AmperialWebsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA593B7-4CDC-4D9F-ACB1-C8BED8AC9EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7C9522-A676-4A78-A384-4B47D353DE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1905" yWindow="1905" windowWidth="11520" windowHeight="7995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2450,7 +2450,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2523,9 +2523,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -2622,9 +2619,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2733,6 +2727,15 @@
     <xf numFmtId="0" fontId="9" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="15" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="15" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2744,13 +2747,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="15" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="15" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="15" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3281,31 +3278,31 @@
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
+      <c r="B2" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
       <c r="H2" s="1"/>
-      <c r="J2" s="98" t="s">
+      <c r="J2" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="O2" s="98" t="s">
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="O2" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
-      <c r="R2" s="98"/>
-      <c r="T2" s="56" t="s">
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
+      <c r="R2" s="99"/>
+      <c r="T2" s="55" t="s">
         <v>574</v>
       </c>
-      <c r="U2" s="56" t="s">
+      <c r="U2" s="55" t="s">
         <v>573</v>
       </c>
     </row>
@@ -3320,70 +3317,70 @@
       <c r="D3" s="23" t="s">
         <v>568</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="63" t="s">
+      <c r="H3" s="61" t="s">
         <v>578</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="34" t="s">
+      <c r="J3" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="35" t="s">
+      <c r="K3" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="35" t="s">
+      <c r="L3" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="36" t="s">
+      <c r="M3" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="32"/>
-      <c r="O3" s="34" t="s">
+      <c r="N3" s="31"/>
+      <c r="O3" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="35" t="s">
+      <c r="P3" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="Q3" s="35" t="s">
+      <c r="Q3" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="R3" s="36" t="s">
+      <c r="R3" s="35" t="s">
         <v>9</v>
       </c>
       <c r="S3" s="1"/>
-      <c r="T3" s="50" t="s">
+      <c r="T3" s="49" t="s">
         <v>570</v>
       </c>
-      <c r="U3" s="51"/>
+      <c r="U3" s="50"/>
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="104" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="39">
-        <v>0</v>
-      </c>
-      <c r="E4" s="38">
+      <c r="D4" s="38">
+        <v>0</v>
+      </c>
+      <c r="E4" s="37">
         <f t="shared" ref="E4:E68" si="0">SUMIF($J$4:$J$5000, B4, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="38">
+      <c r="F4" s="37">
         <f t="shared" ref="F4:F68" si="1">SUMIF($O$4:$O$5000, B4, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="37">
+      <c r="G4" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E4-F4</f>
         <v>0</v>
       </c>
@@ -3417,31 +3414,31 @@
         <v>210</v>
       </c>
       <c r="S4" s="1"/>
-      <c r="T4" s="50" t="s">
+      <c r="T4" s="49" t="s">
         <v>571</v>
       </c>
-      <c r="U4" s="77"/>
+      <c r="U4" s="75"/>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="26" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="40">
-        <v>0</v>
-      </c>
-      <c r="E5" s="38">
+      <c r="D5" s="39">
+        <v>0</v>
+      </c>
+      <c r="E5" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F5" s="38">
+      <c r="F5" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G5" s="37">
+      <c r="G5" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E5-F5</f>
         <v>0</v>
       </c>
@@ -3475,29 +3472,29 @@
         <v>125</v>
       </c>
       <c r="S5" s="1"/>
-      <c r="T5" s="50" t="s">
+      <c r="T5" s="49" t="s">
         <v>572</v>
       </c>
-      <c r="U5" s="52"/>
+      <c r="U5" s="51"/>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="26" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="41"/>
-      <c r="E6" s="38">
+      <c r="D6" s="40"/>
+      <c r="E6" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G6" s="37">
+      <c r="G6" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E6-F6</f>
         <v>0</v>
       </c>
@@ -3525,29 +3522,29 @@
         <v>28</v>
       </c>
       <c r="S6" s="1"/>
-      <c r="T6" s="53" t="s">
+      <c r="T6" s="52" t="s">
         <v>577</v>
       </c>
-      <c r="U6" s="54"/>
+      <c r="U6" s="53"/>
     </row>
     <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="26" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="41"/>
-      <c r="E7" s="38">
+      <c r="D7" s="40"/>
+      <c r="E7" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E7-F7</f>
         <v>0</v>
       </c>
@@ -3575,27 +3572,27 @@
         <v>20</v>
       </c>
       <c r="S7" s="1"/>
-      <c r="T7" s="55"/>
-      <c r="U7" s="55"/>
+      <c r="T7" s="54"/>
+      <c r="U7" s="54"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="26" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="41"/>
-      <c r="E8" s="38">
+      <c r="D8" s="40"/>
+      <c r="E8" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="38">
+      <c r="F8" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E8-F8</f>
         <v>0</v>
       </c>
@@ -3626,22 +3623,22 @@
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="26" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="41"/>
-      <c r="E9" s="38">
+      <c r="D9" s="40"/>
+      <c r="E9" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F9" s="38">
+      <c r="F9" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E9-F9</f>
         <v>0</v>
       </c>
@@ -3661,22 +3658,22 @@
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="26" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="38">
+      <c r="D10" s="40"/>
+      <c r="E10" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="38">
+      <c r="F10" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E10-F10</f>
         <v>0</v>
       </c>
@@ -3701,22 +3698,22 @@
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="26" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="38">
+      <c r="D11" s="40"/>
+      <c r="E11" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E11-F11</f>
         <v>0</v>
       </c>
@@ -3741,22 +3738,22 @@
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="96" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="41"/>
-      <c r="E12" s="38">
+      <c r="D12" s="40"/>
+      <c r="E12" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G12" s="37">
+      <c r="G12" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E12-F12</f>
         <v>0</v>
       </c>
@@ -3781,22 +3778,22 @@
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="78" t="s">
+      <c r="B13" s="76" t="s">
         <v>608</v>
       </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79" t="s">
+      <c r="C13" s="77"/>
+      <c r="D13" s="77" t="s">
         <v>609</v>
       </c>
-      <c r="E13" s="81">
+      <c r="E13" s="79">
         <f>SUMIF($J$4:$J$5000, B13, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="81">
+      <c r="F13" s="79">
         <f>SUMIF($O$4:$O$5000, B13, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="82">
+      <c r="G13" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E13-F13</f>
         <v>75</v>
       </c>
@@ -3821,24 +3818,24 @@
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="79" t="s">
+      <c r="C14" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="80">
+      <c r="D14" s="78">
         <v>20</v>
       </c>
-      <c r="E14" s="81">
+      <c r="E14" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F14" s="81">
+      <c r="F14" s="79">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G14" s="82">
+      <c r="G14" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E14-F14</f>
         <v>20</v>
       </c>
@@ -3863,22 +3860,22 @@
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="26" t="s">
         <v>32</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="41"/>
-      <c r="E15" s="38">
+      <c r="D15" s="40"/>
+      <c r="E15" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E15-F15</f>
         <v>0</v>
       </c>
@@ -3903,22 +3900,22 @@
     </row>
     <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="26" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="41"/>
-      <c r="E16" s="38">
+      <c r="D16" s="40"/>
+      <c r="E16" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E16-F16</f>
         <v>0</v>
       </c>
@@ -3942,22 +3939,22 @@
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="26" t="s">
         <v>36</v>
       </c>
       <c r="C17" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="38">
+      <c r="D17" s="40"/>
+      <c r="E17" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E17-F17</f>
         <v>0</v>
       </c>
@@ -3978,22 +3975,22 @@
       <c r="R17" s="11"/>
     </row>
     <row r="18" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="26" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="38">
+      <c r="D18" s="40"/>
+      <c r="E18" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F18" s="38">
+      <c r="F18" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G18" s="37">
+      <c r="G18" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E18-F18</f>
         <v>0</v>
       </c>
@@ -4013,22 +4010,22 @@
       <c r="R18" s="14"/>
     </row>
     <row r="19" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="38">
+      <c r="D19" s="40"/>
+      <c r="E19" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F19" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E19-F19</f>
         <v>0</v>
       </c>
@@ -4048,24 +4045,24 @@
       <c r="R19" s="11"/>
     </row>
     <row r="20" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="72" t="s">
+      <c r="B20" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="73" t="s">
+      <c r="C20" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="74">
+      <c r="D20" s="72">
         <v>4</v>
       </c>
-      <c r="E20" s="75">
+      <c r="E20" s="73">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F20" s="75">
+      <c r="F20" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="76">
+      <c r="G20" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E20-F20</f>
         <v>4</v>
       </c>
@@ -4085,22 +4082,22 @@
       <c r="R20" s="14"/>
     </row>
     <row r="21" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="41"/>
-      <c r="E21" s="38">
+      <c r="D21" s="40"/>
+      <c r="E21" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F21" s="38">
+      <c r="F21" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G21" s="37">
+      <c r="G21" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E21-F21</f>
         <v>0</v>
       </c>
@@ -4120,22 +4117,22 @@
       <c r="R21" s="11"/>
     </row>
     <row r="22" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="41"/>
-      <c r="E22" s="38">
+      <c r="D22" s="40"/>
+      <c r="E22" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G22" s="37">
+      <c r="G22" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E22-F22</f>
         <v>0</v>
       </c>
@@ -4155,22 +4152,22 @@
       <c r="R22" s="14"/>
     </row>
     <row r="23" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C23" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="41"/>
-      <c r="E23" s="38">
+      <c r="D23" s="40"/>
+      <c r="E23" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F23" s="38">
+      <c r="F23" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G23" s="37">
+      <c r="G23" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E23-F23</f>
         <v>0</v>
       </c>
@@ -4190,22 +4187,22 @@
       <c r="R23" s="11"/>
     </row>
     <row r="24" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C24" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="41"/>
-      <c r="E24" s="38">
+      <c r="D24" s="40"/>
+      <c r="E24" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F24" s="38">
+      <c r="F24" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G24" s="37">
+      <c r="G24" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E24-F24</f>
         <v>0</v>
       </c>
@@ -4225,22 +4222,22 @@
       <c r="R24" s="14"/>
     </row>
     <row r="25" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C25" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="41"/>
-      <c r="E25" s="38">
+      <c r="D25" s="40"/>
+      <c r="E25" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F25" s="38">
+      <c r="F25" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G25" s="37">
+      <c r="G25" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E25-F25</f>
         <v>0</v>
       </c>
@@ -4260,22 +4257,22 @@
       <c r="R25" s="11"/>
     </row>
     <row r="26" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="26" t="s">
         <v>54</v>
       </c>
       <c r="C26" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="41"/>
-      <c r="E26" s="38">
+      <c r="D26" s="40"/>
+      <c r="E26" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F26" s="38">
+      <c r="F26" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G26" s="37">
+      <c r="G26" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E26-F26</f>
         <v>0</v>
       </c>
@@ -4295,22 +4292,22 @@
       <c r="R26" s="14"/>
     </row>
     <row r="27" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C27" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="41"/>
-      <c r="E27" s="38">
+      <c r="D27" s="40"/>
+      <c r="E27" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F27" s="38">
+      <c r="F27" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G27" s="37">
+      <c r="G27" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E27-F27</f>
         <v>0</v>
       </c>
@@ -4330,22 +4327,22 @@
       <c r="R27" s="11"/>
     </row>
     <row r="28" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C28" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="41"/>
-      <c r="E28" s="38">
+      <c r="D28" s="40"/>
+      <c r="E28" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F28" s="38">
+      <c r="F28" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G28" s="37">
+      <c r="G28" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E28-F28</f>
         <v>0</v>
       </c>
@@ -4365,22 +4362,22 @@
       <c r="R28" s="14"/>
     </row>
     <row r="29" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C29" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="41"/>
-      <c r="E29" s="38">
+      <c r="D29" s="40"/>
+      <c r="E29" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F29" s="38">
+      <c r="F29" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G29" s="37">
+      <c r="G29" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E29-F29</f>
         <v>0</v>
       </c>
@@ -4400,24 +4397,24 @@
       <c r="R29" s="11"/>
     </row>
     <row r="30" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="78" t="s">
+      <c r="B30" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="79" t="s">
+      <c r="C30" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="80">
+      <c r="D30" s="78">
         <v>10</v>
       </c>
-      <c r="E30" s="81">
+      <c r="E30" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F30" s="81">
+      <c r="F30" s="79">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G30" s="82">
+      <c r="G30" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E30-F30</f>
         <v>10</v>
       </c>
@@ -4437,24 +4434,24 @@
       <c r="R30" s="14"/>
     </row>
     <row r="31" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="78" t="s">
+      <c r="B31" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="79" t="s">
+      <c r="C31" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="80">
+      <c r="D31" s="78">
         <v>20</v>
       </c>
-      <c r="E31" s="81">
+      <c r="E31" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F31" s="81">
+      <c r="F31" s="79">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G31" s="82">
+      <c r="G31" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E31-F31</f>
         <v>20</v>
       </c>
@@ -4474,22 +4471,22 @@
       <c r="R31" s="11"/>
     </row>
     <row r="32" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="26" t="s">
         <v>65</v>
       </c>
       <c r="C32" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="38">
+      <c r="D32" s="40"/>
+      <c r="E32" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F32" s="38">
+      <c r="F32" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G32" s="37">
+      <c r="G32" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E32-F32</f>
         <v>0</v>
       </c>
@@ -4509,22 +4506,22 @@
       <c r="R32" s="14"/>
     </row>
     <row r="33" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="26" t="s">
         <v>67</v>
       </c>
       <c r="C33" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="D33" s="41"/>
-      <c r="E33" s="38">
+      <c r="D33" s="40"/>
+      <c r="E33" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F33" s="38">
+      <c r="F33" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G33" s="37">
+      <c r="G33" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E33-F33</f>
         <v>0</v>
       </c>
@@ -4544,22 +4541,22 @@
       <c r="R33" s="11"/>
     </row>
     <row r="34" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="26" t="s">
         <v>69</v>
       </c>
       <c r="C34" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="41"/>
-      <c r="E34" s="38">
+      <c r="D34" s="40"/>
+      <c r="E34" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F34" s="38">
+      <c r="F34" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G34" s="37">
+      <c r="G34" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E34-F34</f>
         <v>0</v>
       </c>
@@ -4579,22 +4576,22 @@
       <c r="R34" s="14"/>
     </row>
     <row r="35" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="26" t="s">
         <v>71</v>
       </c>
       <c r="C35" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="41"/>
-      <c r="E35" s="38">
+      <c r="D35" s="40"/>
+      <c r="E35" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F35" s="38">
+      <c r="F35" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G35" s="37">
+      <c r="G35" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E35-F35</f>
         <v>0</v>
       </c>
@@ -4614,22 +4611,22 @@
       <c r="R35" s="11"/>
     </row>
     <row r="36" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="26" t="s">
         <v>73</v>
       </c>
       <c r="C36" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="41"/>
-      <c r="E36" s="38">
+      <c r="D36" s="40"/>
+      <c r="E36" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F36" s="38">
+      <c r="F36" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G36" s="37">
+      <c r="G36" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E36-F36</f>
         <v>0</v>
       </c>
@@ -4649,22 +4646,22 @@
       <c r="R36" s="14"/>
     </row>
     <row r="37" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="26" t="s">
         <v>75</v>
       </c>
       <c r="C37" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="41"/>
-      <c r="E37" s="38">
+      <c r="D37" s="40"/>
+      <c r="E37" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F37" s="38">
+      <c r="F37" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G37" s="37">
+      <c r="G37" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E37-F37</f>
         <v>0</v>
       </c>
@@ -4684,22 +4681,22 @@
       <c r="R37" s="11"/>
     </row>
     <row r="38" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="26" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="41"/>
-      <c r="E38" s="38">
+      <c r="D38" s="40"/>
+      <c r="E38" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F38" s="38">
+      <c r="F38" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G38" s="37">
+      <c r="G38" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E38-F38</f>
         <v>0</v>
       </c>
@@ -4719,22 +4716,22 @@
       <c r="R38" s="14"/>
     </row>
     <row r="39" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="26" t="s">
         <v>79</v>
       </c>
       <c r="C39" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="41"/>
-      <c r="E39" s="38">
+      <c r="D39" s="40"/>
+      <c r="E39" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F39" s="38">
+      <c r="F39" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G39" s="37">
+      <c r="G39" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E39-F39</f>
         <v>0</v>
       </c>
@@ -4754,22 +4751,22 @@
       <c r="R39" s="11"/>
     </row>
     <row r="40" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="26" t="s">
         <v>81</v>
       </c>
       <c r="C40" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="41"/>
-      <c r="E40" s="38">
+      <c r="D40" s="40"/>
+      <c r="E40" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F40" s="38">
+      <c r="F40" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G40" s="37">
+      <c r="G40" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E40-F40</f>
         <v>0</v>
       </c>
@@ -4789,22 +4786,22 @@
       <c r="R40" s="14"/>
     </row>
     <row r="41" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="26" t="s">
         <v>83</v>
       </c>
       <c r="C41" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="D41" s="41"/>
-      <c r="E41" s="38">
+      <c r="D41" s="40"/>
+      <c r="E41" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F41" s="38">
+      <c r="F41" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G41" s="37">
+      <c r="G41" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E41-F41</f>
         <v>0</v>
       </c>
@@ -4824,22 +4821,22 @@
       <c r="R41" s="11"/>
     </row>
     <row r="42" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="27" t="s">
+      <c r="B42" s="26" t="s">
         <v>85</v>
       </c>
       <c r="C42" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="D42" s="41"/>
-      <c r="E42" s="38">
+      <c r="D42" s="40"/>
+      <c r="E42" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F42" s="38">
+      <c r="F42" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G42" s="37">
+      <c r="G42" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E42-F42</f>
         <v>0</v>
       </c>
@@ -4859,22 +4856,22 @@
       <c r="R42" s="14"/>
     </row>
     <row r="43" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="26" t="s">
         <v>87</v>
       </c>
       <c r="C43" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="41"/>
-      <c r="E43" s="38">
+      <c r="D43" s="40"/>
+      <c r="E43" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F43" s="38">
+      <c r="F43" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G43" s="37">
+      <c r="G43" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E43-F43</f>
         <v>0</v>
       </c>
@@ -4894,22 +4891,22 @@
       <c r="R43" s="11"/>
     </row>
     <row r="44" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="26" t="s">
         <v>89</v>
       </c>
       <c r="C44" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="41"/>
-      <c r="E44" s="38">
+      <c r="D44" s="40"/>
+      <c r="E44" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F44" s="38">
+      <c r="F44" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G44" s="37">
+      <c r="G44" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E44-F44</f>
         <v>0</v>
       </c>
@@ -4929,22 +4926,22 @@
       <c r="R44" s="14"/>
     </row>
     <row r="45" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="26" t="s">
         <v>91</v>
       </c>
       <c r="C45" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="D45" s="41"/>
-      <c r="E45" s="38">
+      <c r="D45" s="40"/>
+      <c r="E45" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F45" s="38">
+      <c r="F45" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G45" s="37">
+      <c r="G45" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E45-F45</f>
         <v>0</v>
       </c>
@@ -4964,22 +4961,22 @@
       <c r="R45" s="11"/>
     </row>
     <row r="46" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="27" t="s">
+      <c r="B46" s="26" t="s">
         <v>93</v>
       </c>
       <c r="C46" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="D46" s="41"/>
-      <c r="E46" s="38">
+      <c r="D46" s="40"/>
+      <c r="E46" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F46" s="38">
+      <c r="F46" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G46" s="37">
+      <c r="G46" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E46-F46</f>
         <v>0</v>
       </c>
@@ -4999,22 +4996,22 @@
       <c r="R46" s="14"/>
     </row>
     <row r="47" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="26" t="s">
         <v>95</v>
       </c>
       <c r="C47" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D47" s="41"/>
-      <c r="E47" s="38">
+      <c r="D47" s="40"/>
+      <c r="E47" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F47" s="38">
+      <c r="F47" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G47" s="37">
+      <c r="G47" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E47-F47</f>
         <v>0</v>
       </c>
@@ -5034,22 +5031,22 @@
       <c r="R47" s="11"/>
     </row>
     <row r="48" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="26" t="s">
         <v>97</v>
       </c>
       <c r="C48" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="D48" s="41"/>
-      <c r="E48" s="38">
+      <c r="D48" s="40"/>
+      <c r="E48" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F48" s="38">
+      <c r="F48" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G48" s="37">
+      <c r="G48" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E48-F48</f>
         <v>0</v>
       </c>
@@ -5069,22 +5066,22 @@
       <c r="R48" s="14"/>
     </row>
     <row r="49" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="26" t="s">
         <v>99</v>
       </c>
       <c r="C49" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="D49" s="41"/>
-      <c r="E49" s="38">
+      <c r="D49" s="40"/>
+      <c r="E49" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F49" s="38">
+      <c r="F49" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G49" s="37">
+      <c r="G49" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E49-F49</f>
         <v>0</v>
       </c>
@@ -5104,22 +5101,22 @@
       <c r="R49" s="11"/>
     </row>
     <row r="50" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="26" t="s">
         <v>101</v>
       </c>
       <c r="C50" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="D50" s="41"/>
-      <c r="E50" s="38">
+      <c r="D50" s="40"/>
+      <c r="E50" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F50" s="38">
+      <c r="F50" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G50" s="37">
+      <c r="G50" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E50-F50</f>
         <v>0</v>
       </c>
@@ -5139,22 +5136,22 @@
       <c r="R50" s="14"/>
     </row>
     <row r="51" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="26" t="s">
         <v>103</v>
       </c>
       <c r="C51" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="D51" s="41"/>
-      <c r="E51" s="38">
+      <c r="D51" s="40"/>
+      <c r="E51" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F51" s="38">
+      <c r="F51" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G51" s="37">
+      <c r="G51" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E51-F51</f>
         <v>0</v>
       </c>
@@ -5174,22 +5171,22 @@
       <c r="R51" s="11"/>
     </row>
     <row r="52" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="27" t="s">
+      <c r="B52" s="26" t="s">
         <v>105</v>
       </c>
       <c r="C52" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="D52" s="41"/>
-      <c r="E52" s="38">
+      <c r="D52" s="40"/>
+      <c r="E52" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F52" s="38">
+      <c r="F52" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G52" s="37">
+      <c r="G52" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E52-F52</f>
         <v>0</v>
       </c>
@@ -5209,22 +5206,22 @@
       <c r="R52" s="14"/>
     </row>
     <row r="53" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="26" t="s">
         <v>107</v>
       </c>
       <c r="C53" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="D53" s="41"/>
-      <c r="E53" s="38">
+      <c r="D53" s="40"/>
+      <c r="E53" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F53" s="38">
+      <c r="F53" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G53" s="37">
+      <c r="G53" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E53-F53</f>
         <v>0</v>
       </c>
@@ -5244,22 +5241,22 @@
       <c r="R53" s="11"/>
     </row>
     <row r="54" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="26" t="s">
         <v>109</v>
       </c>
       <c r="C54" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="D54" s="41"/>
-      <c r="E54" s="38">
+      <c r="D54" s="40"/>
+      <c r="E54" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F54" s="38">
+      <c r="F54" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G54" s="37">
+      <c r="G54" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E54-F54</f>
         <v>0</v>
       </c>
@@ -5279,24 +5276,24 @@
       <c r="R54" s="14"/>
     </row>
     <row r="55" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="78" t="s">
+      <c r="B55" s="76" t="s">
         <v>111</v>
       </c>
-      <c r="C55" s="79" t="s">
+      <c r="C55" s="77" t="s">
         <v>112</v>
       </c>
-      <c r="D55" s="80">
+      <c r="D55" s="78">
         <v>64</v>
       </c>
-      <c r="E55" s="81">
+      <c r="E55" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F55" s="81">
+      <c r="F55" s="79">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G55" s="82">
+      <c r="G55" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E55-F55</f>
         <v>64</v>
       </c>
@@ -5316,22 +5313,22 @@
       <c r="R55" s="11"/>
     </row>
     <row r="56" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="27" t="s">
+      <c r="B56" s="26" t="s">
         <v>113</v>
       </c>
       <c r="C56" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="D56" s="41"/>
-      <c r="E56" s="38">
+      <c r="D56" s="40"/>
+      <c r="E56" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F56" s="38">
+      <c r="F56" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G56" s="37">
+      <c r="G56" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E56-F56</f>
         <v>0</v>
       </c>
@@ -5351,22 +5348,22 @@
       <c r="R56" s="14"/>
     </row>
     <row r="57" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="26" t="s">
         <v>115</v>
       </c>
       <c r="C57" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="D57" s="41"/>
-      <c r="E57" s="38">
+      <c r="D57" s="40"/>
+      <c r="E57" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F57" s="38">
+      <c r="F57" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G57" s="37">
+      <c r="G57" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E57-F57</f>
         <v>0</v>
       </c>
@@ -5386,22 +5383,22 @@
       <c r="R57" s="11"/>
     </row>
     <row r="58" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="26" t="s">
         <v>117</v>
       </c>
       <c r="C58" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="D58" s="41"/>
-      <c r="E58" s="38">
+      <c r="D58" s="40"/>
+      <c r="E58" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F58" s="38">
+      <c r="F58" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G58" s="37">
+      <c r="G58" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E58-F58</f>
         <v>0</v>
       </c>
@@ -5421,22 +5418,22 @@
       <c r="R58" s="14"/>
     </row>
     <row r="59" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="26" t="s">
         <v>119</v>
       </c>
       <c r="C59" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="D59" s="41"/>
-      <c r="E59" s="38">
+      <c r="D59" s="40"/>
+      <c r="E59" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F59" s="38">
+      <c r="F59" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G59" s="37">
+      <c r="G59" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E59-F59</f>
         <v>0</v>
       </c>
@@ -5456,22 +5453,22 @@
       <c r="R59" s="11"/>
     </row>
     <row r="60" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="27" t="s">
+      <c r="B60" s="26" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="D60" s="41"/>
-      <c r="E60" s="38">
+      <c r="D60" s="40"/>
+      <c r="E60" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F60" s="38">
+      <c r="F60" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G60" s="37">
+      <c r="G60" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E60-F60</f>
         <v>0</v>
       </c>
@@ -5491,22 +5488,22 @@
       <c r="R60" s="14"/>
     </row>
     <row r="61" spans="2:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="27" t="s">
+      <c r="B61" s="26" t="s">
         <v>123</v>
       </c>
       <c r="C61" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="D61" s="41"/>
-      <c r="E61" s="38">
+      <c r="D61" s="40"/>
+      <c r="E61" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F61" s="38">
+      <c r="F61" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G61" s="37">
+      <c r="G61" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E61-F61</f>
         <v>0</v>
       </c>
@@ -5526,22 +5523,22 @@
       <c r="R61" s="11"/>
     </row>
     <row r="62" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="27" t="s">
+      <c r="B62" s="26" t="s">
         <v>125</v>
       </c>
       <c r="C62" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="D62" s="41"/>
-      <c r="E62" s="38">
+      <c r="D62" s="40"/>
+      <c r="E62" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F62" s="38">
+      <c r="F62" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G62" s="37">
+      <c r="G62" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E62-F62</f>
         <v>0</v>
       </c>
@@ -5561,22 +5558,22 @@
       <c r="R62" s="14"/>
     </row>
     <row r="63" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="27" t="s">
+      <c r="B63" s="26" t="s">
         <v>127</v>
       </c>
       <c r="C63" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="D63" s="41"/>
-      <c r="E63" s="38">
+      <c r="D63" s="40"/>
+      <c r="E63" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F63" s="38">
+      <c r="F63" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G63" s="37">
+      <c r="G63" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E63-F63</f>
         <v>0</v>
       </c>
@@ -5596,22 +5593,22 @@
       <c r="R63" s="11"/>
     </row>
     <row r="64" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="27" t="s">
+      <c r="B64" s="26" t="s">
         <v>129</v>
       </c>
       <c r="C64" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="D64" s="41"/>
-      <c r="E64" s="38">
+      <c r="D64" s="40"/>
+      <c r="E64" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F64" s="38">
+      <c r="F64" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G64" s="37">
+      <c r="G64" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E64-F64</f>
         <v>0</v>
       </c>
@@ -5631,22 +5628,22 @@
       <c r="R64" s="14"/>
     </row>
     <row r="65" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="27" t="s">
+      <c r="B65" s="26" t="s">
         <v>131</v>
       </c>
       <c r="C65" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="D65" s="41"/>
-      <c r="E65" s="38">
+      <c r="D65" s="40"/>
+      <c r="E65" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F65" s="38">
+      <c r="F65" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G65" s="37">
+      <c r="G65" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E65-F65</f>
         <v>0</v>
       </c>
@@ -5666,22 +5663,22 @@
       <c r="R65" s="11"/>
     </row>
     <row r="66" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="27" t="s">
+      <c r="B66" s="26" t="s">
         <v>133</v>
       </c>
       <c r="C66" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="D66" s="41"/>
-      <c r="E66" s="38">
+      <c r="D66" s="40"/>
+      <c r="E66" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F66" s="38">
+      <c r="F66" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G66" s="37">
+      <c r="G66" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E66-F66</f>
         <v>0</v>
       </c>
@@ -5701,24 +5698,24 @@
       <c r="R66" s="14"/>
     </row>
     <row r="67" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="72" t="s">
+      <c r="B67" s="70" t="s">
         <v>600</v>
       </c>
-      <c r="C67" s="73" t="s">
+      <c r="C67" s="71" t="s">
         <v>136</v>
       </c>
-      <c r="D67" s="74">
+      <c r="D67" s="72">
         <v>8</v>
       </c>
-      <c r="E67" s="75">
+      <c r="E67" s="73">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F67" s="75">
+      <c r="F67" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G67" s="76">
+      <c r="G67" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E67-F67</f>
         <v>8</v>
       </c>
@@ -5738,24 +5735,24 @@
       <c r="R67" s="11"/>
     </row>
     <row r="68" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="72" t="s">
+      <c r="B68" s="70" t="s">
         <v>601</v>
       </c>
-      <c r="C68" s="73" t="s">
+      <c r="C68" s="71" t="s">
         <v>138</v>
       </c>
-      <c r="D68" s="74">
+      <c r="D68" s="72">
         <v>3</v>
       </c>
-      <c r="E68" s="75">
+      <c r="E68" s="73">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F68" s="75">
+      <c r="F68" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G68" s="76">
+      <c r="G68" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E68-F68</f>
         <v>3</v>
       </c>
@@ -5775,22 +5772,22 @@
       <c r="R68" s="14"/>
     </row>
     <row r="69" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="27" t="s">
+      <c r="B69" s="26" t="s">
         <v>602</v>
       </c>
       <c r="C69" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="D69" s="41"/>
-      <c r="E69" s="38">
+      <c r="D69" s="40"/>
+      <c r="E69" s="37">
         <f t="shared" ref="E69:E132" si="5">SUMIF($J$4:$J$5000, B69, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F69" s="38">
+      <c r="F69" s="37">
         <f t="shared" ref="F69:F132" si="6">SUMIF($O$4:$O$5000, B69, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G69" s="37">
+      <c r="G69" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E69-F69</f>
         <v>0</v>
       </c>
@@ -5810,22 +5807,22 @@
       <c r="R69" s="11"/>
     </row>
     <row r="70" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="27" t="s">
+      <c r="B70" s="26" t="s">
         <v>603</v>
       </c>
       <c r="C70" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="D70" s="41"/>
-      <c r="E70" s="38">
+      <c r="D70" s="40"/>
+      <c r="E70" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F70" s="38">
+      <c r="F70" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G70" s="37">
+      <c r="G70" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E70-F70</f>
         <v>0</v>
       </c>
@@ -5845,22 +5842,22 @@
       <c r="R70" s="14"/>
     </row>
     <row r="71" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="27" t="s">
+      <c r="B71" s="26" t="s">
         <v>142</v>
       </c>
       <c r="C71" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="D71" s="41"/>
-      <c r="E71" s="38">
+      <c r="D71" s="40"/>
+      <c r="E71" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F71" s="38">
+      <c r="F71" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G71" s="37">
+      <c r="G71" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E71-F71</f>
         <v>0</v>
       </c>
@@ -5880,22 +5877,22 @@
       <c r="R71" s="11"/>
     </row>
     <row r="72" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="27" t="s">
+      <c r="B72" s="26" t="s">
         <v>144</v>
       </c>
       <c r="C72" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="D72" s="41"/>
-      <c r="E72" s="38">
+      <c r="D72" s="40"/>
+      <c r="E72" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F72" s="38">
+      <c r="F72" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G72" s="37">
+      <c r="G72" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E72-F72</f>
         <v>0</v>
       </c>
@@ -5915,22 +5912,22 @@
       <c r="R72" s="14"/>
     </row>
     <row r="73" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="27" t="s">
+      <c r="B73" s="26" t="s">
         <v>146</v>
       </c>
       <c r="C73" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="D73" s="41"/>
-      <c r="E73" s="38">
+      <c r="D73" s="40"/>
+      <c r="E73" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F73" s="38">
+      <c r="F73" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G73" s="37">
+      <c r="G73" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E73-F73</f>
         <v>0</v>
       </c>
@@ -5950,22 +5947,22 @@
       <c r="R73" s="11"/>
     </row>
     <row r="74" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="27" t="s">
+      <c r="B74" s="26" t="s">
         <v>148</v>
       </c>
       <c r="C74" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="D74" s="41"/>
-      <c r="E74" s="38">
+      <c r="D74" s="40"/>
+      <c r="E74" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F74" s="38">
+      <c r="F74" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G74" s="37">
+      <c r="G74" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E74-F74</f>
         <v>0</v>
       </c>
@@ -5985,22 +5982,22 @@
       <c r="R74" s="14"/>
     </row>
     <row r="75" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="27" t="s">
+      <c r="B75" s="26" t="s">
         <v>150</v>
       </c>
       <c r="C75" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="D75" s="41"/>
-      <c r="E75" s="38">
+      <c r="D75" s="40"/>
+      <c r="E75" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F75" s="38">
+      <c r="F75" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G75" s="37">
+      <c r="G75" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E75-F75</f>
         <v>0</v>
       </c>
@@ -6019,65 +6016,65 @@
       <c r="Q75" s="10"/>
       <c r="R75" s="11"/>
     </row>
-    <row r="76" spans="2:18" s="69" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="27" t="s">
+    <row r="76" spans="2:18" s="67" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="26" t="s">
         <v>152</v>
       </c>
       <c r="C76" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="D76" s="41"/>
-      <c r="E76" s="38">
+      <c r="D76" s="40"/>
+      <c r="E76" s="37">
         <f t="shared" si="5"/>
         <v>250</v>
       </c>
-      <c r="F76" s="38">
+      <c r="F76" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G76" s="37">
+      <c r="G76" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E76-F76</f>
         <v>250</v>
       </c>
       <c r="H76"/>
-      <c r="J76" s="86"/>
-      <c r="K76" s="83" t="str">
+      <c r="J76" s="84"/>
+      <c r="K76" s="81" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="L76" s="87"/>
-      <c r="M76" s="88"/>
-      <c r="O76" s="86"/>
-      <c r="P76" s="83" t="str">
+      <c r="L76" s="85"/>
+      <c r="M76" s="86"/>
+      <c r="O76" s="84"/>
+      <c r="P76" s="81" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q76" s="89"/>
-      <c r="R76" s="88"/>
+      <c r="Q76" s="87"/>
+      <c r="R76" s="86"/>
     </row>
     <row r="77" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="78" t="s">
+      <c r="B77" s="76" t="s">
         <v>154</v>
       </c>
-      <c r="C77" s="79" t="s">
+      <c r="C77" s="77" t="s">
         <v>155</v>
       </c>
-      <c r="D77" s="80">
+      <c r="D77" s="78">
         <v>900</v>
       </c>
-      <c r="E77" s="81">
+      <c r="E77" s="79">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F77" s="81">
+      <c r="F77" s="79">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G77" s="82">
+      <c r="G77" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E77-F77</f>
         <v>900</v>
       </c>
-      <c r="H77" s="69"/>
+      <c r="H77" s="67"/>
       <c r="J77" s="9"/>
       <c r="K77" s="19" t="str">
         <f t="shared" si="4"/>
@@ -6094,24 +6091,24 @@
       <c r="R77" s="11"/>
     </row>
     <row r="78" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="78" t="s">
+      <c r="B78" s="76" t="s">
         <v>156</v>
       </c>
-      <c r="C78" s="79" t="s">
+      <c r="C78" s="77" t="s">
         <v>157</v>
       </c>
-      <c r="D78" s="80">
+      <c r="D78" s="78">
         <v>132</v>
       </c>
-      <c r="E78" s="81">
+      <c r="E78" s="79">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F78" s="81">
+      <c r="F78" s="79">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G78" s="82">
+      <c r="G78" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E78-F78</f>
         <v>132</v>
       </c>
@@ -6131,22 +6128,22 @@
       <c r="R78" s="14"/>
     </row>
     <row r="79" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="27" t="s">
+      <c r="B79" s="26" t="s">
         <v>158</v>
       </c>
       <c r="C79" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="D79" s="41"/>
-      <c r="E79" s="38">
+      <c r="D79" s="40"/>
+      <c r="E79" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F79" s="38">
+      <c r="F79" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G79" s="37">
+      <c r="G79" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E79-F79</f>
         <v>0</v>
       </c>
@@ -6165,65 +6162,65 @@
       <c r="Q79" s="10"/>
       <c r="R79" s="11"/>
     </row>
-    <row r="80" spans="2:18" s="69" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="27" t="s">
+    <row r="80" spans="2:18" s="67" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="26" t="s">
         <v>160</v>
       </c>
       <c r="C80" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="D80" s="41"/>
-      <c r="E80" s="38">
+      <c r="D80" s="40"/>
+      <c r="E80" s="37">
         <f t="shared" si="5"/>
         <v>250</v>
       </c>
-      <c r="F80" s="38">
+      <c r="F80" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G80" s="37">
+      <c r="G80" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E80-F80</f>
         <v>250</v>
       </c>
       <c r="H80"/>
-      <c r="J80" s="86"/>
-      <c r="K80" s="83" t="str">
+      <c r="J80" s="84"/>
+      <c r="K80" s="81" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="L80" s="87"/>
-      <c r="M80" s="88"/>
-      <c r="O80" s="86"/>
-      <c r="P80" s="83" t="str">
+      <c r="L80" s="85"/>
+      <c r="M80" s="86"/>
+      <c r="O80" s="84"/>
+      <c r="P80" s="81" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q80" s="89"/>
-      <c r="R80" s="88"/>
+      <c r="Q80" s="87"/>
+      <c r="R80" s="86"/>
     </row>
     <row r="81" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="78" t="s">
+      <c r="B81" s="76" t="s">
         <v>162</v>
       </c>
-      <c r="C81" s="79" t="s">
+      <c r="C81" s="77" t="s">
         <v>163</v>
       </c>
-      <c r="D81" s="80">
+      <c r="D81" s="78">
         <v>1000</v>
       </c>
-      <c r="E81" s="81">
+      <c r="E81" s="79">
         <f>SUMIF($J$4:$J$5000, B81, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F81" s="81">
+      <c r="F81" s="79">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G81" s="82">
+      <c r="G81" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E81-F81</f>
         <v>1000</v>
       </c>
-      <c r="H81" s="69"/>
+      <c r="H81" s="67"/>
       <c r="J81" s="9"/>
       <c r="K81" s="19" t="str">
         <f t="shared" si="4"/>
@@ -6240,22 +6237,22 @@
       <c r="R81" s="11"/>
     </row>
     <row r="82" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="27" t="s">
+      <c r="B82" s="26" t="s">
         <v>164</v>
       </c>
       <c r="C82" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="D82" s="41"/>
-      <c r="E82" s="38">
+      <c r="D82" s="40"/>
+      <c r="E82" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F82" s="38">
+      <c r="F82" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G82" s="37">
+      <c r="G82" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E82-F82</f>
         <v>0</v>
       </c>
@@ -6275,22 +6272,22 @@
       <c r="R82" s="12"/>
     </row>
     <row r="83" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="27" t="s">
+      <c r="B83" s="26" t="s">
         <v>166</v>
       </c>
       <c r="C83" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="D83" s="41"/>
-      <c r="E83" s="38">
+      <c r="D83" s="40"/>
+      <c r="E83" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F83" s="38">
+      <c r="F83" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G83" s="37">
+      <c r="G83" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E83-F83</f>
         <v>0</v>
       </c>
@@ -6310,22 +6307,22 @@
       <c r="R83" s="11"/>
     </row>
     <row r="84" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="27" t="s">
+      <c r="B84" s="26" t="s">
         <v>168</v>
       </c>
       <c r="C84" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="D84" s="41"/>
-      <c r="E84" s="38">
+      <c r="D84" s="40"/>
+      <c r="E84" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F84" s="38">
+      <c r="F84" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G84" s="37">
+      <c r="G84" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E84-F84</f>
         <v>0</v>
       </c>
@@ -6345,22 +6342,22 @@
       <c r="R84" s="12"/>
     </row>
     <row r="85" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="27" t="s">
+      <c r="B85" s="26" t="s">
         <v>170</v>
       </c>
       <c r="C85" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="D85" s="41"/>
-      <c r="E85" s="38">
+      <c r="D85" s="40"/>
+      <c r="E85" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F85" s="38">
+      <c r="F85" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G85" s="37">
+      <c r="G85" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E85-F85</f>
         <v>0</v>
       </c>
@@ -6380,22 +6377,22 @@
       <c r="R85" s="11"/>
     </row>
     <row r="86" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="27" t="s">
+      <c r="B86" s="26" t="s">
         <v>172</v>
       </c>
       <c r="C86" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="D86" s="41"/>
-      <c r="E86" s="38">
+      <c r="D86" s="40"/>
+      <c r="E86" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F86" s="38">
+      <c r="F86" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G86" s="37">
+      <c r="G86" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E86-F86</f>
         <v>0</v>
       </c>
@@ -6415,22 +6412,22 @@
       <c r="R86" s="14"/>
     </row>
     <row r="87" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="27" t="s">
+      <c r="B87" s="26" t="s">
         <v>174</v>
       </c>
       <c r="C87" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="D87" s="41"/>
-      <c r="E87" s="38">
+      <c r="D87" s="40"/>
+      <c r="E87" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F87" s="38">
+      <c r="F87" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G87" s="37">
+      <c r="G87" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E87-F87</f>
         <v>0</v>
       </c>
@@ -6450,22 +6447,22 @@
       <c r="R87" s="11"/>
     </row>
     <row r="88" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="27" t="s">
+      <c r="B88" s="26" t="s">
         <v>176</v>
       </c>
       <c r="C88" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="D88" s="41"/>
-      <c r="E88" s="38">
+      <c r="D88" s="40"/>
+      <c r="E88" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F88" s="38">
+      <c r="F88" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G88" s="37">
+      <c r="G88" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E88-F88</f>
         <v>0</v>
       </c>
@@ -6485,22 +6482,22 @@
       <c r="R88" s="14"/>
     </row>
     <row r="89" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="27" t="s">
+      <c r="B89" s="26" t="s">
         <v>178</v>
       </c>
       <c r="C89" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="D89" s="41"/>
-      <c r="E89" s="38">
+      <c r="D89" s="40"/>
+      <c r="E89" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F89" s="38">
+      <c r="F89" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G89" s="37">
+      <c r="G89" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E89-F89</f>
         <v>0</v>
       </c>
@@ -6520,22 +6517,22 @@
       <c r="R89" s="11"/>
     </row>
     <row r="90" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B90" s="27" t="s">
+      <c r="B90" s="26" t="s">
         <v>180</v>
       </c>
       <c r="C90" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="D90" s="41"/>
-      <c r="E90" s="38">
+      <c r="D90" s="40"/>
+      <c r="E90" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F90" s="38">
+      <c r="F90" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G90" s="37">
+      <c r="G90" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E90-F90</f>
         <v>0</v>
       </c>
@@ -6555,24 +6552,24 @@
       <c r="R90" s="14"/>
     </row>
     <row r="91" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B91" s="72" t="s">
+      <c r="B91" s="70" t="s">
         <v>182</v>
       </c>
-      <c r="C91" s="73" t="s">
+      <c r="C91" s="71" t="s">
         <v>183</v>
       </c>
-      <c r="D91" s="74">
+      <c r="D91" s="72">
         <v>4</v>
       </c>
-      <c r="E91" s="75">
+      <c r="E91" s="73">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F91" s="75">
+      <c r="F91" s="73">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G91" s="76">
+      <c r="G91" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E91-F91</f>
         <v>4</v>
       </c>
@@ -6592,22 +6589,22 @@
       <c r="R91" s="11"/>
     </row>
     <row r="92" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B92" s="27" t="s">
+      <c r="B92" s="26" t="s">
         <v>184</v>
       </c>
       <c r="C92" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="D92" s="41"/>
-      <c r="E92" s="38">
+      <c r="D92" s="40"/>
+      <c r="E92" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F92" s="38">
+      <c r="F92" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G92" s="37">
+      <c r="G92" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E92-F92</f>
         <v>0</v>
       </c>
@@ -6627,22 +6624,22 @@
       <c r="R92" s="14"/>
     </row>
     <row r="93" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B93" s="27" t="s">
+      <c r="B93" s="26" t="s">
         <v>186</v>
       </c>
       <c r="C93" s="25" t="s">
         <v>187</v>
       </c>
-      <c r="D93" s="41"/>
-      <c r="E93" s="38">
+      <c r="D93" s="40"/>
+      <c r="E93" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F93" s="38">
+      <c r="F93" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G93" s="37">
+      <c r="G93" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E93-F93</f>
         <v>0</v>
       </c>
@@ -6662,22 +6659,22 @@
       <c r="R93" s="11"/>
     </row>
     <row r="94" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B94" s="27" t="s">
+      <c r="B94" s="96" t="s">
         <v>188</v>
       </c>
       <c r="C94" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="D94" s="41"/>
-      <c r="E94" s="38">
+      <c r="D94" s="40"/>
+      <c r="E94" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F94" s="38">
+      <c r="F94" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G94" s="37">
+      <c r="G94" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E94-F94</f>
         <v>0</v>
       </c>
@@ -6697,22 +6694,22 @@
       <c r="R94" s="14"/>
     </row>
     <row r="95" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B95" s="27" t="s">
+      <c r="B95" s="96" t="s">
         <v>190</v>
       </c>
       <c r="C95" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="D95" s="41"/>
-      <c r="E95" s="38">
+      <c r="D95" s="40"/>
+      <c r="E95" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F95" s="38">
+      <c r="F95" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G95" s="37">
+      <c r="G95" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E95-F95</f>
         <v>0</v>
       </c>
@@ -6732,22 +6729,22 @@
       <c r="R95" s="11"/>
     </row>
     <row r="96" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B96" s="27" t="s">
+      <c r="B96" s="96" t="s">
         <v>192</v>
       </c>
       <c r="C96" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="D96" s="41"/>
-      <c r="E96" s="38">
+      <c r="D96" s="40"/>
+      <c r="E96" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F96" s="38">
+      <c r="F96" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G96" s="37">
+      <c r="G96" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E96-F96</f>
         <v>0</v>
       </c>
@@ -6767,22 +6764,22 @@
       <c r="R96" s="14"/>
     </row>
     <row r="97" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B97" s="27" t="s">
+      <c r="B97" s="26" t="s">
         <v>194</v>
       </c>
       <c r="C97" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="D97" s="41"/>
-      <c r="E97" s="38">
+      <c r="D97" s="40"/>
+      <c r="E97" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F97" s="38">
+      <c r="F97" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G97" s="37">
+      <c r="G97" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E97-F97</f>
         <v>0</v>
       </c>
@@ -6802,22 +6799,22 @@
       <c r="R97" s="11"/>
     </row>
     <row r="98" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B98" s="27" t="s">
+      <c r="B98" s="26" t="s">
         <v>196</v>
       </c>
       <c r="C98" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="D98" s="41"/>
-      <c r="E98" s="38">
+      <c r="D98" s="40"/>
+      <c r="E98" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F98" s="38">
+      <c r="F98" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G98" s="37">
+      <c r="G98" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E98-F98</f>
         <v>0</v>
       </c>
@@ -6837,22 +6834,22 @@
       <c r="R98" s="14"/>
     </row>
     <row r="99" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B99" s="27" t="s">
+      <c r="B99" s="26" t="s">
         <v>198</v>
       </c>
       <c r="C99" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="D99" s="41"/>
-      <c r="E99" s="38">
+      <c r="D99" s="40"/>
+      <c r="E99" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F99" s="38">
+      <c r="F99" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G99" s="37">
+      <c r="G99" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E99-F99</f>
         <v>0</v>
       </c>
@@ -6872,24 +6869,24 @@
       <c r="R99" s="22"/>
     </row>
     <row r="100" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B100" s="59" t="s">
+      <c r="B100" s="96" t="s">
         <v>200</v>
       </c>
-      <c r="C100" s="60" t="s">
+      <c r="C100" s="58" t="s">
         <v>201</v>
       </c>
-      <c r="D100" s="58">
+      <c r="D100" s="57">
         <v>38</v>
       </c>
-      <c r="E100" s="61">
+      <c r="E100" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F100" s="61">
+      <c r="F100" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G100" s="62">
+      <c r="G100" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E100-F100</f>
         <v>38</v>
       </c>
@@ -6909,22 +6906,22 @@
       <c r="R100" s="15"/>
     </row>
     <row r="101" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B101" s="27" t="s">
+      <c r="B101" s="26" t="s">
         <v>202</v>
       </c>
       <c r="C101" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="D101" s="41"/>
-      <c r="E101" s="38">
+      <c r="D101" s="40"/>
+      <c r="E101" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F101" s="38">
+      <c r="F101" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G101" s="37">
+      <c r="G101" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E101-F101</f>
         <v>0</v>
       </c>
@@ -6938,22 +6935,22 @@
       </c>
     </row>
     <row r="102" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B102" s="27" t="s">
+      <c r="B102" s="26" t="s">
         <v>204</v>
       </c>
       <c r="C102" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="D102" s="41"/>
-      <c r="E102" s="38">
+      <c r="D102" s="40"/>
+      <c r="E102" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F102" s="38">
+      <c r="F102" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G102" s="37">
+      <c r="G102" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E102-F102</f>
         <v>0</v>
       </c>
@@ -6967,24 +6964,24 @@
       </c>
     </row>
     <row r="103" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B103" s="28" t="s">
+      <c r="B103" s="27" t="s">
         <v>569</v>
       </c>
       <c r="C103" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D103" s="40">
-        <v>0</v>
-      </c>
-      <c r="E103" s="38">
+      <c r="D103" s="39">
+        <v>0</v>
+      </c>
+      <c r="E103" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F103" s="38">
+      <c r="F103" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G103" s="37">
+      <c r="G103" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E103-F103</f>
         <v>0</v>
       </c>
@@ -6998,22 +6995,22 @@
       </c>
     </row>
     <row r="104" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B104" s="103" t="s">
+      <c r="B104" s="96" t="s">
         <v>214</v>
       </c>
       <c r="C104" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="D104" s="41"/>
-      <c r="E104" s="38">
+      <c r="D104" s="40"/>
+      <c r="E104" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F104" s="38">
+      <c r="F104" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G104" s="37">
+      <c r="G104" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E104-F104</f>
         <v>0</v>
       </c>
@@ -7027,24 +7024,24 @@
       </c>
     </row>
     <row r="105" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="103" t="s">
+      <c r="B105" s="96" t="s">
         <v>216</v>
       </c>
-      <c r="C105" s="44" t="s">
+      <c r="C105" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="D105" s="45">
+      <c r="D105" s="44">
         <v>158</v>
       </c>
-      <c r="E105" s="46">
+      <c r="E105" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F105" s="46">
+      <c r="F105" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G105" s="47">
+      <c r="G105" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E105-F105</f>
         <v>158</v>
       </c>
@@ -7058,24 +7055,24 @@
       </c>
     </row>
     <row r="106" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="103" t="s">
+      <c r="B106" s="96" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="44" t="s">
+      <c r="C106" s="43" t="s">
         <v>219</v>
       </c>
-      <c r="D106" s="45">
+      <c r="D106" s="44">
         <v>308</v>
       </c>
-      <c r="E106" s="46">
+      <c r="E106" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F106" s="46">
+      <c r="F106" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G106" s="47">
+      <c r="G106" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E106-F106</f>
         <v>308</v>
       </c>
@@ -7089,24 +7086,24 @@
       </c>
     </row>
     <row r="107" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="103" t="s">
+      <c r="B107" s="96" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="44" t="s">
+      <c r="C107" s="43" t="s">
         <v>221</v>
       </c>
-      <c r="D107" s="45">
+      <c r="D107" s="44">
         <v>50</v>
       </c>
-      <c r="E107" s="46">
+      <c r="E107" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F107" s="46">
+      <c r="F107" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G107" s="47">
+      <c r="G107" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E107-F107</f>
         <v>50</v>
       </c>
@@ -7120,22 +7117,22 @@
       </c>
     </row>
     <row r="108" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="103" t="s">
+      <c r="B108" s="96" t="s">
         <v>222</v>
       </c>
       <c r="C108" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="D108" s="41"/>
-      <c r="E108" s="38">
+      <c r="D108" s="40"/>
+      <c r="E108" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F108" s="38">
+      <c r="F108" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G108" s="37">
+      <c r="G108" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E108-F108</f>
         <v>0</v>
       </c>
@@ -7149,22 +7146,22 @@
       </c>
     </row>
     <row r="109" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="103" t="s">
+      <c r="B109" s="96" t="s">
         <v>224</v>
       </c>
-      <c r="C109" s="73" t="s">
+      <c r="C109" s="71" t="s">
         <v>225</v>
       </c>
-      <c r="D109" s="74"/>
-      <c r="E109" s="75">
+      <c r="D109" s="72"/>
+      <c r="E109" s="73">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F109" s="75">
+      <c r="F109" s="73">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G109" s="76">
+      <c r="G109" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E109-F109</f>
         <v>0</v>
       </c>
@@ -7178,22 +7175,22 @@
       </c>
     </row>
     <row r="110" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B110" s="103" t="s">
+      <c r="B110" s="96" t="s">
         <v>226</v>
       </c>
       <c r="C110" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="D110" s="41"/>
-      <c r="E110" s="38">
+      <c r="D110" s="40"/>
+      <c r="E110" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F110" s="38">
+      <c r="F110" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G110" s="37">
+      <c r="G110" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E110-F110</f>
         <v>0</v>
       </c>
@@ -7207,24 +7204,24 @@
       </c>
     </row>
     <row r="111" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="103" t="s">
+      <c r="B111" s="96" t="s">
         <v>228</v>
       </c>
-      <c r="C111" s="44" t="s">
+      <c r="C111" s="43" t="s">
         <v>229</v>
       </c>
-      <c r="D111" s="45">
+      <c r="D111" s="44">
         <v>143</v>
       </c>
-      <c r="E111" s="46">
+      <c r="E111" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F111" s="46">
+      <c r="F111" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G111" s="47">
+      <c r="G111" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E111-F111</f>
         <v>143</v>
       </c>
@@ -7238,22 +7235,22 @@
       </c>
     </row>
     <row r="112" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="27" t="s">
+      <c r="B112" s="26" t="s">
         <v>230</v>
       </c>
       <c r="C112" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="D112" s="41"/>
-      <c r="E112" s="38">
+      <c r="D112" s="40"/>
+      <c r="E112" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F112" s="38">
+      <c r="F112" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G112" s="37">
+      <c r="G112" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E112-F112</f>
         <v>0</v>
       </c>
@@ -7267,28 +7264,28 @@
       </c>
     </row>
     <row r="113" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="103" t="s">
+      <c r="B113" s="96" t="s">
         <v>206</v>
       </c>
-      <c r="C113" s="60" t="s">
+      <c r="C113" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="D113" s="58">
+      <c r="D113" s="57">
         <v>13</v>
       </c>
-      <c r="E113" s="61">
+      <c r="E113" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F113" s="61">
+      <c r="F113" s="59">
         <f t="shared" si="6"/>
         <v>28</v>
       </c>
-      <c r="G113" s="62">
+      <c r="G113" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E113-F113</f>
         <v>-15</v>
       </c>
-      <c r="H113" s="64" t="s">
+      <c r="H113" s="62" t="s">
         <v>579</v>
       </c>
       <c r="K113" s="19" t="str">
@@ -7301,22 +7298,22 @@
       </c>
     </row>
     <row r="114" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="103" t="s">
+      <c r="B114" s="96" t="s">
         <v>232</v>
       </c>
       <c r="C114" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="D114" s="41"/>
-      <c r="E114" s="38">
+      <c r="D114" s="40"/>
+      <c r="E114" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F114" s="38">
+      <c r="F114" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G114" s="37">
+      <c r="G114" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E114-F114</f>
         <v>0</v>
       </c>
@@ -7330,24 +7327,24 @@
       </c>
     </row>
     <row r="115" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="103" t="s">
+      <c r="B115" s="96" t="s">
         <v>234</v>
       </c>
-      <c r="C115" s="44" t="s">
+      <c r="C115" s="43" t="s">
         <v>235</v>
       </c>
-      <c r="D115" s="45">
+      <c r="D115" s="44">
         <v>89</v>
       </c>
-      <c r="E115" s="46">
+      <c r="E115" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F115" s="46">
+      <c r="F115" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G115" s="47">
+      <c r="G115" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E115-F115</f>
         <v>89</v>
       </c>
@@ -7361,22 +7358,22 @@
       </c>
     </row>
     <row r="116" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B116" s="103" t="s">
+      <c r="B116" s="96" t="s">
         <v>236</v>
       </c>
       <c r="C116" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="D116" s="41"/>
-      <c r="E116" s="38">
+      <c r="D116" s="40"/>
+      <c r="E116" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F116" s="38">
+      <c r="F116" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G116" s="37">
+      <c r="G116" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E116-F116</f>
         <v>0</v>
       </c>
@@ -7390,24 +7387,24 @@
       </c>
     </row>
     <row r="117" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="103" t="s">
+      <c r="B117" s="96" t="s">
         <v>238</v>
       </c>
-      <c r="C117" s="44" t="s">
+      <c r="C117" s="43" t="s">
         <v>239</v>
       </c>
-      <c r="D117" s="45">
+      <c r="D117" s="44">
         <v>69</v>
       </c>
-      <c r="E117" s="46">
+      <c r="E117" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F117" s="46">
+      <c r="F117" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G117" s="47">
+      <c r="G117" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E117-F117</f>
         <v>69</v>
       </c>
@@ -7421,24 +7418,24 @@
       </c>
     </row>
     <row r="118" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="103" t="s">
+      <c r="B118" s="96" t="s">
         <v>240</v>
       </c>
-      <c r="C118" s="44" t="s">
+      <c r="C118" s="43" t="s">
         <v>241</v>
       </c>
-      <c r="D118" s="45">
+      <c r="D118" s="44">
         <v>180</v>
       </c>
-      <c r="E118" s="46">
+      <c r="E118" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F118" s="46">
+      <c r="F118" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G118" s="47">
+      <c r="G118" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E118-F118</f>
         <v>180</v>
       </c>
@@ -7452,22 +7449,22 @@
       </c>
     </row>
     <row r="119" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="103" t="s">
+      <c r="B119" s="96" t="s">
         <v>242</v>
       </c>
       <c r="C119" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="D119" s="41"/>
-      <c r="E119" s="38">
+      <c r="D119" s="40"/>
+      <c r="E119" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F119" s="38">
+      <c r="F119" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G119" s="37">
+      <c r="G119" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E119-F119</f>
         <v>0</v>
       </c>
@@ -7481,24 +7478,24 @@
       </c>
     </row>
     <row r="120" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="103" t="s">
+      <c r="B120" s="96" t="s">
         <v>208</v>
       </c>
-      <c r="C120" s="60" t="s">
+      <c r="C120" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="D120" s="58">
+      <c r="D120" s="57">
         <v>54</v>
       </c>
-      <c r="E120" s="61">
+      <c r="E120" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F120" s="61">
+      <c r="F120" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G120" s="62">
+      <c r="G120" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E120-F120</f>
         <v>54</v>
       </c>
@@ -7512,24 +7509,24 @@
       </c>
     </row>
     <row r="121" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="103" t="s">
+      <c r="B121" s="96" t="s">
         <v>244</v>
       </c>
-      <c r="C121" s="44" t="s">
+      <c r="C121" s="43" t="s">
         <v>245</v>
       </c>
-      <c r="D121" s="45">
+      <c r="D121" s="44">
         <v>99</v>
       </c>
-      <c r="E121" s="46">
+      <c r="E121" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F121" s="46">
+      <c r="F121" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G121" s="47">
+      <c r="G121" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E121-F121</f>
         <v>99</v>
       </c>
@@ -7543,24 +7540,24 @@
       </c>
     </row>
     <row r="122" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B122" s="103" t="s">
+      <c r="B122" s="96" t="s">
         <v>210</v>
       </c>
-      <c r="C122" s="60" t="s">
+      <c r="C122" s="58" t="s">
         <v>211</v>
       </c>
-      <c r="D122" s="58">
+      <c r="D122" s="57">
         <v>39</v>
       </c>
-      <c r="E122" s="61">
+      <c r="E122" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F122" s="61">
+      <c r="F122" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G122" s="62">
+      <c r="G122" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E122-F122</f>
         <v>39</v>
       </c>
@@ -7574,22 +7571,22 @@
       </c>
     </row>
     <row r="123" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="103" t="s">
+      <c r="B123" s="96" t="s">
         <v>246</v>
       </c>
       <c r="C123" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="D123" s="41"/>
-      <c r="E123" s="38">
+      <c r="D123" s="40"/>
+      <c r="E123" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F123" s="38">
+      <c r="F123" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G123" s="37">
+      <c r="G123" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E123-F123</f>
         <v>0</v>
       </c>
@@ -7603,22 +7600,22 @@
       </c>
     </row>
     <row r="124" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="103" t="s">
+      <c r="B124" s="96" t="s">
         <v>248</v>
       </c>
       <c r="C124" s="25" t="s">
         <v>249</v>
       </c>
-      <c r="D124" s="41"/>
-      <c r="E124" s="38">
+      <c r="D124" s="40"/>
+      <c r="E124" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F124" s="38">
+      <c r="F124" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G124" s="37">
+      <c r="G124" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E124-F124</f>
         <v>0</v>
       </c>
@@ -7632,24 +7629,24 @@
       </c>
     </row>
     <row r="125" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="103" t="s">
+      <c r="B125" s="96" t="s">
         <v>250</v>
       </c>
-      <c r="C125" s="44" t="s">
+      <c r="C125" s="43" t="s">
         <v>251</v>
       </c>
-      <c r="D125" s="45">
+      <c r="D125" s="44">
         <v>99</v>
       </c>
-      <c r="E125" s="46">
+      <c r="E125" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F125" s="46">
+      <c r="F125" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G125" s="47">
+      <c r="G125" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E125-F125</f>
         <v>99</v>
       </c>
@@ -7663,24 +7660,24 @@
       </c>
     </row>
     <row r="126" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="103" t="s">
+      <c r="B126" s="96" t="s">
         <v>252</v>
       </c>
-      <c r="C126" s="60" t="s">
+      <c r="C126" s="58" t="s">
         <v>253</v>
       </c>
-      <c r="D126" s="58">
+      <c r="D126" s="57">
         <v>90</v>
       </c>
-      <c r="E126" s="61">
+      <c r="E126" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F126" s="61">
+      <c r="F126" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G126" s="62">
+      <c r="G126" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E126-F126</f>
         <v>90</v>
       </c>
@@ -7694,24 +7691,24 @@
       </c>
     </row>
     <row r="127" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="103" t="s">
+      <c r="B127" s="96" t="s">
         <v>254</v>
       </c>
-      <c r="C127" s="60" t="s">
+      <c r="C127" s="58" t="s">
         <v>255</v>
       </c>
-      <c r="D127" s="58">
+      <c r="D127" s="57">
         <v>34</v>
       </c>
-      <c r="E127" s="61">
+      <c r="E127" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F127" s="61">
+      <c r="F127" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G127" s="62">
+      <c r="G127" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E127-F127</f>
         <v>34</v>
       </c>
@@ -7725,24 +7722,24 @@
       </c>
     </row>
     <row r="128" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B128" s="103" t="s">
+      <c r="B128" s="96" t="s">
         <v>256</v>
       </c>
-      <c r="C128" s="60" t="s">
+      <c r="C128" s="58" t="s">
         <v>257</v>
       </c>
-      <c r="D128" s="58">
+      <c r="D128" s="57">
         <v>74</v>
       </c>
-      <c r="E128" s="61">
+      <c r="E128" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F128" s="61">
+      <c r="F128" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G128" s="62">
+      <c r="G128" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E128-F128</f>
         <v>74</v>
       </c>
@@ -7756,24 +7753,24 @@
       </c>
     </row>
     <row r="129" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="104" t="s">
+      <c r="B129" s="97" t="s">
         <v>258</v>
       </c>
-      <c r="C129" s="60" t="s">
+      <c r="C129" s="58" t="s">
         <v>259</v>
       </c>
-      <c r="D129" s="58">
+      <c r="D129" s="57">
         <v>200</v>
       </c>
-      <c r="E129" s="61">
+      <c r="E129" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F129" s="61">
+      <c r="F129" s="59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G129" s="62">
+      <c r="G129" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E129-F129</f>
         <v>200</v>
       </c>
@@ -7787,24 +7784,24 @@
       </c>
     </row>
     <row r="130" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="103" t="s">
+      <c r="B130" s="96" t="s">
         <v>260</v>
       </c>
-      <c r="C130" s="79" t="s">
+      <c r="C130" s="77" t="s">
         <v>261</v>
       </c>
-      <c r="D130" s="80">
+      <c r="D130" s="78">
         <v>253</v>
       </c>
-      <c r="E130" s="81">
+      <c r="E130" s="79">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F130" s="81">
+      <c r="F130" s="79">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G130" s="82">
+      <c r="G130" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E130-F130</f>
         <v>253</v>
       </c>
@@ -7818,24 +7815,24 @@
       </c>
     </row>
     <row r="131" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="103" t="s">
+      <c r="B131" s="96" t="s">
         <v>262</v>
       </c>
-      <c r="C131" s="44" t="s">
+      <c r="C131" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="D131" s="45">
+      <c r="D131" s="44">
         <v>29</v>
       </c>
-      <c r="E131" s="46">
+      <c r="E131" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F131" s="46">
+      <c r="F131" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G131" s="47">
+      <c r="G131" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E131-F131</f>
         <v>29</v>
       </c>
@@ -7849,22 +7846,22 @@
       </c>
     </row>
     <row r="132" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="103" t="s">
+      <c r="B132" s="96" t="s">
         <v>264</v>
       </c>
       <c r="C132" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="D132" s="41"/>
-      <c r="E132" s="38">
+      <c r="D132" s="40"/>
+      <c r="E132" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F132" s="38">
+      <c r="F132" s="37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G132" s="37">
+      <c r="G132" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E132-F132</f>
         <v>0</v>
       </c>
@@ -7878,24 +7875,24 @@
       </c>
     </row>
     <row r="133" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="103" t="s">
+      <c r="B133" s="96" t="s">
         <v>266</v>
       </c>
-      <c r="C133" s="73" t="s">
+      <c r="C133" s="71" t="s">
         <v>267</v>
       </c>
-      <c r="D133" s="74">
+      <c r="D133" s="72">
         <v>54</v>
       </c>
-      <c r="E133" s="75">
+      <c r="E133" s="73">
         <f t="shared" ref="E133:E198" si="9">SUMIF($J$4:$J$5000, B133, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F133" s="75">
+      <c r="F133" s="73">
         <f t="shared" ref="F133:F198" si="10">SUMIF($O$4:$O$5000, B133, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G133" s="76">
+      <c r="G133" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E133-F133</f>
         <v>54</v>
       </c>
@@ -7909,24 +7906,24 @@
       </c>
     </row>
     <row r="134" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B134" s="103" t="s">
+      <c r="B134" s="96" t="s">
         <v>268</v>
       </c>
-      <c r="C134" s="73" t="s">
+      <c r="C134" s="71" t="s">
         <v>269</v>
       </c>
-      <c r="D134" s="74">
+      <c r="D134" s="72">
         <v>60</v>
       </c>
-      <c r="E134" s="75">
+      <c r="E134" s="73">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F134" s="75">
+      <c r="F134" s="73">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G134" s="76">
+      <c r="G134" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E134-F134</f>
         <v>60</v>
       </c>
@@ -7940,24 +7937,24 @@
       </c>
     </row>
     <row r="135" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B135" s="103" t="s">
+      <c r="B135" s="96" t="s">
         <v>270</v>
       </c>
-      <c r="C135" s="44" t="s">
+      <c r="C135" s="43" t="s">
         <v>271</v>
       </c>
-      <c r="D135" s="45">
+      <c r="D135" s="44">
         <v>11</v>
       </c>
-      <c r="E135" s="46">
+      <c r="E135" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F135" s="46">
+      <c r="F135" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G135" s="47">
+      <c r="G135" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E135-F135</f>
         <v>11</v>
       </c>
@@ -7971,24 +7968,24 @@
       </c>
     </row>
     <row r="136" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B136" s="103" t="s">
+      <c r="B136" s="96" t="s">
         <v>272</v>
       </c>
-      <c r="C136" s="44" t="s">
+      <c r="C136" s="43" t="s">
         <v>273</v>
       </c>
-      <c r="D136" s="45">
+      <c r="D136" s="44">
         <v>40</v>
       </c>
-      <c r="E136" s="46">
+      <c r="E136" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F136" s="46">
+      <c r="F136" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G136" s="47">
+      <c r="G136" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E136-F136</f>
         <v>40</v>
       </c>
@@ -8002,24 +7999,24 @@
       </c>
     </row>
     <row r="137" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B137" s="103" t="s">
+      <c r="B137" s="96" t="s">
         <v>274</v>
       </c>
-      <c r="C137" s="44" t="s">
+      <c r="C137" s="43" t="s">
         <v>275</v>
       </c>
-      <c r="D137" s="45">
+      <c r="D137" s="44">
         <v>16</v>
       </c>
-      <c r="E137" s="46">
+      <c r="E137" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F137" s="46">
+      <c r="F137" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G137" s="47">
+      <c r="G137" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E137-F137</f>
         <v>16</v>
       </c>
@@ -8033,24 +8030,24 @@
       </c>
     </row>
     <row r="138" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B138" s="103" t="s">
+      <c r="B138" s="96" t="s">
         <v>276</v>
       </c>
-      <c r="C138" s="44" t="s">
+      <c r="C138" s="43" t="s">
         <v>277</v>
       </c>
-      <c r="D138" s="45">
+      <c r="D138" s="44">
         <v>5</v>
       </c>
-      <c r="E138" s="46">
+      <c r="E138" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F138" s="46">
+      <c r="F138" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G138" s="47">
+      <c r="G138" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E138-F138</f>
         <v>5</v>
       </c>
@@ -8064,22 +8061,22 @@
       </c>
     </row>
     <row r="139" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B139" s="103" t="s">
+      <c r="B139" s="96" t="s">
         <v>278</v>
       </c>
       <c r="C139" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="D139" s="41"/>
-      <c r="E139" s="38">
+      <c r="D139" s="40"/>
+      <c r="E139" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F139" s="38">
+      <c r="F139" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G139" s="37">
+      <c r="G139" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E139-F139</f>
         <v>0</v>
       </c>
@@ -8093,24 +8090,24 @@
       </c>
     </row>
     <row r="140" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B140" s="103" t="s">
+      <c r="B140" s="96" t="s">
         <v>280</v>
       </c>
-      <c r="C140" s="44" t="s">
+      <c r="C140" s="43" t="s">
         <v>281</v>
       </c>
-      <c r="D140" s="45">
+      <c r="D140" s="44">
         <v>39</v>
       </c>
-      <c r="E140" s="46">
+      <c r="E140" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F140" s="46">
+      <c r="F140" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G140" s="47">
+      <c r="G140" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E140-F140</f>
         <v>39</v>
       </c>
@@ -8123,95 +8120,95 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:16" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B141" s="103" t="s">
+    <row r="141" spans="2:16" s="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B141" s="96" t="s">
         <v>282</v>
       </c>
-      <c r="C141" s="44" t="s">
+      <c r="C141" s="43" t="s">
         <v>283</v>
       </c>
-      <c r="D141" s="45">
+      <c r="D141" s="44">
         <v>47</v>
       </c>
-      <c r="E141" s="46">
+      <c r="E141" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F141" s="46">
+      <c r="F141" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G141" s="47">
+      <c r="G141" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E141-F141</f>
         <v>47</v>
       </c>
       <c r="H141"/>
-      <c r="K141" s="83" t="str">
+      <c r="K141" s="81" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P141" s="83" t="str">
+      <c r="P141" s="81" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="142" spans="2:16" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B142" s="103" t="s">
+    <row r="142" spans="2:16" s="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B142" s="96" t="s">
         <v>284</v>
       </c>
-      <c r="C142" s="79" t="s">
+      <c r="C142" s="77" t="s">
         <v>285</v>
       </c>
-      <c r="D142" s="80">
+      <c r="D142" s="78">
         <v>38</v>
       </c>
-      <c r="E142" s="81">
+      <c r="E142" s="79">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F142" s="81">
+      <c r="F142" s="79">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G142" s="82">
+      <c r="G142" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E142-F142</f>
         <v>38</v>
       </c>
-      <c r="H142" s="69" t="s">
+      <c r="H142" s="67" t="s">
         <v>605</v>
       </c>
-      <c r="K142" s="83" t="str">
+      <c r="K142" s="81" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P142" s="83" t="str">
+      <c r="P142" s="81" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="143" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B143" s="103" t="s">
+      <c r="B143" s="96" t="s">
         <v>286</v>
       </c>
-      <c r="C143" s="79" t="s">
+      <c r="C143" s="77" t="s">
         <v>287</v>
       </c>
-      <c r="D143" s="80">
+      <c r="D143" s="78">
         <v>18</v>
       </c>
-      <c r="E143" s="81">
+      <c r="E143" s="79">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F143" s="81">
+      <c r="F143" s="79">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G143" s="82">
+      <c r="G143" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E143-F143</f>
         <v>18</v>
       </c>
-      <c r="H143" s="69"/>
+      <c r="H143" s="67"/>
       <c r="K143" s="19" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8222,24 +8219,24 @@
       </c>
     </row>
     <row r="144" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B144" s="103" t="s">
+      <c r="B144" s="96" t="s">
         <v>212</v>
       </c>
-      <c r="C144" s="60" t="s">
+      <c r="C144" s="58" t="s">
         <v>213</v>
       </c>
-      <c r="D144" s="58">
+      <c r="D144" s="57">
         <v>7</v>
       </c>
-      <c r="E144" s="61">
+      <c r="E144" s="59">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F144" s="61">
+      <c r="F144" s="59">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G144" s="62">
+      <c r="G144" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E144-F144</f>
         <v>7</v>
       </c>
@@ -8253,24 +8250,24 @@
       </c>
     </row>
     <row r="145" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B145" s="103" t="s">
+      <c r="B145" s="96" t="s">
         <v>288</v>
       </c>
-      <c r="C145" s="44" t="s">
+      <c r="C145" s="43" t="s">
         <v>289</v>
       </c>
-      <c r="D145" s="45">
+      <c r="D145" s="44">
         <v>50</v>
       </c>
-      <c r="E145" s="46">
+      <c r="E145" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F145" s="46">
+      <c r="F145" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G145" s="47">
+      <c r="G145" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E145-F145</f>
         <v>50</v>
       </c>
@@ -8284,24 +8281,24 @@
       </c>
     </row>
     <row r="146" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B146" s="103" t="s">
+      <c r="B146" s="96" t="s">
         <v>290</v>
       </c>
-      <c r="C146" s="44" t="s">
+      <c r="C146" s="43" t="s">
         <v>291</v>
       </c>
-      <c r="D146" s="45">
+      <c r="D146" s="44">
         <v>39</v>
       </c>
-      <c r="E146" s="46">
+      <c r="E146" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F146" s="46">
+      <c r="F146" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G146" s="47">
+      <c r="G146" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E146-F146</f>
         <v>39</v>
       </c>
@@ -8315,22 +8312,22 @@
       </c>
     </row>
     <row r="147" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B147" s="103" t="s">
+      <c r="B147" s="96" t="s">
         <v>292</v>
       </c>
       <c r="C147" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="D147" s="41"/>
-      <c r="E147" s="38">
+      <c r="D147" s="40"/>
+      <c r="E147" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F147" s="38">
+      <c r="F147" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G147" s="37">
+      <c r="G147" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E147-F147</f>
         <v>0</v>
       </c>
@@ -8344,22 +8341,22 @@
       </c>
     </row>
     <row r="148" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B148" s="103" t="s">
+      <c r="B148" s="96" t="s">
         <v>294</v>
       </c>
       <c r="C148" s="25" t="s">
         <v>295</v>
       </c>
-      <c r="D148" s="41"/>
-      <c r="E148" s="38">
+      <c r="D148" s="40"/>
+      <c r="E148" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F148" s="38">
+      <c r="F148" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G148" s="37">
+      <c r="G148" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E148-F148</f>
         <v>0</v>
       </c>
@@ -8373,22 +8370,22 @@
       </c>
     </row>
     <row r="149" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B149" s="103" t="s">
+      <c r="B149" s="96" t="s">
         <v>296</v>
       </c>
       <c r="C149" s="25" t="s">
         <v>297</v>
       </c>
-      <c r="D149" s="41"/>
-      <c r="E149" s="38">
+      <c r="D149" s="40"/>
+      <c r="E149" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F149" s="38">
+      <c r="F149" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G149" s="37">
+      <c r="G149" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E149-F149</f>
         <v>0</v>
       </c>
@@ -8402,22 +8399,22 @@
       </c>
     </row>
     <row r="150" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B150" s="103" t="s">
+      <c r="B150" s="96" t="s">
         <v>298</v>
       </c>
       <c r="C150" s="25" t="s">
         <v>299</v>
       </c>
-      <c r="D150" s="41"/>
-      <c r="E150" s="38">
+      <c r="D150" s="40"/>
+      <c r="E150" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F150" s="38">
+      <c r="F150" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G150" s="37">
+      <c r="G150" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E150-F150</f>
         <v>0</v>
       </c>
@@ -8431,22 +8428,22 @@
       </c>
     </row>
     <row r="151" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B151" s="103" t="s">
+      <c r="B151" s="96" t="s">
         <v>300</v>
       </c>
       <c r="C151" s="25" t="s">
         <v>301</v>
       </c>
-      <c r="D151" s="41"/>
-      <c r="E151" s="38">
+      <c r="D151" s="40"/>
+      <c r="E151" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F151" s="38">
+      <c r="F151" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G151" s="37">
+      <c r="G151" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E151-F151</f>
         <v>0</v>
       </c>
@@ -8460,22 +8457,22 @@
       </c>
     </row>
     <row r="152" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B152" s="103" t="s">
+      <c r="B152" s="96" t="s">
         <v>302</v>
       </c>
       <c r="C152" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="D152" s="41"/>
-      <c r="E152" s="38">
+      <c r="D152" s="40"/>
+      <c r="E152" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F152" s="38">
+      <c r="F152" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G152" s="37">
+      <c r="G152" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E152-F152</f>
         <v>0</v>
       </c>
@@ -8488,57 +8485,57 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:16" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B153" s="48" t="s">
+    <row r="153" spans="2:16" s="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B153" s="47" t="s">
         <v>576</v>
       </c>
-      <c r="C153" s="44"/>
-      <c r="D153" s="49">
+      <c r="C153" s="43"/>
+      <c r="D153" s="48">
         <v>37</v>
       </c>
-      <c r="E153" s="46">
+      <c r="E153" s="45">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F153" s="46">
+      <c r="F153" s="45">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G153" s="47">
+      <c r="G153" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E153-F153</f>
         <v>37</v>
       </c>
       <c r="H153"/>
-      <c r="K153" s="83" t="str">
+      <c r="K153" s="81" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P153" s="83" t="str">
+      <c r="P153" s="81" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="154" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B154" s="84" t="s">
+      <c r="B154" s="82" t="s">
         <v>606</v>
       </c>
-      <c r="C154" s="79"/>
-      <c r="D154" s="85" t="s">
+      <c r="C154" s="77"/>
+      <c r="D154" s="83" t="s">
         <v>607</v>
       </c>
-      <c r="E154" s="81">
+      <c r="E154" s="79">
         <f>SUMIF($J$4:$J$5000, B154, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F154" s="81">
+      <c r="F154" s="79">
         <f>SUMIF($O$4:$O$5000, B154, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G154" s="82">
+      <c r="G154" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E154-F154</f>
         <v>47</v>
       </c>
-      <c r="H154" s="69"/>
+      <c r="H154" s="67"/>
       <c r="K154" s="19" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8549,24 +8546,24 @@
       </c>
     </row>
     <row r="155" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B155" s="78" t="s">
+      <c r="B155" s="76" t="s">
         <v>304</v>
       </c>
-      <c r="C155" s="79" t="s">
+      <c r="C155" s="77" t="s">
         <v>305</v>
       </c>
-      <c r="D155" s="80">
+      <c r="D155" s="78">
         <v>260</v>
       </c>
-      <c r="E155" s="81">
+      <c r="E155" s="79">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F155" s="81">
+      <c r="F155" s="79">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G155" s="82">
+      <c r="G155" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E155-F155</f>
         <v>260</v>
       </c>
@@ -8580,22 +8577,22 @@
       </c>
     </row>
     <row r="156" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B156" s="27" t="s">
+      <c r="B156" s="26" t="s">
         <v>306</v>
       </c>
       <c r="C156" s="25" t="s">
         <v>307</v>
       </c>
-      <c r="D156" s="41"/>
-      <c r="E156" s="38">
+      <c r="D156" s="40"/>
+      <c r="E156" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F156" s="38">
+      <c r="F156" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G156" s="37">
+      <c r="G156" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E156-F156</f>
         <v>0</v>
       </c>
@@ -8609,22 +8606,22 @@
       </c>
     </row>
     <row r="157" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B157" s="27" t="s">
+      <c r="B157" s="26" t="s">
         <v>308</v>
       </c>
       <c r="C157" s="25" t="s">
         <v>309</v>
       </c>
-      <c r="D157" s="41"/>
-      <c r="E157" s="38">
+      <c r="D157" s="40"/>
+      <c r="E157" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F157" s="38">
+      <c r="F157" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G157" s="37">
+      <c r="G157" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E157-F157</f>
         <v>0</v>
       </c>
@@ -8638,24 +8635,24 @@
       </c>
     </row>
     <row r="158" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B158" s="78" t="s">
+      <c r="B158" s="76" t="s">
         <v>310</v>
       </c>
-      <c r="C158" s="79" t="s">
+      <c r="C158" s="77" t="s">
         <v>311</v>
       </c>
-      <c r="D158" s="80">
+      <c r="D158" s="78">
         <v>33</v>
       </c>
-      <c r="E158" s="81">
+      <c r="E158" s="79">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F158" s="81">
+      <c r="F158" s="79">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G158" s="82">
+      <c r="G158" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E158-F158</f>
         <v>33</v>
       </c>
@@ -8669,22 +8666,22 @@
       </c>
     </row>
     <row r="159" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B159" s="27" t="s">
+      <c r="B159" s="26" t="s">
         <v>312</v>
       </c>
       <c r="C159" s="25" t="s">
         <v>313</v>
       </c>
-      <c r="D159" s="41"/>
-      <c r="E159" s="38">
+      <c r="D159" s="40"/>
+      <c r="E159" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F159" s="38">
+      <c r="F159" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G159" s="37">
+      <c r="G159" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E159-F159</f>
         <v>0</v>
       </c>
@@ -8698,22 +8695,22 @@
       </c>
     </row>
     <row r="160" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B160" s="27" t="s">
+      <c r="B160" s="26" t="s">
         <v>314</v>
       </c>
       <c r="C160" s="25" t="s">
         <v>315</v>
       </c>
-      <c r="D160" s="41"/>
-      <c r="E160" s="38">
+      <c r="D160" s="40"/>
+      <c r="E160" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F160" s="38">
+      <c r="F160" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G160" s="37">
+      <c r="G160" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E160-F160</f>
         <v>0</v>
       </c>
@@ -8727,22 +8724,22 @@
       </c>
     </row>
     <row r="161" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B161" s="27" t="s">
+      <c r="B161" s="26" t="s">
         <v>316</v>
       </c>
       <c r="C161" s="25" t="s">
         <v>317</v>
       </c>
-      <c r="D161" s="41"/>
-      <c r="E161" s="38">
+      <c r="D161" s="40"/>
+      <c r="E161" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F161" s="38">
+      <c r="F161" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G161" s="37">
+      <c r="G161" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E161-F161</f>
         <v>0</v>
       </c>
@@ -8756,22 +8753,22 @@
       </c>
     </row>
     <row r="162" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B162" s="27" t="s">
+      <c r="B162" s="26" t="s">
         <v>318</v>
       </c>
       <c r="C162" s="25" t="s">
         <v>319</v>
       </c>
-      <c r="D162" s="41"/>
-      <c r="E162" s="38">
+      <c r="D162" s="40"/>
+      <c r="E162" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F162" s="38">
+      <c r="F162" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G162" s="37">
+      <c r="G162" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E162-F162</f>
         <v>0</v>
       </c>
@@ -8785,22 +8782,22 @@
       </c>
     </row>
     <row r="163" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B163" s="27" t="s">
+      <c r="B163" s="26" t="s">
         <v>320</v>
       </c>
       <c r="C163" s="25" t="s">
         <v>321</v>
       </c>
-      <c r="D163" s="41"/>
-      <c r="E163" s="38">
+      <c r="D163" s="40"/>
+      <c r="E163" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F163" s="38">
+      <c r="F163" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G163" s="37">
+      <c r="G163" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E163-F163</f>
         <v>0</v>
       </c>
@@ -8814,22 +8811,22 @@
       </c>
     </row>
     <row r="164" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B164" s="27" t="s">
+      <c r="B164" s="26" t="s">
         <v>322</v>
       </c>
       <c r="C164" s="25" t="s">
         <v>323</v>
       </c>
-      <c r="D164" s="41"/>
-      <c r="E164" s="38">
+      <c r="D164" s="40"/>
+      <c r="E164" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F164" s="38">
+      <c r="F164" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G164" s="37">
+      <c r="G164" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E164-F164</f>
         <v>0</v>
       </c>
@@ -8843,28 +8840,28 @@
       </c>
     </row>
     <row r="165" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B165" s="103" t="s">
+      <c r="B165" s="96" t="s">
         <v>324</v>
       </c>
-      <c r="C165" s="73" t="s">
+      <c r="C165" s="71" t="s">
         <v>325</v>
       </c>
-      <c r="D165" s="74">
+      <c r="D165" s="72">
         <v>2</v>
       </c>
-      <c r="E165" s="75">
+      <c r="E165" s="73">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F165" s="75">
+      <c r="F165" s="73">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G165" s="76">
+      <c r="G165" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E165-F165</f>
         <v>2</v>
       </c>
-      <c r="H165" s="70" t="s">
+      <c r="H165" s="68" t="s">
         <v>586</v>
       </c>
       <c r="K165" s="19" t="str">
@@ -8877,22 +8874,22 @@
       </c>
     </row>
     <row r="166" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B166" s="103" t="s">
+      <c r="B166" s="96" t="s">
         <v>326</v>
       </c>
       <c r="C166" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="D166" s="41"/>
-      <c r="E166" s="38">
+      <c r="D166" s="40"/>
+      <c r="E166" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F166" s="38">
+      <c r="F166" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G166" s="37">
+      <c r="G166" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E166-F166</f>
         <v>0</v>
       </c>
@@ -8906,24 +8903,24 @@
       </c>
     </row>
     <row r="167" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B167" s="103" t="s">
+      <c r="B167" s="96" t="s">
         <v>328</v>
       </c>
-      <c r="C167" s="73" t="s">
+      <c r="C167" s="71" t="s">
         <v>329</v>
       </c>
-      <c r="D167" s="74">
+      <c r="D167" s="72">
         <v>5</v>
       </c>
-      <c r="E167" s="75">
+      <c r="E167" s="73">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F167" s="75">
+      <c r="F167" s="73">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G167" s="76">
+      <c r="G167" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E167-F167</f>
         <v>5</v>
       </c>
@@ -8937,24 +8934,24 @@
       </c>
     </row>
     <row r="168" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B168" s="103" t="s">
+      <c r="B168" s="96" t="s">
         <v>332</v>
       </c>
-      <c r="C168" s="79" t="s">
+      <c r="C168" s="77" t="s">
         <v>333</v>
       </c>
-      <c r="D168" s="80">
+      <c r="D168" s="78">
         <v>10</v>
       </c>
-      <c r="E168" s="81">
+      <c r="E168" s="79">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F168" s="81">
+      <c r="F168" s="79">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G168" s="82">
+      <c r="G168" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E168-F168</f>
         <v>10</v>
       </c>
@@ -8968,24 +8965,24 @@
       </c>
     </row>
     <row r="169" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B169" s="103" t="s">
+      <c r="B169" s="96" t="s">
         <v>330</v>
       </c>
-      <c r="C169" s="79" t="s">
+      <c r="C169" s="77" t="s">
         <v>331</v>
       </c>
-      <c r="D169" s="80">
+      <c r="D169" s="78">
         <v>4</v>
       </c>
-      <c r="E169" s="81">
+      <c r="E169" s="79">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F169" s="81">
+      <c r="F169" s="79">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G169" s="82">
+      <c r="G169" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E169-F169</f>
         <v>4</v>
       </c>
@@ -8999,22 +8996,22 @@
       </c>
     </row>
     <row r="170" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B170" s="27" t="s">
+      <c r="B170" s="26" t="s">
         <v>336</v>
       </c>
       <c r="C170" s="25" t="s">
         <v>337</v>
       </c>
-      <c r="D170" s="41"/>
-      <c r="E170" s="38">
+      <c r="D170" s="40"/>
+      <c r="E170" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F170" s="38">
+      <c r="F170" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G170" s="37">
+      <c r="G170" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E170-F170</f>
         <v>0</v>
       </c>
@@ -9028,22 +9025,22 @@
       </c>
     </row>
     <row r="171" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B171" s="27" t="s">
+      <c r="B171" s="26" t="s">
         <v>338</v>
       </c>
       <c r="C171" s="25" t="s">
         <v>339</v>
       </c>
-      <c r="D171" s="41"/>
-      <c r="E171" s="38">
+      <c r="D171" s="40"/>
+      <c r="E171" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F171" s="38">
+      <c r="F171" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G171" s="37">
+      <c r="G171" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E171-F171</f>
         <v>0</v>
       </c>
@@ -9057,22 +9054,22 @@
       </c>
     </row>
     <row r="172" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B172" s="27" t="s">
+      <c r="B172" s="26" t="s">
         <v>340</v>
       </c>
       <c r="C172" s="25" t="s">
         <v>341</v>
       </c>
-      <c r="D172" s="41"/>
-      <c r="E172" s="38">
+      <c r="D172" s="40"/>
+      <c r="E172" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F172" s="38">
+      <c r="F172" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G172" s="37">
+      <c r="G172" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E172-F172</f>
         <v>0</v>
       </c>
@@ -9086,22 +9083,22 @@
       </c>
     </row>
     <row r="173" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B173" s="27" t="s">
+      <c r="B173" s="26" t="s">
         <v>342</v>
       </c>
       <c r="C173" s="25" t="s">
         <v>343</v>
       </c>
-      <c r="D173" s="41"/>
-      <c r="E173" s="38">
+      <c r="D173" s="40"/>
+      <c r="E173" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F173" s="38">
+      <c r="F173" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G173" s="37">
+      <c r="G173" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E173-F173</f>
         <v>0</v>
       </c>
@@ -9115,22 +9112,22 @@
       </c>
     </row>
     <row r="174" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B174" s="27" t="s">
+      <c r="B174" s="26" t="s">
         <v>344</v>
       </c>
       <c r="C174" s="25" t="s">
         <v>345</v>
       </c>
-      <c r="D174" s="41"/>
-      <c r="E174" s="38">
+      <c r="D174" s="40"/>
+      <c r="E174" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F174" s="38">
+      <c r="F174" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G174" s="37">
+      <c r="G174" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E174-F174</f>
         <v>0</v>
       </c>
@@ -9144,24 +9141,24 @@
       </c>
     </row>
     <row r="175" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B175" s="103" t="s">
+      <c r="B175" s="96" t="s">
         <v>346</v>
       </c>
-      <c r="C175" s="73" t="s">
+      <c r="C175" s="71" t="s">
         <v>347</v>
       </c>
-      <c r="D175" s="74">
+      <c r="D175" s="72">
         <v>156</v>
       </c>
-      <c r="E175" s="75">
+      <c r="E175" s="73">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F175" s="75">
+      <c r="F175" s="73">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G175" s="76">
+      <c r="G175" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E175-F175</f>
         <v>156</v>
       </c>
@@ -9175,24 +9172,24 @@
       </c>
     </row>
     <row r="176" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B176" s="103" t="s">
+      <c r="B176" s="96" t="s">
         <v>348</v>
       </c>
-      <c r="C176" s="73" t="s">
+      <c r="C176" s="71" t="s">
         <v>349</v>
       </c>
-      <c r="D176" s="74">
+      <c r="D176" s="72">
         <v>1</v>
       </c>
-      <c r="E176" s="75">
+      <c r="E176" s="73">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F176" s="75">
+      <c r="F176" s="73">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G176" s="76">
+      <c r="G176" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E176-F176</f>
         <v>1</v>
       </c>
@@ -9206,24 +9203,24 @@
       </c>
     </row>
     <row r="177" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B177" s="103" t="s">
+      <c r="B177" s="96" t="s">
         <v>350</v>
       </c>
-      <c r="C177" s="73" t="s">
+      <c r="C177" s="71" t="s">
         <v>351</v>
       </c>
-      <c r="D177" s="74">
+      <c r="D177" s="72">
         <v>42</v>
       </c>
-      <c r="E177" s="75">
+      <c r="E177" s="73">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F177" s="75">
+      <c r="F177" s="73">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G177" s="76">
+      <c r="G177" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E177-F177</f>
         <v>42</v>
       </c>
@@ -9237,24 +9234,24 @@
       </c>
     </row>
     <row r="178" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B178" s="103" t="s">
+      <c r="B178" s="96" t="s">
         <v>352</v>
       </c>
-      <c r="C178" s="73" t="s">
+      <c r="C178" s="71" t="s">
         <v>353</v>
       </c>
-      <c r="D178" s="74">
+      <c r="D178" s="72">
         <v>2</v>
       </c>
-      <c r="E178" s="75">
+      <c r="E178" s="73">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F178" s="75">
+      <c r="F178" s="73">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G178" s="76">
+      <c r="G178" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E178-F178</f>
         <v>2</v>
       </c>
@@ -9268,24 +9265,24 @@
       </c>
     </row>
     <row r="179" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B179" s="103" t="s">
+      <c r="B179" s="96" t="s">
         <v>620</v>
       </c>
-      <c r="C179" s="73" t="s">
+      <c r="C179" s="71" t="s">
         <v>621</v>
       </c>
-      <c r="D179" s="73" t="s">
+      <c r="D179" s="71" t="s">
         <v>622</v>
       </c>
-      <c r="E179" s="75">
+      <c r="E179" s="73">
         <f>SUMIF($J$4:$J$5000, B179, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F179" s="75">
+      <c r="F179" s="73">
         <f>SUMIF($O$4:$O$5000, B179, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G179" s="76">
+      <c r="G179" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E179-F179</f>
         <v>4</v>
       </c>
@@ -9299,22 +9296,22 @@
       </c>
     </row>
     <row r="180" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B180" s="27" t="s">
+      <c r="B180" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C180" s="25" t="s">
         <v>355</v>
       </c>
-      <c r="D180" s="41"/>
-      <c r="E180" s="38">
+      <c r="D180" s="40"/>
+      <c r="E180" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F180" s="38">
+      <c r="F180" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G180" s="37">
+      <c r="G180" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E180-F180</f>
         <v>0</v>
       </c>
@@ -9328,22 +9325,22 @@
       </c>
     </row>
     <row r="181" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B181" s="27" t="s">
+      <c r="B181" s="26" t="s">
         <v>334</v>
       </c>
       <c r="C181" s="25" t="s">
         <v>335</v>
       </c>
-      <c r="D181" s="41"/>
-      <c r="E181" s="38">
+      <c r="D181" s="40"/>
+      <c r="E181" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F181" s="38">
+      <c r="F181" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G181" s="37">
+      <c r="G181" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E181-F181</f>
         <v>0</v>
       </c>
@@ -9357,22 +9354,22 @@
       </c>
     </row>
     <row r="182" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B182" s="27" t="s">
+      <c r="B182" s="26" t="s">
         <v>356</v>
       </c>
       <c r="C182" s="25" t="s">
         <v>317</v>
       </c>
-      <c r="D182" s="41"/>
-      <c r="E182" s="38">
+      <c r="D182" s="40"/>
+      <c r="E182" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F182" s="38">
+      <c r="F182" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G182" s="37">
+      <c r="G182" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E182-F182</f>
         <v>0</v>
       </c>
@@ -9386,22 +9383,22 @@
       </c>
     </row>
     <row r="183" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B183" s="27" t="s">
+      <c r="B183" s="26" t="s">
         <v>357</v>
       </c>
       <c r="C183" s="25" t="s">
         <v>358</v>
       </c>
-      <c r="D183" s="41"/>
-      <c r="E183" s="38">
+      <c r="D183" s="40"/>
+      <c r="E183" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F183" s="38">
+      <c r="F183" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G183" s="37">
+      <c r="G183" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E183-F183</f>
         <v>0</v>
       </c>
@@ -9415,22 +9412,22 @@
       </c>
     </row>
     <row r="184" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B184" s="27" t="s">
+      <c r="B184" s="26" t="s">
         <v>359</v>
       </c>
       <c r="C184" s="25" t="s">
         <v>360</v>
       </c>
-      <c r="D184" s="41"/>
-      <c r="E184" s="38">
+      <c r="D184" s="40"/>
+      <c r="E184" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F184" s="38">
+      <c r="F184" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G184" s="37">
+      <c r="G184" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E184-F184</f>
         <v>0</v>
       </c>
@@ -9444,22 +9441,22 @@
       </c>
     </row>
     <row r="185" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B185" s="27" t="s">
+      <c r="B185" s="26" t="s">
         <v>361</v>
       </c>
       <c r="C185" s="25" t="s">
         <v>362</v>
       </c>
-      <c r="D185" s="41"/>
-      <c r="E185" s="38">
+      <c r="D185" s="40"/>
+      <c r="E185" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F185" s="38">
+      <c r="F185" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G185" s="37">
+      <c r="G185" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E185-F185</f>
         <v>0</v>
       </c>
@@ -9473,22 +9470,22 @@
       </c>
     </row>
     <row r="186" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B186" s="27" t="s">
+      <c r="B186" s="26" t="s">
         <v>363</v>
       </c>
       <c r="C186" s="25" t="s">
         <v>364</v>
       </c>
-      <c r="D186" s="41"/>
-      <c r="E186" s="38">
+      <c r="D186" s="40"/>
+      <c r="E186" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F186" s="38">
+      <c r="F186" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G186" s="37">
+      <c r="G186" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E186-F186</f>
         <v>0</v>
       </c>
@@ -9502,24 +9499,24 @@
       </c>
     </row>
     <row r="187" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B187" s="72" t="s">
+      <c r="B187" s="70" t="s">
         <v>604</v>
       </c>
-      <c r="C187" s="73" t="s">
+      <c r="C187" s="71" t="s">
         <v>366</v>
       </c>
-      <c r="D187" s="74">
+      <c r="D187" s="72">
         <v>1</v>
       </c>
-      <c r="E187" s="75">
+      <c r="E187" s="73">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F187" s="75">
+      <c r="F187" s="73">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G187" s="76">
+      <c r="G187" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E187-F187</f>
         <v>1</v>
       </c>
@@ -9533,22 +9530,22 @@
       </c>
     </row>
     <row r="188" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B188" s="27" t="s">
+      <c r="B188" s="26" t="s">
         <v>375</v>
       </c>
       <c r="C188" s="25" t="s">
         <v>368</v>
       </c>
-      <c r="D188" s="41"/>
-      <c r="E188" s="38">
+      <c r="D188" s="40"/>
+      <c r="E188" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F188" s="38">
+      <c r="F188" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G188" s="37">
+      <c r="G188" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E188-F188</f>
         <v>0</v>
       </c>
@@ -9562,24 +9559,24 @@
       </c>
     </row>
     <row r="189" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B189" s="72" t="s">
+      <c r="B189" s="70" t="s">
         <v>369</v>
       </c>
-      <c r="C189" s="73" t="s">
+      <c r="C189" s="71" t="s">
         <v>370</v>
       </c>
-      <c r="D189" s="74">
+      <c r="D189" s="72">
         <v>4</v>
       </c>
-      <c r="E189" s="75">
+      <c r="E189" s="73">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F189" s="75">
+      <c r="F189" s="73">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G189" s="76">
+      <c r="G189" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E189-F189</f>
         <v>4</v>
       </c>
@@ -9593,24 +9590,24 @@
       </c>
     </row>
     <row r="190" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B190" s="72" t="s">
+      <c r="B190" s="70" t="s">
         <v>371</v>
       </c>
-      <c r="C190" s="73" t="s">
+      <c r="C190" s="71" t="s">
         <v>372</v>
       </c>
-      <c r="D190" s="74">
+      <c r="D190" s="72">
         <v>61</v>
       </c>
-      <c r="E190" s="75">
+      <c r="E190" s="73">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F190" s="75">
+      <c r="F190" s="73">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G190" s="76">
+      <c r="G190" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E190-F190</f>
         <v>61</v>
       </c>
@@ -9624,22 +9621,22 @@
       </c>
     </row>
     <row r="191" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B191" s="27" t="s">
+      <c r="B191" s="26" t="s">
         <v>373</v>
       </c>
       <c r="C191" s="25" t="s">
         <v>374</v>
       </c>
-      <c r="D191" s="41"/>
-      <c r="E191" s="38">
+      <c r="D191" s="40"/>
+      <c r="E191" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F191" s="38">
+      <c r="F191" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G191" s="37">
+      <c r="G191" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E191-F191</f>
         <v>0</v>
       </c>
@@ -9652,89 +9649,89 @@
         <v/>
       </c>
     </row>
-    <row r="192" spans="2:16" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B192" s="27" t="s">
+    <row r="192" spans="2:16" s="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B192" s="26" t="s">
         <v>375</v>
       </c>
       <c r="C192" s="25" t="s">
         <v>366</v>
       </c>
-      <c r="D192" s="41"/>
-      <c r="E192" s="38">
+      <c r="D192" s="40"/>
+      <c r="E192" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F192" s="38">
+      <c r="F192" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G192" s="37">
+      <c r="G192" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E192-F192</f>
         <v>0</v>
       </c>
       <c r="H192"/>
-      <c r="K192" s="83" t="str">
+      <c r="K192" s="81" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P192" s="83" t="str">
+      <c r="P192" s="81" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="193" spans="2:16" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B193" s="27" t="s">
+    <row r="193" spans="2:16" s="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B193" s="26" t="s">
         <v>376</v>
       </c>
       <c r="C193" s="25" t="s">
         <v>377</v>
       </c>
-      <c r="D193" s="41"/>
-      <c r="E193" s="38">
+      <c r="D193" s="40"/>
+      <c r="E193" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F193" s="38">
+      <c r="F193" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G193" s="37">
+      <c r="G193" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E193-F193</f>
         <v>0</v>
       </c>
       <c r="H193"/>
-      <c r="K193" s="83" t="str">
+      <c r="K193" s="81" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P193" s="83" t="str">
+      <c r="P193" s="81" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="194" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B194" s="78" t="s">
+      <c r="B194" s="76" t="s">
         <v>378</v>
       </c>
-      <c r="C194" s="79" t="s">
+      <c r="C194" s="77" t="s">
         <v>379</v>
       </c>
-      <c r="D194" s="80">
+      <c r="D194" s="78">
         <v>165</v>
       </c>
-      <c r="E194" s="81">
+      <c r="E194" s="79">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F194" s="81">
+      <c r="F194" s="79">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G194" s="82">
+      <c r="G194" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E194-F194</f>
         <v>165</v>
       </c>
-      <c r="H194" s="69"/>
+      <c r="H194" s="67"/>
       <c r="K194" s="19" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9745,28 +9742,28 @@
       </c>
     </row>
     <row r="195" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B195" s="78" t="s">
+      <c r="B195" s="76" t="s">
         <v>380</v>
       </c>
-      <c r="C195" s="79" t="s">
+      <c r="C195" s="77" t="s">
         <v>381</v>
       </c>
-      <c r="D195" s="80">
+      <c r="D195" s="78">
         <v>329</v>
       </c>
-      <c r="E195" s="81">
+      <c r="E195" s="79">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F195" s="81">
+      <c r="F195" s="79">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G195" s="82">
+      <c r="G195" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E195-F195</f>
         <v>329</v>
       </c>
-      <c r="H195" s="69"/>
+      <c r="H195" s="67"/>
       <c r="K195" s="19" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9777,22 +9774,22 @@
       </c>
     </row>
     <row r="196" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B196" s="27" t="s">
+      <c r="B196" s="26" t="s">
         <v>382</v>
       </c>
       <c r="C196" s="25" t="s">
         <v>383</v>
       </c>
-      <c r="D196" s="41"/>
-      <c r="E196" s="38">
+      <c r="D196" s="40"/>
+      <c r="E196" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F196" s="38">
+      <c r="F196" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G196" s="37">
+      <c r="G196" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E196-F196</f>
         <v>0</v>
       </c>
@@ -9806,22 +9803,22 @@
       </c>
     </row>
     <row r="197" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B197" s="27" t="s">
+      <c r="B197" s="26" t="s">
         <v>384</v>
       </c>
       <c r="C197" s="25" t="s">
         <v>385</v>
       </c>
-      <c r="D197" s="41"/>
-      <c r="E197" s="38">
+      <c r="D197" s="40"/>
+      <c r="E197" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F197" s="38">
+      <c r="F197" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G197" s="37">
+      <c r="G197" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E197-F197</f>
         <v>0</v>
       </c>
@@ -9835,22 +9832,22 @@
       </c>
     </row>
     <row r="198" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B198" s="27" t="s">
+      <c r="B198" s="26" t="s">
         <v>386</v>
       </c>
       <c r="C198" s="25" t="s">
         <v>387</v>
       </c>
-      <c r="D198" s="41"/>
-      <c r="E198" s="38">
+      <c r="D198" s="40"/>
+      <c r="E198" s="37">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F198" s="38">
+      <c r="F198" s="37">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G198" s="37">
+      <c r="G198" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E198-F198</f>
         <v>0</v>
       </c>
@@ -9864,22 +9861,22 @@
       </c>
     </row>
     <row r="199" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B199" s="27" t="s">
+      <c r="B199" s="26" t="s">
         <v>388</v>
       </c>
       <c r="C199" s="25" t="s">
         <v>389</v>
       </c>
-      <c r="D199" s="41"/>
-      <c r="E199" s="38">
+      <c r="D199" s="40"/>
+      <c r="E199" s="37">
         <f t="shared" ref="E199:E262" si="13">SUMIF($J$4:$J$5000, B199, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F199" s="38">
+      <c r="F199" s="37">
         <f t="shared" ref="F199:F262" si="14">SUMIF($O$4:$O$5000, B199, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G199" s="37">
+      <c r="G199" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E199-F199</f>
         <v>0</v>
       </c>
@@ -9893,22 +9890,22 @@
       </c>
     </row>
     <row r="200" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B200" s="27" t="s">
+      <c r="B200" s="26" t="s">
         <v>390</v>
       </c>
       <c r="C200" s="25" t="s">
         <v>391</v>
       </c>
-      <c r="D200" s="41"/>
-      <c r="E200" s="38">
+      <c r="D200" s="40"/>
+      <c r="E200" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F200" s="38">
+      <c r="F200" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G200" s="37">
+      <c r="G200" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E200-F200</f>
         <v>0</v>
       </c>
@@ -9922,22 +9919,22 @@
       </c>
     </row>
     <row r="201" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B201" s="27" t="s">
+      <c r="B201" s="26" t="s">
         <v>392</v>
       </c>
       <c r="C201" s="25" t="s">
         <v>393</v>
       </c>
-      <c r="D201" s="41"/>
-      <c r="E201" s="38">
+      <c r="D201" s="40"/>
+      <c r="E201" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F201" s="38">
+      <c r="F201" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G201" s="37">
+      <c r="G201" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E201-F201</f>
         <v>0</v>
       </c>
@@ -9951,22 +9948,22 @@
       </c>
     </row>
     <row r="202" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B202" s="27" t="s">
+      <c r="B202" s="26" t="s">
         <v>398</v>
       </c>
       <c r="C202" s="25" t="s">
         <v>399</v>
       </c>
-      <c r="D202" s="41"/>
-      <c r="E202" s="38">
+      <c r="D202" s="40"/>
+      <c r="E202" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F202" s="38">
+      <c r="F202" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G202" s="37">
+      <c r="G202" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E202-F202</f>
         <v>0</v>
       </c>
@@ -9980,22 +9977,22 @@
       </c>
     </row>
     <row r="203" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B203" s="27" t="s">
+      <c r="B203" s="26" t="s">
         <v>400</v>
       </c>
       <c r="C203" s="25" t="s">
         <v>401</v>
       </c>
-      <c r="D203" s="41"/>
-      <c r="E203" s="38">
+      <c r="D203" s="40"/>
+      <c r="E203" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F203" s="38">
+      <c r="F203" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G203" s="37">
+      <c r="G203" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E203-F203</f>
         <v>0</v>
       </c>
@@ -10009,22 +10006,22 @@
       </c>
     </row>
     <row r="204" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B204" s="27" t="s">
+      <c r="B204" s="26" t="s">
         <v>402</v>
       </c>
       <c r="C204" s="25" t="s">
         <v>403</v>
       </c>
-      <c r="D204" s="41"/>
-      <c r="E204" s="38">
+      <c r="D204" s="40"/>
+      <c r="E204" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F204" s="38">
+      <c r="F204" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G204" s="37">
+      <c r="G204" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E204-F204</f>
         <v>0</v>
       </c>
@@ -10038,22 +10035,22 @@
       </c>
     </row>
     <row r="205" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B205" s="103" t="s">
+      <c r="B205" s="96" t="s">
         <v>404</v>
       </c>
       <c r="C205" s="25" t="s">
         <v>405</v>
       </c>
-      <c r="D205" s="41"/>
-      <c r="E205" s="38">
+      <c r="D205" s="40"/>
+      <c r="E205" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F205" s="38">
+      <c r="F205" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G205" s="37">
+      <c r="G205" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E205-F205</f>
         <v>0</v>
       </c>
@@ -10067,24 +10064,24 @@
       </c>
     </row>
     <row r="206" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B206" s="103" t="s">
+      <c r="B206" s="96" t="s">
         <v>406</v>
       </c>
-      <c r="C206" s="73" t="s">
+      <c r="C206" s="71" t="s">
         <v>407</v>
       </c>
-      <c r="D206" s="74">
+      <c r="D206" s="72">
         <v>50</v>
       </c>
-      <c r="E206" s="75">
+      <c r="E206" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F206" s="75">
+      <c r="F206" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G206" s="76">
+      <c r="G206" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E206-F206</f>
         <v>50</v>
       </c>
@@ -10098,24 +10095,24 @@
       </c>
     </row>
     <row r="207" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B207" s="103" t="s">
+      <c r="B207" s="96" t="s">
         <v>408</v>
       </c>
-      <c r="C207" s="73" t="s">
+      <c r="C207" s="71" t="s">
         <v>409</v>
       </c>
-      <c r="D207" s="74">
+      <c r="D207" s="72">
         <v>30</v>
       </c>
-      <c r="E207" s="75">
+      <c r="E207" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F207" s="75">
+      <c r="F207" s="73">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
-      <c r="G207" s="76">
+      <c r="G207" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E207-F207</f>
         <v>10</v>
       </c>
@@ -10132,22 +10129,22 @@
       </c>
     </row>
     <row r="208" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B208" s="103" t="s">
+      <c r="B208" s="96" t="s">
         <v>410</v>
       </c>
       <c r="C208" s="25" t="s">
         <v>411</v>
       </c>
-      <c r="D208" s="41"/>
-      <c r="E208" s="38">
+      <c r="D208" s="40"/>
+      <c r="E208" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F208" s="38">
+      <c r="F208" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G208" s="37">
+      <c r="G208" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E208-F208</f>
         <v>0</v>
       </c>
@@ -10161,24 +10158,24 @@
       </c>
     </row>
     <row r="209" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B209" s="103" t="s">
+      <c r="B209" s="96" t="s">
         <v>412</v>
       </c>
-      <c r="C209" s="73" t="s">
+      <c r="C209" s="71" t="s">
         <v>413</v>
       </c>
-      <c r="D209" s="74">
+      <c r="D209" s="72">
         <v>70</v>
       </c>
-      <c r="E209" s="75">
+      <c r="E209" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F209" s="75">
+      <c r="F209" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G209" s="76">
+      <c r="G209" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E209-F209</f>
         <v>70</v>
       </c>
@@ -10192,24 +10189,24 @@
       </c>
     </row>
     <row r="210" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B210" s="103" t="s">
+      <c r="B210" s="96" t="s">
         <v>414</v>
       </c>
-      <c r="C210" s="73" t="s">
+      <c r="C210" s="71" t="s">
         <v>415</v>
       </c>
-      <c r="D210" s="74">
+      <c r="D210" s="72">
         <v>80</v>
       </c>
-      <c r="E210" s="75">
+      <c r="E210" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F210" s="75">
+      <c r="F210" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G210" s="76">
+      <c r="G210" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E210-F210</f>
         <v>80</v>
       </c>
@@ -10223,22 +10220,22 @@
       </c>
     </row>
     <row r="211" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B211" s="103" t="s">
+      <c r="B211" s="96" t="s">
         <v>416</v>
       </c>
       <c r="C211" s="25" t="s">
         <v>417</v>
       </c>
-      <c r="D211" s="41"/>
-      <c r="E211" s="38">
+      <c r="D211" s="40"/>
+      <c r="E211" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F211" s="38">
+      <c r="F211" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G211" s="37">
+      <c r="G211" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E211-F211</f>
         <v>0</v>
       </c>
@@ -10252,24 +10249,24 @@
       </c>
     </row>
     <row r="212" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B212" s="103" t="s">
+      <c r="B212" s="96" t="s">
         <v>418</v>
       </c>
-      <c r="C212" s="73" t="s">
+      <c r="C212" s="71" t="s">
         <v>419</v>
       </c>
-      <c r="D212" s="74">
+      <c r="D212" s="72">
         <v>50</v>
       </c>
-      <c r="E212" s="75">
+      <c r="E212" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F212" s="75">
+      <c r="F212" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G212" s="76">
+      <c r="G212" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E212-F212</f>
         <v>50</v>
       </c>
@@ -10283,22 +10280,22 @@
       </c>
     </row>
     <row r="213" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B213" s="103" t="s">
+      <c r="B213" s="96" t="s">
         <v>420</v>
       </c>
       <c r="C213" s="25" t="s">
         <v>421</v>
       </c>
-      <c r="D213" s="41"/>
-      <c r="E213" s="38">
+      <c r="D213" s="40"/>
+      <c r="E213" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F213" s="38">
+      <c r="F213" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G213" s="37">
+      <c r="G213" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E213-F213</f>
         <v>0</v>
       </c>
@@ -10312,22 +10309,22 @@
       </c>
     </row>
     <row r="214" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B214" s="103" t="s">
+      <c r="B214" s="96" t="s">
         <v>422</v>
       </c>
       <c r="C214" s="25" t="s">
         <v>423</v>
       </c>
-      <c r="D214" s="41"/>
-      <c r="E214" s="38">
+      <c r="D214" s="40"/>
+      <c r="E214" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F214" s="38">
+      <c r="F214" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G214" s="37">
+      <c r="G214" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E214-F214</f>
         <v>0</v>
       </c>
@@ -10341,22 +10338,22 @@
       </c>
     </row>
     <row r="215" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B215" s="27" t="s">
+      <c r="B215" s="26" t="s">
         <v>424</v>
       </c>
       <c r="C215" s="25" t="s">
         <v>425</v>
       </c>
-      <c r="D215" s="41"/>
-      <c r="E215" s="38">
+      <c r="D215" s="40"/>
+      <c r="E215" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F215" s="38">
+      <c r="F215" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G215" s="37">
+      <c r="G215" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E215-F215</f>
         <v>0</v>
       </c>
@@ -10370,22 +10367,22 @@
       </c>
     </row>
     <row r="216" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B216" s="27" t="s">
+      <c r="B216" s="26" t="s">
         <v>426</v>
       </c>
       <c r="C216" s="25" t="s">
         <v>427</v>
       </c>
-      <c r="D216" s="41"/>
-      <c r="E216" s="38">
+      <c r="D216" s="40"/>
+      <c r="E216" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F216" s="38">
+      <c r="F216" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G216" s="37">
+      <c r="G216" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E216-F216</f>
         <v>0</v>
       </c>
@@ -10399,22 +10396,22 @@
       </c>
     </row>
     <row r="217" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B217" s="103" t="s">
+      <c r="B217" s="96" t="s">
         <v>575</v>
       </c>
-      <c r="C217" s="44"/>
-      <c r="D217" s="49">
+      <c r="C217" s="43"/>
+      <c r="D217" s="48">
         <v>20</v>
       </c>
-      <c r="E217" s="46">
+      <c r="E217" s="45">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F217" s="46">
+      <c r="F217" s="45">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G217" s="47">
+      <c r="G217" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E217-F217</f>
         <v>20</v>
       </c>
@@ -10428,22 +10425,22 @@
       </c>
     </row>
     <row r="218" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B218" s="103" t="s">
+      <c r="B218" s="96" t="s">
         <v>428</v>
       </c>
       <c r="C218" s="25" t="s">
         <v>429</v>
       </c>
-      <c r="D218" s="41"/>
-      <c r="E218" s="38">
+      <c r="D218" s="40"/>
+      <c r="E218" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F218" s="38">
+      <c r="F218" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G218" s="37">
+      <c r="G218" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E218-F218</f>
         <v>0</v>
       </c>
@@ -10457,22 +10454,22 @@
       </c>
     </row>
     <row r="219" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B219" s="103" t="s">
+      <c r="B219" s="96" t="s">
         <v>430</v>
       </c>
       <c r="C219" s="25" t="s">
         <v>431</v>
       </c>
-      <c r="D219" s="41"/>
-      <c r="E219" s="38">
+      <c r="D219" s="40"/>
+      <c r="E219" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F219" s="38">
+      <c r="F219" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G219" s="37">
+      <c r="G219" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E219-F219</f>
         <v>0</v>
       </c>
@@ -10486,22 +10483,22 @@
       </c>
     </row>
     <row r="220" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B220" s="27" t="s">
+      <c r="B220" s="26" t="s">
         <v>432</v>
       </c>
       <c r="C220" s="25" t="s">
         <v>433</v>
       </c>
-      <c r="D220" s="41"/>
-      <c r="E220" s="38">
+      <c r="D220" s="40"/>
+      <c r="E220" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F220" s="38">
+      <c r="F220" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G220" s="37">
+      <c r="G220" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E220-F220</f>
         <v>0</v>
       </c>
@@ -10515,22 +10512,22 @@
       </c>
     </row>
     <row r="221" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B221" s="27" t="s">
+      <c r="B221" s="26" t="s">
         <v>434</v>
       </c>
       <c r="C221" s="25" t="s">
         <v>435</v>
       </c>
-      <c r="D221" s="41"/>
-      <c r="E221" s="38">
+      <c r="D221" s="40"/>
+      <c r="E221" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F221" s="38">
+      <c r="F221" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G221" s="37">
+      <c r="G221" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E221-F221</f>
         <v>0</v>
       </c>
@@ -10544,24 +10541,24 @@
       </c>
     </row>
     <row r="222" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B222" s="103" t="s">
+      <c r="B222" s="96" t="s">
         <v>436</v>
       </c>
-      <c r="C222" s="44" t="s">
+      <c r="C222" s="43" t="s">
         <v>437</v>
       </c>
-      <c r="D222" s="45">
+      <c r="D222" s="44">
         <v>480</v>
       </c>
-      <c r="E222" s="46">
+      <c r="E222" s="45">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F222" s="46">
+      <c r="F222" s="45">
         <f t="shared" si="14"/>
         <v>210</v>
       </c>
-      <c r="G222" s="47">
+      <c r="G222" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E222-F222</f>
         <v>270</v>
       </c>
@@ -10575,24 +10572,24 @@
       </c>
     </row>
     <row r="223" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B223" s="103" t="s">
+      <c r="B223" s="96" t="s">
         <v>438</v>
       </c>
-      <c r="C223" s="44" t="s">
+      <c r="C223" s="43" t="s">
         <v>439</v>
       </c>
-      <c r="D223" s="45">
+      <c r="D223" s="44">
         <v>119</v>
       </c>
-      <c r="E223" s="46">
+      <c r="E223" s="45">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F223" s="46">
+      <c r="F223" s="45">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G223" s="47">
+      <c r="G223" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E223-F223</f>
         <v>119</v>
       </c>
@@ -10606,24 +10603,24 @@
       </c>
     </row>
     <row r="224" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B224" s="103" t="s">
+      <c r="B224" s="96" t="s">
         <v>440</v>
       </c>
-      <c r="C224" s="44" t="s">
+      <c r="C224" s="43" t="s">
         <v>441</v>
       </c>
-      <c r="D224" s="45">
+      <c r="D224" s="44">
         <v>89</v>
       </c>
-      <c r="E224" s="46">
+      <c r="E224" s="45">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F224" s="46">
+      <c r="F224" s="45">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G224" s="47">
+      <c r="G224" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E224-F224</f>
         <v>89</v>
       </c>
@@ -10637,22 +10634,22 @@
       </c>
     </row>
     <row r="225" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B225" s="27" t="s">
+      <c r="B225" s="26" t="s">
         <v>442</v>
       </c>
       <c r="C225" s="25" t="s">
         <v>443</v>
       </c>
-      <c r="D225" s="41"/>
-      <c r="E225" s="38">
+      <c r="D225" s="40"/>
+      <c r="E225" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F225" s="38">
+      <c r="F225" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G225" s="37">
+      <c r="G225" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E225-F225</f>
         <v>0</v>
       </c>
@@ -10666,22 +10663,22 @@
       </c>
     </row>
     <row r="226" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B226" s="27" t="s">
+      <c r="B226" s="26" t="s">
         <v>444</v>
       </c>
       <c r="C226" s="25" t="s">
         <v>445</v>
       </c>
-      <c r="D226" s="41"/>
-      <c r="E226" s="38">
+      <c r="D226" s="40"/>
+      <c r="E226" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F226" s="38">
+      <c r="F226" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G226" s="37">
+      <c r="G226" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E226-F226</f>
         <v>0</v>
       </c>
@@ -10695,22 +10692,22 @@
       </c>
     </row>
     <row r="227" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B227" s="103" t="s">
+      <c r="B227" s="96" t="s">
         <v>446</v>
       </c>
       <c r="C227" s="25" t="s">
         <v>447</v>
       </c>
-      <c r="D227" s="41"/>
-      <c r="E227" s="38">
+      <c r="D227" s="40"/>
+      <c r="E227" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F227" s="38">
+      <c r="F227" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G227" s="37">
+      <c r="G227" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E227-F227</f>
         <v>0</v>
       </c>
@@ -10724,24 +10721,24 @@
       </c>
     </row>
     <row r="228" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B228" s="103" t="s">
+      <c r="B228" s="96" t="s">
         <v>448</v>
       </c>
-      <c r="C228" s="60" t="s">
+      <c r="C228" s="58" t="s">
         <v>449</v>
       </c>
-      <c r="D228" s="58">
+      <c r="D228" s="57">
         <v>700</v>
       </c>
-      <c r="E228" s="61">
+      <c r="E228" s="59">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F228" s="61">
+      <c r="F228" s="59">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G228" s="62">
+      <c r="G228" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E228-F228</f>
         <v>700</v>
       </c>
@@ -10755,28 +10752,28 @@
       </c>
     </row>
     <row r="229" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B229" s="103" t="s">
+      <c r="B229" s="96" t="s">
         <v>450</v>
       </c>
-      <c r="C229" s="60" t="s">
+      <c r="C229" s="58" t="s">
         <v>451</v>
       </c>
-      <c r="D229" s="58">
+      <c r="D229" s="57">
         <v>445</v>
       </c>
-      <c r="E229" s="61">
+      <c r="E229" s="59">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F229" s="61">
+      <c r="F229" s="59">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G229" s="62">
+      <c r="G229" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E229-F229</f>
         <v>445</v>
       </c>
-      <c r="H229" s="64" t="s">
+      <c r="H229" s="62" t="s">
         <v>581</v>
       </c>
       <c r="K229" s="19" t="str">
@@ -10789,24 +10786,24 @@
       </c>
     </row>
     <row r="230" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B230" s="103" t="s">
+      <c r="B230" s="96" t="s">
         <v>452</v>
       </c>
-      <c r="C230" s="79" t="s">
+      <c r="C230" s="77" t="s">
         <v>453</v>
       </c>
-      <c r="D230" s="80">
+      <c r="D230" s="78">
         <v>958</v>
       </c>
-      <c r="E230" s="81">
+      <c r="E230" s="79">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F230" s="81">
+      <c r="F230" s="79">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G230" s="82">
+      <c r="G230" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E230-F230</f>
         <v>958</v>
       </c>
@@ -10820,24 +10817,24 @@
       </c>
     </row>
     <row r="231" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B231" s="103" t="s">
+      <c r="B231" s="96" t="s">
         <v>454</v>
       </c>
-      <c r="C231" s="73" t="s">
+      <c r="C231" s="71" t="s">
         <v>455</v>
       </c>
-      <c r="D231" s="74">
+      <c r="D231" s="72">
         <v>14</v>
       </c>
-      <c r="E231" s="75">
+      <c r="E231" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F231" s="75">
+      <c r="F231" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G231" s="76">
+      <c r="G231" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E231-F231</f>
         <v>14</v>
       </c>
@@ -10851,22 +10848,22 @@
       </c>
     </row>
     <row r="232" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B232" s="103" t="s">
+      <c r="B232" s="96" t="s">
         <v>456</v>
       </c>
       <c r="C232" s="25" t="s">
         <v>457</v>
       </c>
-      <c r="D232" s="41"/>
-      <c r="E232" s="38">
+      <c r="D232" s="40"/>
+      <c r="E232" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F232" s="38">
+      <c r="F232" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G232" s="37">
+      <c r="G232" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E232-F232</f>
         <v>0</v>
       </c>
@@ -10880,24 +10877,24 @@
       </c>
     </row>
     <row r="233" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B233" s="103" t="s">
+      <c r="B233" s="96" t="s">
         <v>458</v>
       </c>
-      <c r="C233" s="73" t="s">
+      <c r="C233" s="71" t="s">
         <v>459</v>
       </c>
-      <c r="D233" s="74">
+      <c r="D233" s="72">
         <v>30</v>
       </c>
-      <c r="E233" s="75">
+      <c r="E233" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F233" s="75">
+      <c r="F233" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G233" s="76">
+      <c r="G233" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E233-F233</f>
         <v>30</v>
       </c>
@@ -10911,24 +10908,24 @@
       </c>
     </row>
     <row r="234" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B234" s="103" t="s">
+      <c r="B234" s="96" t="s">
         <v>460</v>
       </c>
-      <c r="C234" s="73" t="s">
+      <c r="C234" s="71" t="s">
         <v>461</v>
       </c>
-      <c r="D234" s="74">
+      <c r="D234" s="72">
         <v>19</v>
       </c>
-      <c r="E234" s="75">
+      <c r="E234" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F234" s="75">
+      <c r="F234" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G234" s="76">
+      <c r="G234" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E234-F234</f>
         <v>19</v>
       </c>
@@ -10942,24 +10939,24 @@
       </c>
     </row>
     <row r="235" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B235" s="103" t="s">
+      <c r="B235" s="96" t="s">
         <v>462</v>
       </c>
-      <c r="C235" s="44" t="s">
+      <c r="C235" s="43" t="s">
         <v>463</v>
       </c>
-      <c r="D235" s="45">
+      <c r="D235" s="44">
         <v>113</v>
       </c>
-      <c r="E235" s="46">
+      <c r="E235" s="45">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F235" s="46">
+      <c r="F235" s="45">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G235" s="47">
+      <c r="G235" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E235-F235</f>
         <v>113</v>
       </c>
@@ -10973,22 +10970,22 @@
       </c>
     </row>
     <row r="236" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B236" s="103" t="s">
+      <c r="B236" s="96" t="s">
         <v>464</v>
       </c>
       <c r="C236" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="D236" s="41"/>
-      <c r="E236" s="38">
+      <c r="D236" s="40"/>
+      <c r="E236" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F236" s="38">
+      <c r="F236" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G236" s="37">
+      <c r="G236" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E236-F236</f>
         <v>0</v>
       </c>
@@ -11002,24 +10999,24 @@
       </c>
     </row>
     <row r="237" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B237" s="103" t="s">
+      <c r="B237" s="96" t="s">
         <v>466</v>
       </c>
-      <c r="C237" s="73" t="s">
+      <c r="C237" s="71" t="s">
         <v>467</v>
       </c>
-      <c r="D237" s="74">
+      <c r="D237" s="72">
         <v>50</v>
       </c>
-      <c r="E237" s="75">
+      <c r="E237" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F237" s="75">
+      <c r="F237" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G237" s="76">
+      <c r="G237" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E237-F237</f>
         <v>50</v>
       </c>
@@ -11033,24 +11030,24 @@
       </c>
     </row>
     <row r="238" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B238" s="103" t="s">
+      <c r="B238" s="96" t="s">
         <v>468</v>
       </c>
-      <c r="C238" s="73" t="s">
+      <c r="C238" s="71" t="s">
         <v>469</v>
       </c>
-      <c r="D238" s="74">
+      <c r="D238" s="72">
         <v>50</v>
       </c>
-      <c r="E238" s="75">
+      <c r="E238" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F238" s="75">
+      <c r="F238" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G238" s="76">
+      <c r="G238" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E238-F238</f>
         <v>50</v>
       </c>
@@ -11064,22 +11061,22 @@
       </c>
     </row>
     <row r="239" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B239" s="103" t="s">
+      <c r="B239" s="96" t="s">
         <v>470</v>
       </c>
-      <c r="C239" s="73" t="s">
+      <c r="C239" s="71" t="s">
         <v>471</v>
       </c>
-      <c r="D239" s="74"/>
-      <c r="E239" s="75">
+      <c r="D239" s="72"/>
+      <c r="E239" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F239" s="75">
+      <c r="F239" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G239" s="76">
+      <c r="G239" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E239-F239</f>
         <v>0</v>
       </c>
@@ -11093,24 +11090,24 @@
       </c>
     </row>
     <row r="240" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B240" s="103" t="s">
+      <c r="B240" s="96" t="s">
         <v>472</v>
       </c>
-      <c r="C240" s="44" t="s">
+      <c r="C240" s="43" t="s">
         <v>473</v>
       </c>
-      <c r="D240" s="45">
+      <c r="D240" s="44">
         <v>34</v>
       </c>
-      <c r="E240" s="46">
+      <c r="E240" s="45">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F240" s="46">
+      <c r="F240" s="45">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G240" s="47">
+      <c r="G240" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E240-F240</f>
         <v>34</v>
       </c>
@@ -11124,24 +11121,24 @@
       </c>
     </row>
     <row r="241" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B241" s="72" t="s">
+      <c r="B241" s="96" t="s">
         <v>591</v>
       </c>
-      <c r="C241" s="73" t="s">
+      <c r="C241" s="71" t="s">
         <v>395</v>
       </c>
-      <c r="D241" s="74">
+      <c r="D241" s="72">
         <v>1000</v>
       </c>
-      <c r="E241" s="75">
+      <c r="E241" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F241" s="75">
+      <c r="F241" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G241" s="76">
+      <c r="G241" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E241-F241</f>
         <v>1000</v>
       </c>
@@ -11155,22 +11152,22 @@
       </c>
     </row>
     <row r="242" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B242" s="27" t="s">
+      <c r="B242" s="26" t="s">
         <v>474</v>
       </c>
       <c r="C242" s="25" t="s">
         <v>475</v>
       </c>
-      <c r="D242" s="41"/>
-      <c r="E242" s="38">
+      <c r="D242" s="40"/>
+      <c r="E242" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F242" s="38">
+      <c r="F242" s="37">
         <f t="shared" si="14"/>
         <v>125</v>
       </c>
-      <c r="G242" s="37">
+      <c r="G242" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E242-F242</f>
         <v>-125</v>
       </c>
@@ -11184,24 +11181,24 @@
       </c>
     </row>
     <row r="243" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B243" s="103" t="s">
+      <c r="B243" s="96" t="s">
         <v>476</v>
       </c>
-      <c r="C243" s="44" t="s">
+      <c r="C243" s="43" t="s">
         <v>477</v>
       </c>
-      <c r="D243" s="45">
+      <c r="D243" s="44">
         <v>210</v>
       </c>
-      <c r="E243" s="46">
+      <c r="E243" s="45">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F243" s="46">
+      <c r="F243" s="45">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G243" s="47">
+      <c r="G243" s="46">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E243-F243</f>
         <v>210</v>
       </c>
@@ -11215,24 +11212,24 @@
       </c>
     </row>
     <row r="244" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B244" s="72" t="s">
+      <c r="B244" s="96" t="s">
         <v>589</v>
       </c>
-      <c r="C244" s="73" t="s">
+      <c r="C244" s="71" t="s">
         <v>397</v>
       </c>
-      <c r="D244" s="74">
+      <c r="D244" s="72">
         <v>100</v>
       </c>
-      <c r="E244" s="75">
+      <c r="E244" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F244" s="75">
+      <c r="F244" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G244" s="76">
+      <c r="G244" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E244-F244</f>
         <v>100</v>
       </c>
@@ -11246,24 +11243,24 @@
       </c>
     </row>
     <row r="245" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B245" s="103" t="s">
+      <c r="B245" s="96" t="s">
         <v>478</v>
       </c>
-      <c r="C245" s="73" t="s">
+      <c r="C245" s="71" t="s">
         <v>479</v>
       </c>
-      <c r="D245" s="74">
+      <c r="D245" s="72">
         <v>32</v>
       </c>
-      <c r="E245" s="75">
+      <c r="E245" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F245" s="75">
+      <c r="F245" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G245" s="76">
+      <c r="G245" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E245-F245</f>
         <v>32</v>
       </c>
@@ -11277,24 +11274,24 @@
       </c>
     </row>
     <row r="246" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B246" s="103" t="s">
+      <c r="B246" s="96" t="s">
         <v>480</v>
       </c>
-      <c r="C246" s="73" t="s">
+      <c r="C246" s="71" t="s">
         <v>481</v>
       </c>
-      <c r="D246" s="74">
+      <c r="D246" s="72">
         <v>4</v>
       </c>
-      <c r="E246" s="75">
+      <c r="E246" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F246" s="75">
+      <c r="F246" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G246" s="76">
+      <c r="G246" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E246-F246</f>
         <v>4</v>
       </c>
@@ -11308,22 +11305,22 @@
       </c>
     </row>
     <row r="247" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B247" s="27" t="s">
+      <c r="B247" s="26" t="s">
         <v>482</v>
       </c>
       <c r="C247" s="25" t="s">
         <v>483</v>
       </c>
-      <c r="D247" s="41"/>
-      <c r="E247" s="38">
+      <c r="D247" s="40"/>
+      <c r="E247" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F247" s="38">
+      <c r="F247" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G247" s="37">
+      <c r="G247" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E247-F247</f>
         <v>0</v>
       </c>
@@ -11337,24 +11334,24 @@
       </c>
     </row>
     <row r="248" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B248" s="103" t="s">
+      <c r="B248" s="96" t="s">
         <v>484</v>
       </c>
-      <c r="C248" s="60" t="s">
+      <c r="C248" s="58" t="s">
         <v>485</v>
       </c>
-      <c r="D248" s="58">
+      <c r="D248" s="57">
         <v>32</v>
       </c>
-      <c r="E248" s="61">
+      <c r="E248" s="59">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F248" s="61">
+      <c r="F248" s="59">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G248" s="62">
+      <c r="G248" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E248-F248</f>
         <v>32</v>
       </c>
@@ -11371,24 +11368,24 @@
       </c>
     </row>
     <row r="249" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B249" s="103" t="s">
+      <c r="B249" s="96" t="s">
         <v>486</v>
       </c>
-      <c r="C249" s="73" t="s">
+      <c r="C249" s="71" t="s">
         <v>487</v>
       </c>
-      <c r="D249" s="74">
+      <c r="D249" s="72">
         <v>30</v>
       </c>
-      <c r="E249" s="75">
+      <c r="E249" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F249" s="75">
+      <c r="F249" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G249" s="76">
+      <c r="G249" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E249-F249</f>
         <v>30</v>
       </c>
@@ -11402,24 +11399,24 @@
       </c>
     </row>
     <row r="250" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B250" s="103" t="s">
+      <c r="B250" s="96" t="s">
         <v>488</v>
       </c>
-      <c r="C250" s="73" t="s">
+      <c r="C250" s="71" t="s">
         <v>489</v>
       </c>
-      <c r="D250" s="74">
+      <c r="D250" s="72">
         <v>30</v>
       </c>
-      <c r="E250" s="75">
+      <c r="E250" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F250" s="75">
+      <c r="F250" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G250" s="76">
+      <c r="G250" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E250-F250</f>
         <v>30</v>
       </c>
@@ -11433,22 +11430,22 @@
       </c>
     </row>
     <row r="251" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B251" s="103" t="s">
+      <c r="B251" s="96" t="s">
         <v>490</v>
       </c>
       <c r="C251" s="25" t="s">
         <v>491</v>
       </c>
-      <c r="D251" s="41"/>
-      <c r="E251" s="38">
+      <c r="D251" s="40"/>
+      <c r="E251" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F251" s="38">
+      <c r="F251" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G251" s="37">
+      <c r="G251" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E251-F251</f>
         <v>0</v>
       </c>
@@ -11462,22 +11459,22 @@
       </c>
     </row>
     <row r="252" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B252" s="103" t="s">
+      <c r="B252" s="96" t="s">
         <v>492</v>
       </c>
       <c r="C252" s="25" t="s">
         <v>493</v>
       </c>
-      <c r="D252" s="41"/>
-      <c r="E252" s="38">
+      <c r="D252" s="40"/>
+      <c r="E252" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F252" s="38">
+      <c r="F252" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G252" s="37">
+      <c r="G252" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E252-F252</f>
         <v>0</v>
       </c>
@@ -11491,24 +11488,24 @@
       </c>
     </row>
     <row r="253" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B253" s="72" t="s">
+      <c r="B253" s="96" t="s">
         <v>494</v>
       </c>
-      <c r="C253" s="73" t="s">
+      <c r="C253" s="71" t="s">
         <v>495</v>
       </c>
-      <c r="D253" s="74">
+      <c r="D253" s="72">
         <v>49</v>
       </c>
-      <c r="E253" s="75">
+      <c r="E253" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F253" s="75">
+      <c r="F253" s="73">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
-      <c r="G253" s="76">
+      <c r="G253" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E253-F253</f>
         <v>29</v>
       </c>
@@ -11525,24 +11522,24 @@
       </c>
     </row>
     <row r="254" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B254" s="103" t="s">
+      <c r="B254" s="96" t="s">
         <v>496</v>
       </c>
-      <c r="C254" s="79" t="s">
+      <c r="C254" s="77" t="s">
         <v>497</v>
       </c>
-      <c r="D254" s="80">
+      <c r="D254" s="78">
         <v>126</v>
       </c>
-      <c r="E254" s="81">
+      <c r="E254" s="79">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F254" s="81">
+      <c r="F254" s="79">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G254" s="82">
+      <c r="G254" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E254-F254</f>
         <v>126</v>
       </c>
@@ -11556,22 +11553,22 @@
       </c>
     </row>
     <row r="255" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B255" s="103" t="s">
+      <c r="B255" s="96" t="s">
         <v>498</v>
       </c>
       <c r="C255" s="25" t="s">
         <v>499</v>
       </c>
-      <c r="D255" s="41"/>
-      <c r="E255" s="38">
+      <c r="D255" s="40"/>
+      <c r="E255" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F255" s="38">
+      <c r="F255" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G255" s="37">
+      <c r="G255" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E255-F255</f>
         <v>0</v>
       </c>
@@ -11585,24 +11582,24 @@
       </c>
     </row>
     <row r="256" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B256" s="103" t="s">
+      <c r="B256" s="96" t="s">
         <v>500</v>
       </c>
-      <c r="C256" s="73" t="s">
+      <c r="C256" s="71" t="s">
         <v>501</v>
       </c>
-      <c r="D256" s="74">
+      <c r="D256" s="72">
         <v>13</v>
       </c>
-      <c r="E256" s="75">
+      <c r="E256" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F256" s="75">
+      <c r="F256" s="73">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G256" s="76">
+      <c r="G256" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E256-F256</f>
         <v>13</v>
       </c>
@@ -11619,22 +11616,22 @@
       </c>
     </row>
     <row r="257" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B257" s="27" t="s">
+      <c r="B257" s="26" t="s">
         <v>504</v>
       </c>
       <c r="C257" s="25" t="s">
         <v>505</v>
       </c>
-      <c r="D257" s="41"/>
-      <c r="E257" s="38">
+      <c r="D257" s="40"/>
+      <c r="E257" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F257" s="38">
+      <c r="F257" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G257" s="37">
+      <c r="G257" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E257-F257</f>
         <v>0</v>
       </c>
@@ -11648,22 +11645,22 @@
       </c>
     </row>
     <row r="258" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B258" s="27" t="s">
+      <c r="B258" s="26" t="s">
         <v>506</v>
       </c>
       <c r="C258" s="25" t="s">
         <v>507</v>
       </c>
-      <c r="D258" s="41"/>
-      <c r="E258" s="38">
+      <c r="D258" s="40"/>
+      <c r="E258" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F258" s="38">
+      <c r="F258" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G258" s="37">
+      <c r="G258" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E258-F258</f>
         <v>0</v>
       </c>
@@ -11677,22 +11674,22 @@
       </c>
     </row>
     <row r="259" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B259" s="27" t="s">
+      <c r="B259" s="26" t="s">
         <v>508</v>
       </c>
       <c r="C259" s="25" t="s">
         <v>509</v>
       </c>
-      <c r="D259" s="41"/>
-      <c r="E259" s="38">
+      <c r="D259" s="40"/>
+      <c r="E259" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F259" s="38">
+      <c r="F259" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G259" s="37">
+      <c r="G259" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E259-F259</f>
         <v>0</v>
       </c>
@@ -11706,22 +11703,22 @@
       </c>
     </row>
     <row r="260" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B260" s="27" t="s">
+      <c r="B260" s="26" t="s">
         <v>510</v>
       </c>
       <c r="C260" s="25" t="s">
         <v>511</v>
       </c>
-      <c r="D260" s="41"/>
-      <c r="E260" s="38">
+      <c r="D260" s="40"/>
+      <c r="E260" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F260" s="38">
+      <c r="F260" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G260" s="37">
+      <c r="G260" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E260-F260</f>
         <v>0</v>
       </c>
@@ -11735,22 +11732,22 @@
       </c>
     </row>
     <row r="261" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B261" s="27" t="s">
+      <c r="B261" s="26" t="s">
         <v>512</v>
       </c>
       <c r="C261" s="25" t="s">
         <v>513</v>
       </c>
-      <c r="D261" s="41"/>
-      <c r="E261" s="38">
+      <c r="D261" s="40"/>
+      <c r="E261" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F261" s="38">
+      <c r="F261" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G261" s="37">
+      <c r="G261" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E261-F261</f>
         <v>0</v>
       </c>
@@ -11764,22 +11761,22 @@
       </c>
     </row>
     <row r="262" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B262" s="27" t="s">
+      <c r="B262" s="26" t="s">
         <v>514</v>
       </c>
       <c r="C262" s="25" t="s">
         <v>515</v>
       </c>
-      <c r="D262" s="41"/>
-      <c r="E262" s="38">
+      <c r="D262" s="40"/>
+      <c r="E262" s="37">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F262" s="38">
+      <c r="F262" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G262" s="37">
+      <c r="G262" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E262-F262</f>
         <v>0</v>
       </c>
@@ -11793,22 +11790,22 @@
       </c>
     </row>
     <row r="263" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B263" s="27" t="s">
+      <c r="B263" s="26" t="s">
         <v>516</v>
       </c>
       <c r="C263" s="25" t="s">
         <v>517</v>
       </c>
-      <c r="D263" s="41"/>
-      <c r="E263" s="38">
+      <c r="D263" s="40"/>
+      <c r="E263" s="37">
         <f t="shared" ref="E263:E292" si="17">SUMIF($J$4:$J$5000, B263, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F263" s="38">
+      <c r="F263" s="37">
         <f t="shared" ref="F263:F292" si="18">SUMIF($O$4:$O$5000, B263, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G263" s="37">
+      <c r="G263" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E263-F263</f>
         <v>0</v>
       </c>
@@ -11822,22 +11819,22 @@
       </c>
     </row>
     <row r="264" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B264" s="27" t="s">
+      <c r="B264" s="26" t="s">
         <v>518</v>
       </c>
       <c r="C264" s="25" t="s">
         <v>519</v>
       </c>
-      <c r="D264" s="41"/>
-      <c r="E264" s="38">
+      <c r="D264" s="40"/>
+      <c r="E264" s="37">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F264" s="38">
+      <c r="F264" s="37">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G264" s="37">
+      <c r="G264" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E264-F264</f>
         <v>0</v>
       </c>
@@ -11851,24 +11848,24 @@
       </c>
     </row>
     <row r="265" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B265" s="103" t="s">
+      <c r="B265" s="96" t="s">
         <v>502</v>
       </c>
-      <c r="C265" s="73" t="s">
+      <c r="C265" s="71" t="s">
         <v>503</v>
       </c>
-      <c r="D265" s="74">
+      <c r="D265" s="72">
         <v>79</v>
       </c>
-      <c r="E265" s="75">
+      <c r="E265" s="73">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F265" s="75">
+      <c r="F265" s="73">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G265" s="76">
+      <c r="G265" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E265-F265</f>
         <v>79</v>
       </c>
@@ -11882,23 +11879,23 @@
       </c>
     </row>
     <row r="266" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B266" s="103" t="s">
+      <c r="B266" s="96" t="s">
         <v>520</v>
       </c>
-      <c r="C266" s="60" t="s">
+      <c r="C266" s="58" t="s">
         <v>521</v>
       </c>
-      <c r="D266" s="58">
+      <c r="D266" s="57">
         <v>50</v>
       </c>
-      <c r="E266" s="61">
-        <v>0</v>
-      </c>
-      <c r="F266" s="61">
+      <c r="E266" s="59">
+        <v>0</v>
+      </c>
+      <c r="F266" s="59">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G266" s="62">
+      <c r="G266" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E266-F266</f>
         <v>50</v>
       </c>
@@ -11912,23 +11909,23 @@
       </c>
     </row>
     <row r="267" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B267" s="103" t="s">
+      <c r="B267" s="96" t="s">
         <v>522</v>
       </c>
-      <c r="C267" s="60" t="s">
+      <c r="C267" s="58" t="s">
         <v>523</v>
       </c>
-      <c r="D267" s="58">
+      <c r="D267" s="57">
         <v>9</v>
       </c>
-      <c r="E267" s="61">
-        <v>0</v>
-      </c>
-      <c r="F267" s="61">
+      <c r="E267" s="59">
+        <v>0</v>
+      </c>
+      <c r="F267" s="59">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G267" s="62">
+      <c r="G267" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E267-F267</f>
         <v>9</v>
       </c>
@@ -11942,27 +11939,27 @@
       </c>
     </row>
     <row r="268" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B268" s="103" t="s">
+      <c r="B268" s="96" t="s">
         <v>524</v>
       </c>
-      <c r="C268" s="60" t="s">
+      <c r="C268" s="58" t="s">
         <v>525</v>
       </c>
-      <c r="D268" s="58">
+      <c r="D268" s="57">
         <v>6</v>
       </c>
-      <c r="E268" s="61">
-        <v>0</v>
-      </c>
-      <c r="F268" s="61">
+      <c r="E268" s="59">
+        <v>0</v>
+      </c>
+      <c r="F268" s="59">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G268" s="62">
+      <c r="G268" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E268-F268</f>
         <v>6</v>
       </c>
-      <c r="H268" s="64" t="s">
+      <c r="H268" s="62" t="s">
         <v>580</v>
       </c>
       <c r="K268" s="19" t="str">
@@ -11975,23 +11972,23 @@
       </c>
     </row>
     <row r="269" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B269" s="103" t="s">
+      <c r="B269" s="96" t="s">
         <v>526</v>
       </c>
-      <c r="C269" s="60" t="s">
+      <c r="C269" s="58" t="s">
         <v>527</v>
       </c>
-      <c r="D269" s="58">
+      <c r="D269" s="57">
         <v>10</v>
       </c>
-      <c r="E269" s="61">
-        <v>0</v>
-      </c>
-      <c r="F269" s="61">
+      <c r="E269" s="59">
+        <v>0</v>
+      </c>
+      <c r="F269" s="59">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G269" s="62">
+      <c r="G269" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E269-F269</f>
         <v>10</v>
       </c>
@@ -12005,22 +12002,22 @@
       </c>
     </row>
     <row r="270" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B270" s="72" t="s">
+      <c r="B270" s="70" t="s">
         <v>528</v>
       </c>
-      <c r="C270" s="73" t="s">
+      <c r="C270" s="71" t="s">
         <v>529</v>
       </c>
-      <c r="D270" s="74"/>
-      <c r="E270" s="75">
+      <c r="D270" s="72"/>
+      <c r="E270" s="73">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F270" s="75">
+      <c r="F270" s="73">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G270" s="76">
+      <c r="G270" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E270-F270</f>
         <v>0</v>
       </c>
@@ -12034,22 +12031,22 @@
       </c>
     </row>
     <row r="271" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B271" s="27" t="s">
+      <c r="B271" s="26" t="s">
         <v>530</v>
       </c>
       <c r="C271" s="25" t="s">
         <v>531</v>
       </c>
-      <c r="D271" s="41"/>
-      <c r="E271" s="38">
+      <c r="D271" s="40"/>
+      <c r="E271" s="37">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F271" s="38">
+      <c r="F271" s="37">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G271" s="37">
+      <c r="G271" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E271-F271</f>
         <v>0</v>
       </c>
@@ -12063,23 +12060,23 @@
       </c>
     </row>
     <row r="272" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B272" s="103" t="s">
+      <c r="B272" s="96" t="s">
         <v>532</v>
       </c>
-      <c r="C272" s="60" t="s">
+      <c r="C272" s="58" t="s">
         <v>533</v>
       </c>
-      <c r="D272" s="58">
+      <c r="D272" s="57">
         <v>17</v>
       </c>
-      <c r="E272" s="61">
-        <v>0</v>
-      </c>
-      <c r="F272" s="61">
+      <c r="E272" s="59">
+        <v>0</v>
+      </c>
+      <c r="F272" s="59">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G272" s="62">
+      <c r="G272" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E272-F272</f>
         <v>17</v>
       </c>
@@ -12093,23 +12090,23 @@
       </c>
     </row>
     <row r="273" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B273" s="103" t="s">
+      <c r="B273" s="96" t="s">
         <v>534</v>
       </c>
-      <c r="C273" s="60" t="s">
+      <c r="C273" s="58" t="s">
         <v>535</v>
       </c>
-      <c r="D273" s="58">
+      <c r="D273" s="57">
         <v>7</v>
       </c>
-      <c r="E273" s="61">
-        <v>0</v>
-      </c>
-      <c r="F273" s="61">
+      <c r="E273" s="59">
+        <v>0</v>
+      </c>
+      <c r="F273" s="59">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G273" s="62">
+      <c r="G273" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E273-F273</f>
         <v>7</v>
       </c>
@@ -12123,22 +12120,22 @@
       </c>
     </row>
     <row r="274" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B274" s="27" t="s">
+      <c r="B274" s="26" t="s">
         <v>536</v>
       </c>
       <c r="C274" s="25" t="s">
         <v>537</v>
       </c>
-      <c r="D274" s="41"/>
-      <c r="E274" s="38">
+      <c r="D274" s="40"/>
+      <c r="E274" s="37">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F274" s="38">
+      <c r="F274" s="37">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G274" s="37">
+      <c r="G274" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E274-F274</f>
         <v>0</v>
       </c>
@@ -12152,22 +12149,22 @@
       </c>
     </row>
     <row r="275" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B275" s="27" t="s">
+      <c r="B275" s="26" t="s">
         <v>538</v>
       </c>
       <c r="C275" s="25" t="s">
         <v>539</v>
       </c>
-      <c r="D275" s="41"/>
-      <c r="E275" s="38">
+      <c r="D275" s="40"/>
+      <c r="E275" s="37">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F275" s="38">
+      <c r="F275" s="37">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G275" s="37">
+      <c r="G275" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E275-F275</f>
         <v>0</v>
       </c>
@@ -12181,22 +12178,22 @@
       </c>
     </row>
     <row r="276" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B276" s="27" t="s">
+      <c r="B276" s="26" t="s">
         <v>540</v>
       </c>
       <c r="C276" s="25" t="s">
         <v>541</v>
       </c>
-      <c r="D276" s="41"/>
-      <c r="E276" s="38">
+      <c r="D276" s="40"/>
+      <c r="E276" s="37">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F276" s="38">
+      <c r="F276" s="37">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G276" s="37">
+      <c r="G276" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E276-F276</f>
         <v>0</v>
       </c>
@@ -12210,24 +12207,24 @@
       </c>
     </row>
     <row r="277" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B277" s="72" t="s">
+      <c r="B277" s="70" t="s">
         <v>542</v>
       </c>
-      <c r="C277" s="73" t="s">
+      <c r="C277" s="71" t="s">
         <v>543</v>
       </c>
-      <c r="D277" s="74">
+      <c r="D277" s="72">
         <v>44</v>
       </c>
-      <c r="E277" s="75">
+      <c r="E277" s="73">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F277" s="75">
+      <c r="F277" s="73">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G277" s="76">
+      <c r="G277" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E277-F277</f>
         <v>44</v>
       </c>
@@ -12241,24 +12238,24 @@
       </c>
     </row>
     <row r="278" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B278" s="72" t="s">
+      <c r="B278" s="70" t="s">
         <v>544</v>
       </c>
-      <c r="C278" s="73" t="s">
+      <c r="C278" s="71" t="s">
         <v>543</v>
       </c>
-      <c r="D278" s="74">
+      <c r="D278" s="72">
         <v>15</v>
       </c>
-      <c r="E278" s="75">
+      <c r="E278" s="73">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F278" s="75">
+      <c r="F278" s="73">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G278" s="76">
+      <c r="G278" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E278-F278</f>
         <v>15</v>
       </c>
@@ -12272,24 +12269,24 @@
       </c>
     </row>
     <row r="279" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B279" s="72" t="s">
+      <c r="B279" s="70" t="s">
         <v>545</v>
       </c>
-      <c r="C279" s="73" t="s">
+      <c r="C279" s="71" t="s">
         <v>546</v>
       </c>
-      <c r="D279" s="74">
+      <c r="D279" s="72">
         <v>10</v>
       </c>
-      <c r="E279" s="75">
+      <c r="E279" s="73">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F279" s="75">
+      <c r="F279" s="73">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G279" s="76">
+      <c r="G279" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E279-F279</f>
         <v>10</v>
       </c>
@@ -12303,22 +12300,22 @@
       </c>
     </row>
     <row r="280" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B280" s="27" t="s">
+      <c r="B280" s="26" t="s">
         <v>547</v>
       </c>
       <c r="C280" s="25" t="s">
         <v>548</v>
       </c>
-      <c r="D280" s="41"/>
-      <c r="E280" s="38">
+      <c r="D280" s="40"/>
+      <c r="E280" s="37">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F280" s="38">
+      <c r="F280" s="37">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G280" s="37">
+      <c r="G280" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E280-F280</f>
         <v>0</v>
       </c>
@@ -12331,125 +12328,125 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="2:16" s="66" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B281" s="78" t="s">
+    <row r="281" spans="2:16" s="64" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B281" s="76" t="s">
         <v>549</v>
       </c>
-      <c r="C281" s="79" t="s">
+      <c r="C281" s="77" t="s">
         <v>550</v>
       </c>
-      <c r="D281" s="80">
+      <c r="D281" s="78">
         <v>6</v>
       </c>
-      <c r="E281" s="81">
+      <c r="E281" s="79">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F281" s="81">
+      <c r="F281" s="79">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G281" s="82">
+      <c r="G281" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E281-F281</f>
         <v>6</v>
       </c>
       <c r="H281"/>
-      <c r="K281" s="67" t="str">
+      <c r="K281" s="65" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="P281" s="67" t="str">
+      <c r="P281" s="65" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="282" spans="2:16" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B282" s="78" t="s">
+    <row r="282" spans="2:16" s="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B282" s="76" t="s">
         <v>551</v>
       </c>
-      <c r="C282" s="79" t="s">
+      <c r="C282" s="77" t="s">
         <v>552</v>
       </c>
-      <c r="D282" s="80">
+      <c r="D282" s="78">
         <v>5</v>
       </c>
-      <c r="E282" s="81">
+      <c r="E282" s="79">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F282" s="81">
+      <c r="F282" s="79">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G282" s="82">
+      <c r="G282" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E282-F282</f>
         <v>5</v>
       </c>
       <c r="H282"/>
-      <c r="K282" s="83" t="str">
+      <c r="K282" s="81" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="P282" s="83" t="str">
+      <c r="P282" s="81" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="283" spans="2:16" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B283" s="78" t="s">
+    <row r="283" spans="2:16" s="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B283" s="76" t="s">
         <v>553</v>
       </c>
-      <c r="C283" s="79" t="s">
+      <c r="C283" s="77" t="s">
         <v>554</v>
       </c>
-      <c r="D283" s="80">
+      <c r="D283" s="78">
         <v>7</v>
       </c>
-      <c r="E283" s="81">
+      <c r="E283" s="79">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F283" s="81">
+      <c r="F283" s="79">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G283" s="82">
+      <c r="G283" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E283-F283</f>
         <v>7</v>
       </c>
       <c r="H283"/>
-      <c r="K283" s="83" t="str">
+      <c r="K283" s="81" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="P283" s="83" t="str">
+      <c r="P283" s="81" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="284" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B284" s="78" t="s">
+      <c r="B284" s="76" t="s">
         <v>555</v>
       </c>
-      <c r="C284" s="79" t="s">
+      <c r="C284" s="77" t="s">
         <v>556</v>
       </c>
-      <c r="D284" s="80">
+      <c r="D284" s="78">
         <v>6</v>
       </c>
-      <c r="E284" s="81">
+      <c r="E284" s="79">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F284" s="81">
+      <c r="F284" s="79">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G284" s="82">
+      <c r="G284" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E284-F284</f>
         <v>6</v>
       </c>
-      <c r="H284" s="69"/>
+      <c r="H284" s="67"/>
       <c r="K284" s="19" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -12460,28 +12457,28 @@
       </c>
     </row>
     <row r="285" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B285" s="78" t="s">
+      <c r="B285" s="76" t="s">
         <v>557</v>
       </c>
-      <c r="C285" s="79" t="s">
+      <c r="C285" s="77" t="s">
         <v>558</v>
       </c>
-      <c r="D285" s="80">
+      <c r="D285" s="78">
         <v>43</v>
       </c>
-      <c r="E285" s="81">
+      <c r="E285" s="79">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F285" s="81">
+      <c r="F285" s="79">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G285" s="82">
+      <c r="G285" s="80">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E285-F285</f>
         <v>43</v>
       </c>
-      <c r="H285" s="69"/>
+      <c r="H285" s="67"/>
       <c r="K285" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -12492,22 +12489,22 @@
       </c>
     </row>
     <row r="286" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B286" s="27" t="s">
+      <c r="B286" s="26" t="s">
         <v>559</v>
       </c>
       <c r="C286" s="25" t="s">
         <v>560</v>
       </c>
-      <c r="D286" s="41"/>
-      <c r="E286" s="38">
+      <c r="D286" s="40"/>
+      <c r="E286" s="37">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F286" s="38">
+      <c r="F286" s="37">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G286" s="37">
+      <c r="G286" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E286-F286</f>
         <v>0</v>
       </c>
@@ -12521,22 +12518,22 @@
       </c>
     </row>
     <row r="287" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B287" s="27" t="s">
+      <c r="B287" s="26" t="s">
         <v>561</v>
       </c>
       <c r="C287" s="25" t="s">
         <v>562</v>
       </c>
-      <c r="D287" s="41"/>
-      <c r="E287" s="38">
+      <c r="D287" s="40"/>
+      <c r="E287" s="37">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F287" s="38">
+      <c r="F287" s="37">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G287" s="37">
+      <c r="G287" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E287-F287</f>
         <v>0</v>
       </c>
@@ -12549,60 +12546,60 @@
         <v/>
       </c>
     </row>
-    <row r="288" spans="2:16" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B288" s="57" t="s">
+    <row r="288" spans="2:16" s="64" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B288" s="56" t="s">
         <v>567</v>
       </c>
       <c r="C288" s="17"/>
       <c r="D288" s="17"/>
-      <c r="E288" s="38">
+      <c r="E288" s="37">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F288" s="38">
+      <c r="F288" s="37">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G288" s="37">
+      <c r="G288" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E288-F288</f>
         <v>0</v>
       </c>
       <c r="H288"/>
-      <c r="J288" s="66" t="str">
+      <c r="J288" s="64" t="str">
         <f t="shared" ref="J288:J351" si="20">IF(I288="", "", IFERROR(VLOOKUP(I288&amp;"", $B$4:$C$5005, 2, FALSE), "NO EXISTE"))</f>
         <v/>
       </c>
-      <c r="O288" s="66" t="str">
+      <c r="O288" s="64" t="str">
         <f t="shared" ref="O288:O351" si="21">IF(N288="", "", IFERROR(VLOOKUP(N288&amp;"", $B$4:$C$5005, 2, FALSE), "NO EXISTE"))</f>
         <v/>
       </c>
     </row>
-    <row r="289" spans="2:15" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B289" s="27" t="s">
+    <row r="289" spans="2:15" s="64" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B289" s="26" t="s">
         <v>563</v>
       </c>
       <c r="C289" s="25" t="s">
         <v>564</v>
       </c>
-      <c r="D289" s="41"/>
-      <c r="E289" s="38">
+      <c r="D289" s="40"/>
+      <c r="E289" s="37">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F289" s="38">
+      <c r="F289" s="37">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G289" s="37">
+      <c r="G289" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E289-F289</f>
         <v>0</v>
       </c>
       <c r="H289"/>
-      <c r="J289" s="66" t="str">
+      <c r="J289" s="64" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="O289" s="66" t="str">
+      <c r="O289" s="64" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -12614,16 +12611,16 @@
       <c r="C290" s="25" t="s">
         <v>566</v>
       </c>
-      <c r="D290" s="41"/>
-      <c r="E290" s="38">
+      <c r="D290" s="40"/>
+      <c r="E290" s="37">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F290" s="38">
+      <c r="F290" s="37">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G290" s="37">
+      <c r="G290" s="36">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E290-F290</f>
         <v>0</v>
       </c>
@@ -12637,25 +12634,25 @@
       </c>
     </row>
     <row r="291" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B291" s="65" t="s">
+      <c r="B291" s="63" t="s">
         <v>582</v>
       </c>
-      <c r="C291" s="65" t="s">
+      <c r="C291" s="63" t="s">
         <v>583</v>
       </c>
-      <c r="D291" s="68" t="s">
+      <c r="D291" s="66" t="s">
         <v>585</v>
       </c>
-      <c r="E291" s="61"/>
-      <c r="F291" s="61">
+      <c r="E291" s="59"/>
+      <c r="F291" s="59">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G291" s="62">
+      <c r="G291" s="60">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E291-F291</f>
         <v>1</v>
       </c>
-      <c r="H291" s="66"/>
+      <c r="H291" s="64"/>
       <c r="J291" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -12666,28 +12663,28 @@
       </c>
     </row>
     <row r="292" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B292" s="105" t="s">
+      <c r="B292" s="98" t="s">
         <v>246</v>
       </c>
-      <c r="C292" s="92" t="s">
+      <c r="C292" s="90" t="s">
         <v>584</v>
       </c>
-      <c r="D292" s="91">
+      <c r="D292" s="89">
         <v>1360</v>
       </c>
-      <c r="E292" s="75">
+      <c r="E292" s="73">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="F292" s="75">
+      <c r="F292" s="73">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G292" s="76">
+      <c r="G292" s="74">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E292-F292</f>
         <v>1360</v>
       </c>
-      <c r="H292" s="66"/>
+      <c r="H292" s="64"/>
       <c r="J292" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -12698,22 +12695,22 @@
       </c>
     </row>
     <row r="293" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B293" s="90" t="s">
+      <c r="B293" s="88" t="s">
         <v>587</v>
       </c>
-      <c r="C293" s="90"/>
-      <c r="D293" s="91" t="s">
+      <c r="C293" s="88"/>
+      <c r="D293" s="89" t="s">
         <v>588</v>
       </c>
-      <c r="E293" s="91">
+      <c r="E293" s="89">
         <f>SUMIF($J$4:$J$5000, B293, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F293" s="91">
+      <c r="F293" s="89">
         <f>SUMIF($O$4:$O$5000, B293, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G293" s="91">
+      <c r="G293" s="89">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E293-F293</f>
         <v>400</v>
       </c>
@@ -12727,16 +12724,16 @@
       </c>
     </row>
     <row r="294" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B294" s="72" t="s">
+      <c r="B294" s="70" t="s">
         <v>408</v>
       </c>
-      <c r="C294" s="90"/>
-      <c r="D294" s="91" t="s">
+      <c r="C294" s="88"/>
+      <c r="D294" s="89" t="s">
         <v>594</v>
       </c>
-      <c r="E294" s="91"/>
-      <c r="F294" s="91"/>
-      <c r="G294" s="91"/>
+      <c r="E294" s="89"/>
+      <c r="F294" s="89"/>
+      <c r="G294" s="89"/>
       <c r="J294" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -12747,22 +12744,22 @@
       </c>
     </row>
     <row r="295" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B295" s="72" t="s">
+      <c r="B295" s="70" t="s">
         <v>597</v>
       </c>
-      <c r="C295" s="90"/>
-      <c r="D295" s="91" t="s">
+      <c r="C295" s="88"/>
+      <c r="D295" s="89" t="s">
         <v>594</v>
       </c>
-      <c r="E295" s="91">
+      <c r="E295" s="89">
         <f t="shared" ref="E295:E302" si="22">SUMIF($J$4:$J$5000, B295, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F295" s="91">
+      <c r="F295" s="89">
         <f t="shared" ref="F295:F302" si="23">SUMIF($O$4:$O$5000, B295, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G295" s="91">
+      <c r="G295" s="89">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E295-F295</f>
         <v>50</v>
       </c>
@@ -12776,22 +12773,22 @@
       </c>
     </row>
     <row r="296" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B296" s="90" t="s">
+      <c r="B296" s="88" t="s">
         <v>598</v>
       </c>
-      <c r="C296" s="90"/>
-      <c r="D296" s="92" t="s">
+      <c r="C296" s="88"/>
+      <c r="D296" s="90" t="s">
         <v>599</v>
       </c>
-      <c r="E296" s="91">
+      <c r="E296" s="89">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F296" s="91">
+      <c r="F296" s="89">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G296" s="93">
+      <c r="G296" s="91">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E296-F296</f>
         <v>91</v>
       </c>
@@ -12805,22 +12802,22 @@
       </c>
     </row>
     <row r="297" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B297" s="94" t="s">
+      <c r="B297" s="92" t="s">
         <v>610</v>
       </c>
-      <c r="C297" s="94"/>
-      <c r="D297" s="95" t="s">
+      <c r="C297" s="92"/>
+      <c r="D297" s="93" t="s">
         <v>611</v>
       </c>
-      <c r="E297" s="96">
+      <c r="E297" s="94">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F297" s="96">
+      <c r="F297" s="94">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G297" s="97">
+      <c r="G297" s="95">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E297-F297</f>
         <v>8</v>
       </c>
@@ -12834,24 +12831,24 @@
       </c>
     </row>
     <row r="298" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B298" s="94" t="s">
+      <c r="B298" s="92" t="s">
         <v>612</v>
       </c>
-      <c r="C298" s="94" t="s">
+      <c r="C298" s="92" t="s">
         <v>613</v>
       </c>
-      <c r="D298" s="95" t="s">
+      <c r="D298" s="93" t="s">
         <v>614</v>
       </c>
-      <c r="E298" s="96">
+      <c r="E298" s="94">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F298" s="96">
+      <c r="F298" s="94">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G298" s="97">
+      <c r="G298" s="95">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E298-F298</f>
         <v>35</v>
       </c>
@@ -12865,22 +12862,22 @@
       </c>
     </row>
     <row r="299" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B299" s="94" t="s">
+      <c r="B299" s="92" t="s">
         <v>615</v>
       </c>
-      <c r="C299" s="94"/>
-      <c r="D299" s="95" t="s">
+      <c r="C299" s="92"/>
+      <c r="D299" s="93" t="s">
         <v>616</v>
       </c>
-      <c r="E299" s="96">
+      <c r="E299" s="94">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F299" s="96">
+      <c r="F299" s="94">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G299" s="97">
+      <c r="G299" s="95">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E299-F299</f>
         <v>192</v>
       </c>
@@ -12894,22 +12891,22 @@
       </c>
     </row>
     <row r="300" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B300" s="94">
+      <c r="B300" s="92">
         <v>41040</v>
       </c>
-      <c r="C300" s="94"/>
-      <c r="D300" s="95" t="s">
+      <c r="C300" s="92"/>
+      <c r="D300" s="93" t="s">
         <v>590</v>
       </c>
-      <c r="E300" s="96">
+      <c r="E300" s="94">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F300" s="96">
+      <c r="F300" s="94">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G300" s="97">
+      <c r="G300" s="95">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E300-F300</f>
         <v>100</v>
       </c>
@@ -12923,22 +12920,22 @@
       </c>
     </row>
     <row r="301" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B301" s="94" t="s">
+      <c r="B301" s="92" t="s">
         <v>617</v>
       </c>
-      <c r="C301" s="94"/>
-      <c r="D301" s="95" t="s">
+      <c r="C301" s="92"/>
+      <c r="D301" s="93" t="s">
         <v>618</v>
       </c>
-      <c r="E301" s="96">
+      <c r="E301" s="94">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F301" s="96">
+      <c r="F301" s="94">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G301" s="97">
+      <c r="G301" s="95">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E301-F301</f>
         <v>15</v>
       </c>
@@ -12951,23 +12948,23 @@
         <v/>
       </c>
     </row>
-    <row r="302" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B302" s="78" t="s">
+    <row r="302" spans="2:15" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B302" s="76" t="s">
         <v>619</v>
       </c>
-      <c r="C302" s="94"/>
-      <c r="D302" s="95" t="s">
+      <c r="C302" s="92"/>
+      <c r="D302" s="93" t="s">
         <v>585</v>
       </c>
-      <c r="E302" s="96">
+      <c r="E302" s="94">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F302" s="96">
+      <c r="F302" s="94">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G302" s="97">
+      <c r="G302" s="95">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E302-F302</f>
         <v>1</v>
       </c>
@@ -12981,22 +12978,22 @@
       </c>
     </row>
     <row r="303" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B303" s="94">
+      <c r="B303" s="92">
         <v>8003</v>
       </c>
-      <c r="C303" s="94"/>
-      <c r="D303" s="95" t="s">
+      <c r="C303" s="92"/>
+      <c r="D303" s="93" t="s">
         <v>623</v>
       </c>
-      <c r="E303" s="96">
+      <c r="E303" s="94">
         <f>SUMIF($J$4:$J$5000, B303, $M$4:$M$5000)</f>
         <v>0</v>
       </c>
-      <c r="F303" s="96">
+      <c r="F303" s="94">
         <f>SUMIF($O$4:$O$5000, B303, $R$4:$R$5000)</f>
         <v>0</v>
       </c>
-      <c r="G303" s="97">
+      <c r="G303" s="95">
         <f>PRODUCTOS[[#This Row],[CONTEO INICIAL]]+E303-F303</f>
         <v>20</v>
       </c>
@@ -13010,10 +13007,10 @@
       </c>
     </row>
     <row r="304" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="D304" s="71"/>
-      <c r="E304" s="71"/>
-      <c r="F304" s="71"/>
-      <c r="G304" s="71"/>
+      <c r="D304" s="69"/>
+      <c r="E304" s="69"/>
+      <c r="F304" s="69"/>
+      <c r="G304" s="69"/>
       <c r="J304" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -15049,28 +15046,28 @@
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="102"/>
+      <c r="B2" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="103"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="100" t="s">
+      <c r="I2" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="103"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="100" t="s">
+      <c r="N2" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="102"/>
+      <c r="O2" s="102"/>
+      <c r="P2" s="102"/>
+      <c r="Q2" s="103"/>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -15081,40 +15078,40 @@
       <c r="C3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="42" t="s">
+      <c r="E3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="29" t="s">
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="30" t="s">
+      <c r="J3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="30" t="s">
+      <c r="K3" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="31" t="s">
+      <c r="L3" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="32"/>
-      <c r="N3" s="29" t="s">
+      <c r="M3" s="31"/>
+      <c r="N3" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="O3" s="30" t="s">
+      <c r="O3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="30" t="s">
+      <c r="P3" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="Q3" s="31" t="s">
+      <c r="Q3" s="30" t="s">
         <v>9</v>
       </c>
       <c r="R3" s="1"/>

--- a/INVENTARIO_AMPERIAL_2026.xlsx
+++ b/INVENTARIO_AMPERIAL_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Amperial Website\AmperialWebsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7C9522-A676-4A78-A384-4B47D353DE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1901AEE9-32ED-456F-AF68-9B29D181D2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1905" yWindow="1905" windowWidth="11520" windowHeight="7995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2450,7 +2450,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2736,6 +2736,9 @@
     <xf numFmtId="49" fontId="9" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="15" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2747,7 +2750,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="15" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3278,27 +3281,27 @@
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
+      <c r="B2" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
       <c r="H2" s="1"/>
-      <c r="J2" s="99" t="s">
+      <c r="J2" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="O2" s="99" t="s">
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="O2" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="99"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
+      <c r="R2" s="100"/>
       <c r="T2" s="55" t="s">
         <v>574</v>
       </c>
@@ -3363,7 +3366,7 @@
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="99" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="24" t="s">
@@ -8635,7 +8638,7 @@
       </c>
     </row>
     <row r="158" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B158" s="76" t="s">
+      <c r="B158" s="96" t="s">
         <v>310</v>
       </c>
       <c r="C158" s="77" t="s">
@@ -9499,7 +9502,7 @@
       </c>
     </row>
     <row r="187" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B187" s="70" t="s">
+      <c r="B187" s="96" t="s">
         <v>604</v>
       </c>
       <c r="C187" s="71" t="s">
@@ -9530,7 +9533,7 @@
       </c>
     </row>
     <row r="188" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B188" s="26" t="s">
+      <c r="B188" s="96" t="s">
         <v>375</v>
       </c>
       <c r="C188" s="25" t="s">
@@ -9559,7 +9562,7 @@
       </c>
     </row>
     <row r="189" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B189" s="70" t="s">
+      <c r="B189" s="96" t="s">
         <v>369</v>
       </c>
       <c r="C189" s="71" t="s">
@@ -9590,7 +9593,7 @@
       </c>
     </row>
     <row r="190" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B190" s="70" t="s">
+      <c r="B190" s="96" t="s">
         <v>371</v>
       </c>
       <c r="C190" s="71" t="s">
@@ -12300,7 +12303,7 @@
       </c>
     </row>
     <row r="280" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B280" s="26" t="s">
+      <c r="B280" s="96" t="s">
         <v>547</v>
       </c>
       <c r="C280" s="25" t="s">
@@ -12329,7 +12332,7 @@
       </c>
     </row>
     <row r="281" spans="2:16" s="64" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B281" s="76" t="s">
+      <c r="B281" s="96" t="s">
         <v>549</v>
       </c>
       <c r="C281" s="77" t="s">
@@ -12361,7 +12364,7 @@
       </c>
     </row>
     <row r="282" spans="2:16" s="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B282" s="76" t="s">
+      <c r="B282" s="96" t="s">
         <v>551</v>
       </c>
       <c r="C282" s="77" t="s">
@@ -12393,7 +12396,7 @@
       </c>
     </row>
     <row r="283" spans="2:16" s="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B283" s="76" t="s">
+      <c r="B283" s="96" t="s">
         <v>553</v>
       </c>
       <c r="C283" s="77" t="s">
@@ -12425,7 +12428,7 @@
       </c>
     </row>
     <row r="284" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B284" s="76" t="s">
+      <c r="B284" s="96" t="s">
         <v>555</v>
       </c>
       <c r="C284" s="77" t="s">
@@ -12457,7 +12460,7 @@
       </c>
     </row>
     <row r="285" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B285" s="76" t="s">
+      <c r="B285" s="96" t="s">
         <v>557</v>
       </c>
       <c r="C285" s="77" t="s">
@@ -12831,7 +12834,7 @@
       </c>
     </row>
     <row r="298" spans="2:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B298" s="92" t="s">
+      <c r="B298" s="105" t="s">
         <v>612</v>
       </c>
       <c r="C298" s="92" t="s">
@@ -15046,28 +15049,28 @@
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="103"/>
+      <c r="B2" s="102" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="104"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="101" t="s">
+      <c r="I2" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="104"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="101" t="s">
+      <c r="N2" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="102"/>
-      <c r="P2" s="102"/>
-      <c r="Q2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="104"/>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
